--- a/StructureDefinition-mii-pr-seltene-kopfumfang.xlsx
+++ b/StructureDefinition-mii-pr-seltene-kopfumfang.xlsx
@@ -9,14 +9,11 @@
     <sheet name="Metadata" r:id="rId3" sheetId="1"/>
     <sheet name="Elements" r:id="rId4" sheetId="2"/>
   </sheets>
-  <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="true">Elements!$A$1:$AK$119</definedName>
-  </definedNames>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="4025" uniqueCount="547">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="3257" uniqueCount="508">
   <si>
     <t>Property</t>
   </si>
@@ -33,7 +30,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>2027.0.0-ballot.rc1</t>
+    <t>2027.0.0-ballot</t>
   </si>
   <si>
     <t>Name</t>
@@ -57,10 +54,13 @@
     <t>Experimental</t>
   </si>
   <si>
+    <t>false</t>
+  </si>
+  <si>
     <t>Date</t>
   </si>
   <si>
-    <t>2026-09-09T13:15:21+00:00</t>
+    <t>2026-09-14T22:11:28+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
@@ -84,7 +84,7 @@
     <t>Description</t>
   </si>
   <si>
-    <t>Profil zur Dokumentation des Kopfumfangs (okzipital-frontal) eines Patienten. Besonders relevant bei seltenen Erkrankungen mit Auswirkungen auf das Schädelwachstum, z.B. Skelettdysplasien, neurologische Erkrankungen. Erbt vom MII ICU Kopfumfang-Profil.</t>
+    <t>Profil zur Dokumentation des Kopfumfangs (okzipital-frontal) eines Patienten. Besonders relevant bei seltenen Erkrankungen mit Auswirkungen auf das Schädelwachstum, z.B. Skelettdysplasien, neurologische Erkrankungen. Erbt vom deutschen Basisprofil für den Vitalparameter Kopfumfang.</t>
   </si>
   <si>
     <t>Purpose</t>
@@ -114,13 +114,10 @@
     <t>Base Definition</t>
   </si>
   <si>
-    <t>https://www.medizininformatik-initiative.de/fhir/ext/modul-icu/StructureDefinition/mii-pr-icu-muv-kopfumfang</t>
+    <t>http://fhir.de/StructureDefinition/observation-de-vitalsign-kopfumfang</t>
   </si>
   <si>
     <t>Abstract</t>
-  </si>
-  <si>
-    <t>false</t>
   </si>
   <si>
     <t>Derivation</t>
@@ -601,24 +598,35 @@
 &lt;/valueCodeableConcept&gt;</t>
   </si>
   <si>
-    <t>Observation.category:sct</t>
-  </si>
-  <si>
-    <t>sct</t>
-  </si>
-  <si>
-    <t>&lt;valueCodeableConcept xmlns="http://hl7.org/fhir"&gt;
-  &lt;coding&gt;
-    &lt;system value="http://snomed.info/sct"/&gt;
-    &lt;code value="248326004"/&gt;
-  &lt;/coding&gt;
-&lt;/valueCodeableConcept&gt;</t>
-  </si>
-  <si>
-    <t>Observation.category:sct.id</t>
-  </si>
-  <si>
-    <t>Observation.category.id</t>
+    <t>Observation.code</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Name
+</t>
+  </si>
+  <si>
+    <t>Kopfumfang okzipital-frontal</t>
+  </si>
+  <si>
+    <t>Describes what was observed. Sometimes this is called the observation "name".</t>
+  </si>
+  <si>
+    <t>*All* code-value and, if present, component.code-component.value pairs need to be taken into account to correctly understand the meaning of the observation.</t>
+  </si>
+  <si>
+    <t>Knowing what kind of observation is being made is essential to understanding the observation.</t>
+  </si>
+  <si>
+    <t>example</t>
+  </si>
+  <si>
+    <t>Codes identifying names of simple observations.</t>
+  </si>
+  <si>
+    <t>http://hl7.org/fhir/ValueSet/observation-codes</t>
+  </si>
+  <si>
+    <t>Observation.code.id</t>
   </si>
   <si>
     <t xml:space="preserve">string
@@ -634,10 +642,7 @@
     <t>Element.id</t>
   </si>
   <si>
-    <t>Observation.category:sct.extension</t>
-  </si>
-  <si>
-    <t>Observation.category.extension</t>
+    <t>Observation.code.extension</t>
   </si>
   <si>
     <t>May be used to represent additional information that is not part of the basic definition of the element. To make the use of extensions safe and manageable, there is a strict set of governance  applied to the definition and use of extensions. Though any implementer can define an extension, there is a set of requirements that SHALL be met as part of the definition of the extension.</t>
@@ -646,10 +651,7 @@
     <t>Element.extension</t>
   </si>
   <si>
-    <t>Observation.category:sct.coding</t>
-  </si>
-  <si>
-    <t>Observation.category.coding</t>
+    <t>Observation.code.coding</t>
   </si>
   <si>
     <t xml:space="preserve">Coding
@@ -668,30 +670,16 @@
     <t>Allows for alternative encodings within a code system, and translations to other code systems.</t>
   </si>
   <si>
-    <t>&lt;valueCoding xmlns="http://hl7.org/fhir"&gt;
-  &lt;system value="http://snomed.info/sct"/&gt;
-&lt;/valueCoding&gt;</t>
-  </si>
-  <si>
     <t>CodeableConcept.coding</t>
   </si>
   <si>
-    <t>Observation.category:sct.coding.id</t>
-  </si>
-  <si>
-    <t>Observation.category.coding.id</t>
-  </si>
-  <si>
-    <t>Observation.category:sct.coding.extension</t>
-  </si>
-  <si>
-    <t>Observation.category.coding.extension</t>
-  </si>
-  <si>
-    <t>Observation.category:sct.coding.system</t>
-  </si>
-  <si>
-    <t>Observation.category.coding.system</t>
+    <t>Observation.code.coding.id</t>
+  </si>
+  <si>
+    <t>Observation.code.coding.extension</t>
+  </si>
+  <si>
+    <t>Observation.code.coding.system</t>
   </si>
   <si>
     <t>Identity of the terminology system</t>
@@ -709,10 +697,7 @@
     <t>Coding.system</t>
   </si>
   <si>
-    <t>Observation.category:sct.coding.version</t>
-  </si>
-  <si>
-    <t>Observation.category.coding.version</t>
+    <t>Observation.code.coding.version</t>
   </si>
   <si>
     <t>Version of the system - if relevant</t>
@@ -727,10 +712,7 @@
     <t>Coding.version</t>
   </si>
   <si>
-    <t>Observation.category:sct.coding.code</t>
-  </si>
-  <si>
-    <t>Observation.category.coding.code</t>
+    <t>Observation.code.coding.code</t>
   </si>
   <si>
     <t>Symbol in syntax defined by the system</t>
@@ -748,10 +730,7 @@
     <t>Coding.code</t>
   </si>
   <si>
-    <t>Observation.category:sct.coding.display</t>
-  </si>
-  <si>
-    <t>Observation.category.coding.display</t>
+    <t>Observation.code.coding.display</t>
   </si>
   <si>
     <t>Representation defined by the system</t>
@@ -766,10 +745,7 @@
     <t>Coding.display</t>
   </si>
   <si>
-    <t>Observation.category:sct.coding.userSelected</t>
-  </si>
-  <si>
-    <t>Observation.category.coding.userSelected</t>
+    <t>Observation.code.coding.userSelected</t>
   </si>
   <si>
     <t xml:space="preserve">boolean
@@ -789,88 +765,6 @@
   </si>
   <si>
     <t>Coding.userSelected</t>
-  </si>
-  <si>
-    <t>Observation.category:sct.text</t>
-  </si>
-  <si>
-    <t>Observation.category.text</t>
-  </si>
-  <si>
-    <t>Plain text representation of the concept</t>
-  </si>
-  <si>
-    <t>A human language representation of the concept as seen/selected/uttered by the user who entered the data and/or which represents the intended meaning of the user.</t>
-  </si>
-  <si>
-    <t>Very often the text is the same as a displayName of one of the codings.</t>
-  </si>
-  <si>
-    <t>The codes from the terminologies do not always capture the correct meaning with all the nuances of the human using them, or sometimes there is no appropriate code at all. In these cases, the text is used to capture the full meaning of the source.</t>
-  </si>
-  <si>
-    <t>CodeableConcept.text</t>
-  </si>
-  <si>
-    <t>Observation.code</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Name
-</t>
-  </si>
-  <si>
-    <t>Kopfumfang okzipital-frontal</t>
-  </si>
-  <si>
-    <t>Describes what was observed. Sometimes this is called the observation "name".</t>
-  </si>
-  <si>
-    <t>*All* code-value and, if present, component.code-component.value pairs need to be taken into account to correctly understand the meaning of the observation.</t>
-  </si>
-  <si>
-    <t>Knowing what kind of observation is being made is essential to understanding the observation.</t>
-  </si>
-  <si>
-    <t>example</t>
-  </si>
-  <si>
-    <t>Codes identifying names of simple observations.</t>
-  </si>
-  <si>
-    <t>http://hl7.org/fhir/ValueSet/observation-codes</t>
-  </si>
-  <si>
-    <t>Observation.code.id</t>
-  </si>
-  <si>
-    <t>Observation.code.extension</t>
-  </si>
-  <si>
-    <t>Observation.code.coding</t>
-  </si>
-  <si>
-    <t>2</t>
-  </si>
-  <si>
-    <t>Observation.code.coding.id</t>
-  </si>
-  <si>
-    <t>Observation.code.coding.extension</t>
-  </si>
-  <si>
-    <t>Observation.code.coding.system</t>
-  </si>
-  <si>
-    <t>Observation.code.coding.version</t>
-  </si>
-  <si>
-    <t>Observation.code.coding.code</t>
-  </si>
-  <si>
-    <t>Observation.code.coding.display</t>
-  </si>
-  <si>
-    <t>Observation.code.coding.userSelected</t>
   </si>
   <si>
     <t>Observation.code.coding:loinc</t>
@@ -912,6 +806,11 @@
     <t>snomed</t>
   </si>
   <si>
+    <t>&lt;valueCoding xmlns="http://hl7.org/fhir"&gt;
+  &lt;system value="http://snomed.info/sct"/&gt;
+&lt;/valueCoding&gt;</t>
+  </si>
+  <si>
     <t>http://fhir.de/ValueSet/VitalSignDE-Kopfumfang-SNOMED-CT</t>
   </si>
   <si>
@@ -937,6 +836,21 @@
   </si>
   <si>
     <t>Observation.code.text</t>
+  </si>
+  <si>
+    <t>Plain text representation of the concept</t>
+  </si>
+  <si>
+    <t>A human language representation of the concept as seen/selected/uttered by the user who entered the data and/or which represents the intended meaning of the user.</t>
+  </si>
+  <si>
+    <t>Very often the text is the same as a displayName of one of the codings.</t>
+  </si>
+  <si>
+    <t>The codes from the terminologies do not always capture the correct meaning with all the nuances of the human using them, or sometimes there is no appropriate code at all. In these cases, the text is used to capture the full meaning of the source.</t>
+  </si>
+  <si>
+    <t>CodeableConcept.text</t>
   </si>
   <si>
     <t>Observation.subject</t>
@@ -1027,9 +941,6 @@
 </t>
   </si>
   <si>
-    <t>closed</t>
-  </si>
-  <si>
     <t>ele-1:All FHIR elements must have a @value or children {hasValue() or (children().count() &gt; id.count())}
 vs-de-1:If Observation.effective[x] has a value then that value shall be precise to the day {(($this is dateTime) implies ($this as dateTime).toString().length() &gt;= 10) and ($this.start.exists() implies ($this.start as dateTime).toString().length() &gt;= 10) and ($this.end.exists() implies ($this.end as dateTime).toString().length() &gt;= 10)}</t>
   </si>
@@ -1098,6 +1009,9 @@
     <t>An observation exists to have a value, though it might not if it is in error, or if it represents a group of observations.</t>
   </si>
   <si>
+    <t>closed</t>
+  </si>
+  <si>
     <t>ele-1
 obs-7</t>
   </si>
@@ -1112,13 +1026,6 @@
 </t>
   </si>
   <si>
-    <t>&lt;valueQuantity xmlns="http://hl7.org/fhir"&gt;
-  &lt;unit value="centimeter"/&gt;
-  &lt;system value="http://unitsofmeasure.org"/&gt;
-  &lt;code value="cm"/&gt;
-&lt;/valueQuantity&gt;</t>
-  </si>
-  <si>
     <t>http://fhir.de/ValueSet/VitalSignDE_Body_Length_UCUM</t>
   </si>
   <si>
@@ -1345,51 +1252,10 @@
 If the use case requires BodySite to be handled as a separate resource (e.g. to identify and track separately) then use the standard extension[ bodySite](http://hl7.org/fhir/R4/extension-bodysite.html).</t>
   </si>
   <si>
-    <t>&lt;valueCodeableConcept xmlns="http://hl7.org/fhir"&gt;
-  &lt;coding&gt;
-    &lt;system value="http://snomed.info/sct"/&gt;
-    &lt;code value="69536005"/&gt;
-  &lt;/coding&gt;
-&lt;/valueCodeableConcept&gt;</t>
-  </si>
-  <si>
     <t>Codes describing anatomical locations. May include laterality.</t>
   </si>
   <si>
     <t>http://hl7.org/fhir/ValueSet/body-site</t>
-  </si>
-  <si>
-    <t>Observation.bodySite.id</t>
-  </si>
-  <si>
-    <t>Observation.bodySite.extension</t>
-  </si>
-  <si>
-    <t>Observation.bodySite.coding</t>
-  </si>
-  <si>
-    <t>Observation.bodySite.coding.id</t>
-  </si>
-  <si>
-    <t>Observation.bodySite.coding.extension</t>
-  </si>
-  <si>
-    <t>Observation.bodySite.coding.system</t>
-  </si>
-  <si>
-    <t>Observation.bodySite.coding.version</t>
-  </si>
-  <si>
-    <t>Observation.bodySite.coding.code</t>
-  </si>
-  <si>
-    <t>Observation.bodySite.coding.display</t>
-  </si>
-  <si>
-    <t>Observation.bodySite.coding.userSelected</t>
-  </si>
-  <si>
-    <t>Observation.bodySite.text</t>
   </si>
   <si>
     <t>Observation.method</t>
@@ -1875,21 +1741,6 @@
       <alignment vertical="top" wrapText="true"/>
     </xf>
   </cellXfs>
-  <dxfs count="2">
-    <dxf>
-      <fill>
-        <patternFill patternType="solid">
-          <bgColor indexed="22"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color indexed="22"/>
-        <i val="true"/>
-      </font>
-    </dxf>
-  </dxfs>
 </styleSheet>
 </file>
 
@@ -1954,98 +1805,100 @@
       <c r="A7" t="s" s="2">
         <v>12</v>
       </c>
-      <c r="B7" s="2"/>
+      <c r="B7" t="s" s="2">
+        <v>13</v>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="s" s="2">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="B8" t="s" s="2">
-        <v>14</v>
+        <v>15</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="s" s="2">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="B9" t="s" s="2">
-        <v>16</v>
+        <v>17</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="s" s="2">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="B10" t="s" s="2">
-        <v>18</v>
+        <v>19</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="s" s="2">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="B11" t="s" s="2">
-        <v>20</v>
+        <v>21</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="s" s="2">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="B12" t="s" s="2">
-        <v>22</v>
+        <v>23</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="s" s="2">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="B13" s="2"/>
     </row>
     <row r="14">
       <c r="A14" t="s" s="2">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="B14" s="2"/>
     </row>
     <row r="15">
       <c r="A15" t="s" s="2">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="B15" t="s" s="2">
-        <v>26</v>
+        <v>27</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="s" s="2">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="B16" t="s" s="2">
-        <v>28</v>
+        <v>29</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="s" s="2">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="B17" t="s" s="2">
-        <v>30</v>
+        <v>31</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="s" s="2">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="B18" t="s" s="2">
-        <v>32</v>
+        <v>33</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="s" s="2">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="B19" t="s" s="2">
-        <v>34</v>
+        <v>13</v>
       </c>
     </row>
     <row r="20">
@@ -2063,7 +1916,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <dimension ref="A1:AK119"/>
+  <dimension ref="A1:AK96"/>
   <sheetFormatPr defaultRowHeight="15.0"/>
   <cols>
     <col min="1" max="1" width="48.07421875" customWidth="true" bestFit="true"/>
@@ -2217,12 +2070,12 @@
         <v>73</v>
       </c>
     </row>
-    <row r="2" hidden="true">
+    <row r="2">
       <c r="A2" t="s" s="2">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="B2" t="s" s="2">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="C2" s="2"/>
       <c r="D2" t="s" s="2">
@@ -2304,7 +2157,7 @@
         <v>77</v>
       </c>
       <c r="AF2" t="s" s="2">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="AG2" t="s" s="2">
         <v>75</v>
@@ -2322,7 +2175,7 @@
         <v>83</v>
       </c>
     </row>
-    <row r="3" hidden="true">
+    <row r="3">
       <c r="A3" t="s" s="2">
         <v>84</v>
       </c>
@@ -2427,7 +2280,7 @@
         <v>77</v>
       </c>
     </row>
-    <row r="4" hidden="true">
+    <row r="4">
       <c r="A4" t="s" s="2">
         <v>94</v>
       </c>
@@ -2530,7 +2383,7 @@
         <v>77</v>
       </c>
     </row>
-    <row r="5" hidden="true">
+    <row r="5">
       <c r="A5" t="s" s="2">
         <v>99</v>
       </c>
@@ -2635,7 +2488,7 @@
         <v>77</v>
       </c>
     </row>
-    <row r="6" hidden="true">
+    <row r="6">
       <c r="A6" t="s" s="2">
         <v>105</v>
       </c>
@@ -2740,7 +2593,7 @@
         <v>77</v>
       </c>
     </row>
-    <row r="7" hidden="true">
+    <row r="7">
       <c r="A7" t="s" s="2">
         <v>114</v>
       </c>
@@ -2845,7 +2698,7 @@
         <v>77</v>
       </c>
     </row>
-    <row r="8" hidden="true">
+    <row r="8">
       <c r="A8" t="s" s="2">
         <v>121</v>
       </c>
@@ -2950,7 +2803,7 @@
         <v>77</v>
       </c>
     </row>
-    <row r="9" hidden="true">
+    <row r="9">
       <c r="A9" t="s" s="2">
         <v>128</v>
       </c>
@@ -3055,7 +2908,7 @@
         <v>77</v>
       </c>
     </row>
-    <row r="10" hidden="true">
+    <row r="10">
       <c r="A10" t="s" s="2">
         <v>139</v>
       </c>
@@ -3162,7 +3015,7 @@
         <v>77</v>
       </c>
     </row>
-    <row r="11" hidden="true">
+    <row r="11">
       <c r="A11" t="s" s="2">
         <v>144</v>
       </c>
@@ -3267,7 +3120,7 @@
         <v>77</v>
       </c>
     </row>
-    <row r="12" hidden="true">
+    <row r="12">
       <c r="A12" t="s" s="2">
         <v>149</v>
       </c>
@@ -3374,7 +3227,7 @@
         <v>77</v>
       </c>
     </row>
-    <row r="13" hidden="true">
+    <row r="13">
       <c r="A13" t="s" s="2">
         <v>157</v>
       </c>
@@ -3498,7 +3351,7 @@
         <v>85</v>
       </c>
       <c r="H14" t="s" s="2">
-        <v>86</v>
+        <v>77</v>
       </c>
       <c r="I14" t="s" s="2">
         <v>86</v>
@@ -3586,7 +3439,7 @@
         <v>171</v>
       </c>
     </row>
-    <row r="15" hidden="true">
+    <row r="15">
       <c r="A15" t="s" s="2">
         <v>172</v>
       </c>
@@ -3691,7 +3544,7 @@
         <v>77</v>
       </c>
     </row>
-    <row r="16" hidden="true">
+    <row r="16">
       <c r="A16" t="s" s="2">
         <v>181</v>
       </c>
@@ -3805,44 +3658,42 @@
         <v>184</v>
       </c>
       <c r="B17" t="s" s="2">
-        <v>172</v>
-      </c>
-      <c r="C17" t="s" s="2">
+        <v>184</v>
+      </c>
+      <c r="C17" s="2"/>
+      <c r="D17" t="s" s="2">
         <v>185</v>
-      </c>
-      <c r="D17" t="s" s="2">
-        <v>77</v>
       </c>
       <c r="E17" s="2"/>
       <c r="F17" t="s" s="2">
-        <v>75</v>
+        <v>85</v>
       </c>
       <c r="G17" t="s" s="2">
         <v>85</v>
       </c>
       <c r="H17" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="I17" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="J17" t="s" s="2">
         <v>86</v>
-      </c>
-      <c r="I17" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="J17" t="s" s="2">
-        <v>77</v>
       </c>
       <c r="K17" t="s" s="2">
         <v>173</v>
       </c>
       <c r="L17" t="s" s="2">
-        <v>174</v>
+        <v>186</v>
       </c>
       <c r="M17" t="s" s="2">
-        <v>175</v>
+        <v>187</v>
       </c>
       <c r="N17" t="s" s="2">
-        <v>176</v>
+        <v>188</v>
       </c>
       <c r="O17" t="s" s="2">
-        <v>177</v>
+        <v>189</v>
       </c>
       <c r="P17" t="s" s="2">
         <v>77</v>
@@ -3852,7 +3703,7 @@
         <v>77</v>
       </c>
       <c r="S17" t="s" s="2">
-        <v>186</v>
+        <v>77</v>
       </c>
       <c r="T17" t="s" s="2">
         <v>77</v>
@@ -3867,13 +3718,13 @@
         <v>77</v>
       </c>
       <c r="X17" t="s" s="2">
-        <v>110</v>
+        <v>190</v>
       </c>
       <c r="Y17" t="s" s="2">
-        <v>178</v>
+        <v>191</v>
       </c>
       <c r="Z17" t="s" s="2">
-        <v>179</v>
+        <v>192</v>
       </c>
       <c r="AA17" t="s" s="2">
         <v>77</v>
@@ -3891,13 +3742,13 @@
         <v>77</v>
       </c>
       <c r="AF17" t="s" s="2">
-        <v>172</v>
+        <v>184</v>
       </c>
       <c r="AG17" t="s" s="2">
-        <v>75</v>
+        <v>85</v>
       </c>
       <c r="AH17" t="s" s="2">
-        <v>76</v>
+        <v>85</v>
       </c>
       <c r="AI17" t="s" s="2">
         <v>92</v>
@@ -3909,12 +3760,12 @@
         <v>77</v>
       </c>
     </row>
-    <row r="18" hidden="true">
+    <row r="18">
       <c r="A18" t="s" s="2">
-        <v>187</v>
+        <v>193</v>
       </c>
       <c r="B18" t="s" s="2">
-        <v>188</v>
+        <v>193</v>
       </c>
       <c r="C18" s="2"/>
       <c r="D18" t="s" s="2">
@@ -3937,13 +3788,13 @@
         <v>77</v>
       </c>
       <c r="K18" t="s" s="2">
-        <v>189</v>
+        <v>194</v>
       </c>
       <c r="L18" t="s" s="2">
-        <v>190</v>
+        <v>195</v>
       </c>
       <c r="M18" t="s" s="2">
-        <v>191</v>
+        <v>196</v>
       </c>
       <c r="N18" s="2"/>
       <c r="O18" s="2"/>
@@ -3994,7 +3845,7 @@
         <v>77</v>
       </c>
       <c r="AF18" t="s" s="2">
-        <v>192</v>
+        <v>197</v>
       </c>
       <c r="AG18" t="s" s="2">
         <v>75</v>
@@ -4012,12 +3863,12 @@
         <v>77</v>
       </c>
     </row>
-    <row r="19" hidden="true">
+    <row r="19">
       <c r="A19" t="s" s="2">
-        <v>193</v>
+        <v>198</v>
       </c>
       <c r="B19" t="s" s="2">
-        <v>194</v>
+        <v>198</v>
       </c>
       <c r="C19" s="2"/>
       <c r="D19" t="s" s="2">
@@ -4046,7 +3897,7 @@
         <v>131</v>
       </c>
       <c r="M19" t="s" s="2">
-        <v>195</v>
+        <v>199</v>
       </c>
       <c r="N19" t="s" s="2">
         <v>133</v>
@@ -4099,7 +3950,7 @@
         <v>136</v>
       </c>
       <c r="AF19" t="s" s="2">
-        <v>196</v>
+        <v>200</v>
       </c>
       <c r="AG19" t="s" s="2">
         <v>75</v>
@@ -4119,10 +3970,10 @@
     </row>
     <row r="20">
       <c r="A20" t="s" s="2">
-        <v>197</v>
+        <v>201</v>
       </c>
       <c r="B20" t="s" s="2">
-        <v>198</v>
+        <v>201</v>
       </c>
       <c r="C20" s="2"/>
       <c r="D20" t="s" s="2">
@@ -4130,13 +3981,13 @@
       </c>
       <c r="E20" s="2"/>
       <c r="F20" t="s" s="2">
-        <v>75</v>
+        <v>85</v>
       </c>
       <c r="G20" t="s" s="2">
         <v>76</v>
       </c>
       <c r="H20" t="s" s="2">
-        <v>86</v>
+        <v>77</v>
       </c>
       <c r="I20" t="s" s="2">
         <v>77</v>
@@ -4145,19 +3996,19 @@
         <v>86</v>
       </c>
       <c r="K20" t="s" s="2">
-        <v>199</v>
+        <v>202</v>
       </c>
       <c r="L20" t="s" s="2">
-        <v>200</v>
+        <v>203</v>
       </c>
       <c r="M20" t="s" s="2">
-        <v>201</v>
+        <v>204</v>
       </c>
       <c r="N20" t="s" s="2">
-        <v>202</v>
+        <v>205</v>
       </c>
       <c r="O20" t="s" s="2">
-        <v>203</v>
+        <v>206</v>
       </c>
       <c r="P20" t="s" s="2">
         <v>77</v>
@@ -4167,7 +4018,7 @@
         <v>77</v>
       </c>
       <c r="S20" t="s" s="2">
-        <v>204</v>
+        <v>77</v>
       </c>
       <c r="T20" t="s" s="2">
         <v>77</v>
@@ -4194,19 +4045,17 @@
         <v>77</v>
       </c>
       <c r="AB20" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="AC20" t="s" s="2">
-        <v>77</v>
-      </c>
+        <v>180</v>
+      </c>
+      <c r="AC20" s="2"/>
       <c r="AD20" t="s" s="2">
         <v>77</v>
       </c>
       <c r="AE20" t="s" s="2">
-        <v>77</v>
+        <v>136</v>
       </c>
       <c r="AF20" t="s" s="2">
-        <v>205</v>
+        <v>207</v>
       </c>
       <c r="AG20" t="s" s="2">
         <v>75</v>
@@ -4224,12 +4073,12 @@
         <v>77</v>
       </c>
     </row>
-    <row r="21" hidden="true">
+    <row r="21">
       <c r="A21" t="s" s="2">
-        <v>206</v>
+        <v>208</v>
       </c>
       <c r="B21" t="s" s="2">
-        <v>207</v>
+        <v>208</v>
       </c>
       <c r="C21" s="2"/>
       <c r="D21" t="s" s="2">
@@ -4252,13 +4101,13 @@
         <v>77</v>
       </c>
       <c r="K21" t="s" s="2">
-        <v>189</v>
+        <v>194</v>
       </c>
       <c r="L21" t="s" s="2">
-        <v>190</v>
+        <v>195</v>
       </c>
       <c r="M21" t="s" s="2">
-        <v>191</v>
+        <v>196</v>
       </c>
       <c r="N21" s="2"/>
       <c r="O21" s="2"/>
@@ -4309,7 +4158,7 @@
         <v>77</v>
       </c>
       <c r="AF21" t="s" s="2">
-        <v>192</v>
+        <v>197</v>
       </c>
       <c r="AG21" t="s" s="2">
         <v>75</v>
@@ -4327,9 +4176,9 @@
         <v>77</v>
       </c>
     </row>
-    <row r="22" hidden="true">
+    <row r="22">
       <c r="A22" t="s" s="2">
-        <v>208</v>
+        <v>209</v>
       </c>
       <c r="B22" t="s" s="2">
         <v>209</v>
@@ -4361,7 +4210,7 @@
         <v>131</v>
       </c>
       <c r="M22" t="s" s="2">
-        <v>195</v>
+        <v>199</v>
       </c>
       <c r="N22" t="s" s="2">
         <v>133</v>
@@ -4414,7 +4263,7 @@
         <v>136</v>
       </c>
       <c r="AF22" t="s" s="2">
-        <v>196</v>
+        <v>200</v>
       </c>
       <c r="AG22" t="s" s="2">
         <v>75</v>
@@ -4437,7 +4286,7 @@
         <v>210</v>
       </c>
       <c r="B23" t="s" s="2">
-        <v>211</v>
+        <v>210</v>
       </c>
       <c r="C23" s="2"/>
       <c r="D23" t="s" s="2">
@@ -4451,7 +4300,7 @@
         <v>85</v>
       </c>
       <c r="H23" t="s" s="2">
-        <v>86</v>
+        <v>77</v>
       </c>
       <c r="I23" t="s" s="2">
         <v>77</v>
@@ -4463,16 +4312,16 @@
         <v>100</v>
       </c>
       <c r="L23" t="s" s="2">
+        <v>211</v>
+      </c>
+      <c r="M23" t="s" s="2">
         <v>212</v>
       </c>
-      <c r="M23" t="s" s="2">
+      <c r="N23" t="s" s="2">
         <v>213</v>
       </c>
-      <c r="N23" t="s" s="2">
+      <c r="O23" t="s" s="2">
         <v>214</v>
-      </c>
-      <c r="O23" t="s" s="2">
-        <v>215</v>
       </c>
       <c r="P23" t="s" s="2">
         <v>77</v>
@@ -4521,7 +4370,7 @@
         <v>77</v>
       </c>
       <c r="AF23" t="s" s="2">
-        <v>216</v>
+        <v>215</v>
       </c>
       <c r="AG23" t="s" s="2">
         <v>75</v>
@@ -4539,12 +4388,12 @@
         <v>77</v>
       </c>
     </row>
-    <row r="24" hidden="true">
+    <row r="24">
       <c r="A24" t="s" s="2">
-        <v>217</v>
+        <v>216</v>
       </c>
       <c r="B24" t="s" s="2">
-        <v>218</v>
+        <v>216</v>
       </c>
       <c r="C24" s="2"/>
       <c r="D24" t="s" s="2">
@@ -4567,16 +4416,16 @@
         <v>86</v>
       </c>
       <c r="K24" t="s" s="2">
-        <v>189</v>
+        <v>194</v>
       </c>
       <c r="L24" t="s" s="2">
+        <v>217</v>
+      </c>
+      <c r="M24" t="s" s="2">
+        <v>218</v>
+      </c>
+      <c r="N24" t="s" s="2">
         <v>219</v>
-      </c>
-      <c r="M24" t="s" s="2">
-        <v>220</v>
-      </c>
-      <c r="N24" t="s" s="2">
-        <v>221</v>
       </c>
       <c r="O24" s="2"/>
       <c r="P24" t="s" s="2">
@@ -4626,7 +4475,7 @@
         <v>77</v>
       </c>
       <c r="AF24" t="s" s="2">
-        <v>222</v>
+        <v>220</v>
       </c>
       <c r="AG24" t="s" s="2">
         <v>75</v>
@@ -4646,10 +4495,10 @@
     </row>
     <row r="25">
       <c r="A25" t="s" s="2">
-        <v>223</v>
+        <v>221</v>
       </c>
       <c r="B25" t="s" s="2">
-        <v>224</v>
+        <v>221</v>
       </c>
       <c r="C25" s="2"/>
       <c r="D25" t="s" s="2">
@@ -4663,7 +4512,7 @@
         <v>85</v>
       </c>
       <c r="H25" t="s" s="2">
-        <v>86</v>
+        <v>77</v>
       </c>
       <c r="I25" t="s" s="2">
         <v>77</v>
@@ -4675,16 +4524,16 @@
         <v>106</v>
       </c>
       <c r="L25" t="s" s="2">
+        <v>222</v>
+      </c>
+      <c r="M25" t="s" s="2">
+        <v>223</v>
+      </c>
+      <c r="N25" t="s" s="2">
+        <v>224</v>
+      </c>
+      <c r="O25" t="s" s="2">
         <v>225</v>
-      </c>
-      <c r="M25" t="s" s="2">
-        <v>226</v>
-      </c>
-      <c r="N25" t="s" s="2">
-        <v>227</v>
-      </c>
-      <c r="O25" t="s" s="2">
-        <v>228</v>
       </c>
       <c r="P25" t="s" s="2">
         <v>77</v>
@@ -4733,7 +4582,7 @@
         <v>77</v>
       </c>
       <c r="AF25" t="s" s="2">
-        <v>229</v>
+        <v>226</v>
       </c>
       <c r="AG25" t="s" s="2">
         <v>75</v>
@@ -4753,10 +4602,10 @@
     </row>
     <row r="26">
       <c r="A26" t="s" s="2">
-        <v>230</v>
+        <v>227</v>
       </c>
       <c r="B26" t="s" s="2">
-        <v>231</v>
+        <v>227</v>
       </c>
       <c r="C26" s="2"/>
       <c r="D26" t="s" s="2">
@@ -4764,13 +4613,13 @@
       </c>
       <c r="E26" s="2"/>
       <c r="F26" t="s" s="2">
-        <v>85</v>
+        <v>75</v>
       </c>
       <c r="G26" t="s" s="2">
         <v>85</v>
       </c>
       <c r="H26" t="s" s="2">
-        <v>86</v>
+        <v>77</v>
       </c>
       <c r="I26" t="s" s="2">
         <v>77</v>
@@ -4779,19 +4628,19 @@
         <v>86</v>
       </c>
       <c r="K26" t="s" s="2">
-        <v>189</v>
+        <v>194</v>
       </c>
       <c r="L26" t="s" s="2">
-        <v>232</v>
+        <v>228</v>
       </c>
       <c r="M26" t="s" s="2">
-        <v>233</v>
+        <v>229</v>
       </c>
       <c r="N26" t="s" s="2">
-        <v>227</v>
+        <v>224</v>
       </c>
       <c r="O26" t="s" s="2">
-        <v>234</v>
+        <v>230</v>
       </c>
       <c r="P26" t="s" s="2">
         <v>77</v>
@@ -4840,7 +4689,7 @@
         <v>77</v>
       </c>
       <c r="AF26" t="s" s="2">
-        <v>235</v>
+        <v>231</v>
       </c>
       <c r="AG26" t="s" s="2">
         <v>75</v>
@@ -4858,12 +4707,12 @@
         <v>77</v>
       </c>
     </row>
-    <row r="27" hidden="true">
+    <row r="27">
       <c r="A27" t="s" s="2">
-        <v>236</v>
+        <v>232</v>
       </c>
       <c r="B27" t="s" s="2">
-        <v>237</v>
+        <v>232</v>
       </c>
       <c r="C27" s="2"/>
       <c r="D27" t="s" s="2">
@@ -4886,19 +4735,19 @@
         <v>86</v>
       </c>
       <c r="K27" t="s" s="2">
-        <v>238</v>
+        <v>233</v>
       </c>
       <c r="L27" t="s" s="2">
-        <v>239</v>
+        <v>234</v>
       </c>
       <c r="M27" t="s" s="2">
-        <v>240</v>
+        <v>235</v>
       </c>
       <c r="N27" t="s" s="2">
-        <v>241</v>
+        <v>236</v>
       </c>
       <c r="O27" t="s" s="2">
-        <v>242</v>
+        <v>237</v>
       </c>
       <c r="P27" t="s" s="2">
         <v>77</v>
@@ -4947,7 +4796,7 @@
         <v>77</v>
       </c>
       <c r="AF27" t="s" s="2">
-        <v>243</v>
+        <v>238</v>
       </c>
       <c r="AG27" t="s" s="2">
         <v>75</v>
@@ -4965,20 +4814,22 @@
         <v>77</v>
       </c>
     </row>
-    <row r="28" hidden="true">
+    <row r="28">
       <c r="A28" t="s" s="2">
-        <v>244</v>
+        <v>239</v>
       </c>
       <c r="B28" t="s" s="2">
-        <v>245</v>
-      </c>
-      <c r="C28" s="2"/>
+        <v>201</v>
+      </c>
+      <c r="C28" t="s" s="2">
+        <v>240</v>
+      </c>
       <c r="D28" t="s" s="2">
         <v>77</v>
       </c>
       <c r="E28" s="2"/>
       <c r="F28" t="s" s="2">
-        <v>75</v>
+        <v>85</v>
       </c>
       <c r="G28" t="s" s="2">
         <v>85</v>
@@ -4993,19 +4844,19 @@
         <v>86</v>
       </c>
       <c r="K28" t="s" s="2">
-        <v>189</v>
+        <v>202</v>
       </c>
       <c r="L28" t="s" s="2">
-        <v>246</v>
+        <v>203</v>
       </c>
       <c r="M28" t="s" s="2">
-        <v>247</v>
+        <v>204</v>
       </c>
       <c r="N28" t="s" s="2">
-        <v>248</v>
+        <v>205</v>
       </c>
       <c r="O28" t="s" s="2">
-        <v>249</v>
+        <v>206</v>
       </c>
       <c r="P28" t="s" s="2">
         <v>77</v>
@@ -5015,7 +4866,7 @@
         <v>77</v>
       </c>
       <c r="S28" t="s" s="2">
-        <v>77</v>
+        <v>241</v>
       </c>
       <c r="T28" t="s" s="2">
         <v>77</v>
@@ -5054,13 +4905,13 @@
         <v>77</v>
       </c>
       <c r="AF28" t="s" s="2">
-        <v>250</v>
+        <v>207</v>
       </c>
       <c r="AG28" t="s" s="2">
         <v>75</v>
       </c>
       <c r="AH28" t="s" s="2">
-        <v>85</v>
+        <v>76</v>
       </c>
       <c r="AI28" t="s" s="2">
         <v>92</v>
@@ -5074,46 +4925,42 @@
     </row>
     <row r="29">
       <c r="A29" t="s" s="2">
-        <v>251</v>
+        <v>242</v>
       </c>
       <c r="B29" t="s" s="2">
-        <v>251</v>
+        <v>208</v>
       </c>
       <c r="C29" s="2"/>
       <c r="D29" t="s" s="2">
-        <v>252</v>
+        <v>77</v>
       </c>
       <c r="E29" s="2"/>
       <c r="F29" t="s" s="2">
-        <v>85</v>
+        <v>75</v>
       </c>
       <c r="G29" t="s" s="2">
         <v>85</v>
       </c>
       <c r="H29" t="s" s="2">
-        <v>86</v>
+        <v>77</v>
       </c>
       <c r="I29" t="s" s="2">
         <v>77</v>
       </c>
       <c r="J29" t="s" s="2">
-        <v>86</v>
+        <v>77</v>
       </c>
       <c r="K29" t="s" s="2">
-        <v>173</v>
+        <v>194</v>
       </c>
       <c r="L29" t="s" s="2">
-        <v>253</v>
+        <v>195</v>
       </c>
       <c r="M29" t="s" s="2">
-        <v>254</v>
-      </c>
-      <c r="N29" t="s" s="2">
-        <v>255</v>
-      </c>
-      <c r="O29" t="s" s="2">
-        <v>256</v>
-      </c>
+        <v>196</v>
+      </c>
+      <c r="N29" s="2"/>
+      <c r="O29" s="2"/>
       <c r="P29" t="s" s="2">
         <v>77</v>
       </c>
@@ -5137,13 +4984,13 @@
         <v>77</v>
       </c>
       <c r="X29" t="s" s="2">
-        <v>257</v>
+        <v>77</v>
       </c>
       <c r="Y29" t="s" s="2">
-        <v>258</v>
+        <v>77</v>
       </c>
       <c r="Z29" t="s" s="2">
-        <v>259</v>
+        <v>77</v>
       </c>
       <c r="AA29" t="s" s="2">
         <v>77</v>
@@ -5161,41 +5008,41 @@
         <v>77</v>
       </c>
       <c r="AF29" t="s" s="2">
-        <v>251</v>
+        <v>197</v>
       </c>
       <c r="AG29" t="s" s="2">
-        <v>85</v>
+        <v>75</v>
       </c>
       <c r="AH29" t="s" s="2">
         <v>85</v>
       </c>
       <c r="AI29" t="s" s="2">
-        <v>92</v>
+        <v>77</v>
       </c>
       <c r="AJ29" t="s" s="2">
-        <v>93</v>
+        <v>77</v>
       </c>
       <c r="AK29" t="s" s="2">
         <v>77</v>
       </c>
     </row>
-    <row r="30" hidden="true">
+    <row r="30">
       <c r="A30" t="s" s="2">
-        <v>260</v>
+        <v>243</v>
       </c>
       <c r="B30" t="s" s="2">
-        <v>260</v>
+        <v>209</v>
       </c>
       <c r="C30" s="2"/>
       <c r="D30" t="s" s="2">
-        <v>77</v>
+        <v>129</v>
       </c>
       <c r="E30" s="2"/>
       <c r="F30" t="s" s="2">
         <v>75</v>
       </c>
       <c r="G30" t="s" s="2">
-        <v>85</v>
+        <v>76</v>
       </c>
       <c r="H30" t="s" s="2">
         <v>77</v>
@@ -5207,15 +5054,17 @@
         <v>77</v>
       </c>
       <c r="K30" t="s" s="2">
-        <v>189</v>
+        <v>130</v>
       </c>
       <c r="L30" t="s" s="2">
-        <v>190</v>
+        <v>131</v>
       </c>
       <c r="M30" t="s" s="2">
-        <v>191</v>
-      </c>
-      <c r="N30" s="2"/>
+        <v>199</v>
+      </c>
+      <c r="N30" t="s" s="2">
+        <v>133</v>
+      </c>
       <c r="O30" s="2"/>
       <c r="P30" t="s" s="2">
         <v>77</v>
@@ -5252,53 +5101,53 @@
         <v>77</v>
       </c>
       <c r="AB30" t="s" s="2">
-        <v>77</v>
+        <v>134</v>
       </c>
       <c r="AC30" t="s" s="2">
-        <v>77</v>
+        <v>135</v>
       </c>
       <c r="AD30" t="s" s="2">
         <v>77</v>
       </c>
       <c r="AE30" t="s" s="2">
-        <v>77</v>
+        <v>136</v>
       </c>
       <c r="AF30" t="s" s="2">
-        <v>192</v>
+        <v>200</v>
       </c>
       <c r="AG30" t="s" s="2">
         <v>75</v>
       </c>
       <c r="AH30" t="s" s="2">
-        <v>85</v>
+        <v>76</v>
       </c>
       <c r="AI30" t="s" s="2">
-        <v>77</v>
+        <v>92</v>
       </c>
       <c r="AJ30" t="s" s="2">
-        <v>77</v>
+        <v>138</v>
       </c>
       <c r="AK30" t="s" s="2">
         <v>77</v>
       </c>
     </row>
-    <row r="31" hidden="true">
+    <row r="31">
       <c r="A31" t="s" s="2">
-        <v>261</v>
+        <v>244</v>
       </c>
       <c r="B31" t="s" s="2">
-        <v>261</v>
+        <v>210</v>
       </c>
       <c r="C31" s="2"/>
       <c r="D31" t="s" s="2">
-        <v>129</v>
+        <v>77</v>
       </c>
       <c r="E31" s="2"/>
       <c r="F31" t="s" s="2">
-        <v>75</v>
+        <v>85</v>
       </c>
       <c r="G31" t="s" s="2">
-        <v>76</v>
+        <v>85</v>
       </c>
       <c r="H31" t="s" s="2">
         <v>77</v>
@@ -5307,21 +5156,23 @@
         <v>77</v>
       </c>
       <c r="J31" t="s" s="2">
-        <v>77</v>
+        <v>86</v>
       </c>
       <c r="K31" t="s" s="2">
-        <v>130</v>
+        <v>100</v>
       </c>
       <c r="L31" t="s" s="2">
-        <v>131</v>
+        <v>211</v>
       </c>
       <c r="M31" t="s" s="2">
-        <v>195</v>
+        <v>212</v>
       </c>
       <c r="N31" t="s" s="2">
-        <v>133</v>
-      </c>
-      <c r="O31" s="2"/>
+        <v>213</v>
+      </c>
+      <c r="O31" t="s" s="2">
+        <v>214</v>
+      </c>
       <c r="P31" t="s" s="2">
         <v>77</v>
       </c>
@@ -5357,42 +5208,42 @@
         <v>77</v>
       </c>
       <c r="AB31" t="s" s="2">
-        <v>134</v>
+        <v>77</v>
       </c>
       <c r="AC31" t="s" s="2">
-        <v>135</v>
+        <v>77</v>
       </c>
       <c r="AD31" t="s" s="2">
         <v>77</v>
       </c>
       <c r="AE31" t="s" s="2">
-        <v>136</v>
+        <v>77</v>
       </c>
       <c r="AF31" t="s" s="2">
-        <v>196</v>
+        <v>215</v>
       </c>
       <c r="AG31" t="s" s="2">
         <v>75</v>
       </c>
       <c r="AH31" t="s" s="2">
-        <v>76</v>
+        <v>85</v>
       </c>
       <c r="AI31" t="s" s="2">
         <v>92</v>
       </c>
       <c r="AJ31" t="s" s="2">
-        <v>138</v>
+        <v>93</v>
       </c>
       <c r="AK31" t="s" s="2">
         <v>77</v>
       </c>
     </row>
-    <row r="32" hidden="true">
+    <row r="32">
       <c r="A32" t="s" s="2">
-        <v>262</v>
+        <v>245</v>
       </c>
       <c r="B32" t="s" s="2">
-        <v>262</v>
+        <v>216</v>
       </c>
       <c r="C32" s="2"/>
       <c r="D32" t="s" s="2">
@@ -5400,13 +5251,13 @@
       </c>
       <c r="E32" s="2"/>
       <c r="F32" t="s" s="2">
-        <v>263</v>
+        <v>75</v>
       </c>
       <c r="G32" t="s" s="2">
-        <v>76</v>
+        <v>85</v>
       </c>
       <c r="H32" t="s" s="2">
-        <v>86</v>
+        <v>77</v>
       </c>
       <c r="I32" t="s" s="2">
         <v>77</v>
@@ -5415,20 +5266,18 @@
         <v>86</v>
       </c>
       <c r="K32" t="s" s="2">
-        <v>199</v>
+        <v>194</v>
       </c>
       <c r="L32" t="s" s="2">
-        <v>200</v>
+        <v>217</v>
       </c>
       <c r="M32" t="s" s="2">
-        <v>201</v>
+        <v>218</v>
       </c>
       <c r="N32" t="s" s="2">
-        <v>202</v>
-      </c>
-      <c r="O32" t="s" s="2">
-        <v>203</v>
-      </c>
+        <v>219</v>
+      </c>
+      <c r="O32" s="2"/>
       <c r="P32" t="s" s="2">
         <v>77</v>
       </c>
@@ -5464,23 +5313,25 @@
         <v>77</v>
       </c>
       <c r="AB32" t="s" s="2">
-        <v>180</v>
-      </c>
-      <c r="AC32" s="2"/>
+        <v>77</v>
+      </c>
+      <c r="AC32" t="s" s="2">
+        <v>77</v>
+      </c>
       <c r="AD32" t="s" s="2">
         <v>77</v>
       </c>
       <c r="AE32" t="s" s="2">
-        <v>136</v>
+        <v>77</v>
       </c>
       <c r="AF32" t="s" s="2">
-        <v>205</v>
+        <v>220</v>
       </c>
       <c r="AG32" t="s" s="2">
         <v>75</v>
       </c>
       <c r="AH32" t="s" s="2">
-        <v>76</v>
+        <v>85</v>
       </c>
       <c r="AI32" t="s" s="2">
         <v>92</v>
@@ -5492,12 +5343,12 @@
         <v>77</v>
       </c>
     </row>
-    <row r="33" hidden="true">
+    <row r="33">
       <c r="A33" t="s" s="2">
-        <v>264</v>
+        <v>246</v>
       </c>
       <c r="B33" t="s" s="2">
-        <v>264</v>
+        <v>221</v>
       </c>
       <c r="C33" s="2"/>
       <c r="D33" t="s" s="2">
@@ -5505,7 +5356,7 @@
       </c>
       <c r="E33" s="2"/>
       <c r="F33" t="s" s="2">
-        <v>75</v>
+        <v>85</v>
       </c>
       <c r="G33" t="s" s="2">
         <v>85</v>
@@ -5517,19 +5368,23 @@
         <v>77</v>
       </c>
       <c r="J33" t="s" s="2">
-        <v>77</v>
+        <v>86</v>
       </c>
       <c r="K33" t="s" s="2">
-        <v>189</v>
+        <v>106</v>
       </c>
       <c r="L33" t="s" s="2">
-        <v>190</v>
+        <v>222</v>
       </c>
       <c r="M33" t="s" s="2">
-        <v>191</v>
-      </c>
-      <c r="N33" s="2"/>
-      <c r="O33" s="2"/>
+        <v>223</v>
+      </c>
+      <c r="N33" t="s" s="2">
+        <v>224</v>
+      </c>
+      <c r="O33" t="s" s="2">
+        <v>225</v>
+      </c>
       <c r="P33" t="s" s="2">
         <v>77</v>
       </c>
@@ -5577,7 +5432,7 @@
         <v>77</v>
       </c>
       <c r="AF33" t="s" s="2">
-        <v>192</v>
+        <v>226</v>
       </c>
       <c r="AG33" t="s" s="2">
         <v>75</v>
@@ -5586,32 +5441,32 @@
         <v>85</v>
       </c>
       <c r="AI33" t="s" s="2">
-        <v>77</v>
+        <v>92</v>
       </c>
       <c r="AJ33" t="s" s="2">
-        <v>77</v>
+        <v>93</v>
       </c>
       <c r="AK33" t="s" s="2">
         <v>77</v>
       </c>
     </row>
-    <row r="34" hidden="true">
+    <row r="34">
       <c r="A34" t="s" s="2">
-        <v>265</v>
+        <v>247</v>
       </c>
       <c r="B34" t="s" s="2">
-        <v>265</v>
+        <v>227</v>
       </c>
       <c r="C34" s="2"/>
       <c r="D34" t="s" s="2">
-        <v>129</v>
+        <v>77</v>
       </c>
       <c r="E34" s="2"/>
       <c r="F34" t="s" s="2">
         <v>75</v>
       </c>
       <c r="G34" t="s" s="2">
-        <v>76</v>
+        <v>85</v>
       </c>
       <c r="H34" t="s" s="2">
         <v>77</v>
@@ -5620,21 +5475,23 @@
         <v>77</v>
       </c>
       <c r="J34" t="s" s="2">
-        <v>77</v>
+        <v>86</v>
       </c>
       <c r="K34" t="s" s="2">
-        <v>130</v>
+        <v>194</v>
       </c>
       <c r="L34" t="s" s="2">
-        <v>131</v>
+        <v>228</v>
       </c>
       <c r="M34" t="s" s="2">
-        <v>195</v>
+        <v>229</v>
       </c>
       <c r="N34" t="s" s="2">
-        <v>133</v>
-      </c>
-      <c r="O34" s="2"/>
+        <v>224</v>
+      </c>
+      <c r="O34" t="s" s="2">
+        <v>230</v>
+      </c>
       <c r="P34" t="s" s="2">
         <v>77</v>
       </c>
@@ -5670,42 +5527,42 @@
         <v>77</v>
       </c>
       <c r="AB34" t="s" s="2">
-        <v>134</v>
+        <v>77</v>
       </c>
       <c r="AC34" t="s" s="2">
-        <v>135</v>
+        <v>77</v>
       </c>
       <c r="AD34" t="s" s="2">
         <v>77</v>
       </c>
       <c r="AE34" t="s" s="2">
-        <v>136</v>
+        <v>77</v>
       </c>
       <c r="AF34" t="s" s="2">
-        <v>196</v>
+        <v>231</v>
       </c>
       <c r="AG34" t="s" s="2">
         <v>75</v>
       </c>
       <c r="AH34" t="s" s="2">
-        <v>76</v>
+        <v>85</v>
       </c>
       <c r="AI34" t="s" s="2">
         <v>92</v>
       </c>
       <c r="AJ34" t="s" s="2">
-        <v>138</v>
+        <v>93</v>
       </c>
       <c r="AK34" t="s" s="2">
         <v>77</v>
       </c>
     </row>
-    <row r="35" hidden="true">
+    <row r="35">
       <c r="A35" t="s" s="2">
-        <v>266</v>
+        <v>248</v>
       </c>
       <c r="B35" t="s" s="2">
-        <v>266</v>
+        <v>232</v>
       </c>
       <c r="C35" s="2"/>
       <c r="D35" t="s" s="2">
@@ -5713,7 +5570,7 @@
       </c>
       <c r="E35" s="2"/>
       <c r="F35" t="s" s="2">
-        <v>85</v>
+        <v>75</v>
       </c>
       <c r="G35" t="s" s="2">
         <v>85</v>
@@ -5728,19 +5585,19 @@
         <v>86</v>
       </c>
       <c r="K35" t="s" s="2">
-        <v>100</v>
+        <v>233</v>
       </c>
       <c r="L35" t="s" s="2">
-        <v>212</v>
+        <v>234</v>
       </c>
       <c r="M35" t="s" s="2">
-        <v>213</v>
+        <v>235</v>
       </c>
       <c r="N35" t="s" s="2">
-        <v>214</v>
+        <v>236</v>
       </c>
       <c r="O35" t="s" s="2">
-        <v>215</v>
+        <v>237</v>
       </c>
       <c r="P35" t="s" s="2">
         <v>77</v>
@@ -5789,7 +5646,7 @@
         <v>77</v>
       </c>
       <c r="AF35" t="s" s="2">
-        <v>216</v>
+        <v>238</v>
       </c>
       <c r="AG35" t="s" s="2">
         <v>75</v>
@@ -5807,14 +5664,16 @@
         <v>77</v>
       </c>
     </row>
-    <row r="36" hidden="true">
+    <row r="36">
       <c r="A36" t="s" s="2">
-        <v>267</v>
+        <v>249</v>
       </c>
       <c r="B36" t="s" s="2">
-        <v>267</v>
-      </c>
-      <c r="C36" s="2"/>
+        <v>201</v>
+      </c>
+      <c r="C36" t="s" s="2">
+        <v>250</v>
+      </c>
       <c r="D36" t="s" s="2">
         <v>77</v>
       </c>
@@ -5823,7 +5682,7 @@
         <v>75</v>
       </c>
       <c r="G36" t="s" s="2">
-        <v>85</v>
+        <v>76</v>
       </c>
       <c r="H36" t="s" s="2">
         <v>77</v>
@@ -5835,18 +5694,20 @@
         <v>86</v>
       </c>
       <c r="K36" t="s" s="2">
-        <v>189</v>
+        <v>202</v>
       </c>
       <c r="L36" t="s" s="2">
-        <v>219</v>
+        <v>203</v>
       </c>
       <c r="M36" t="s" s="2">
-        <v>220</v>
+        <v>204</v>
       </c>
       <c r="N36" t="s" s="2">
-        <v>221</v>
-      </c>
-      <c r="O36" s="2"/>
+        <v>205</v>
+      </c>
+      <c r="O36" t="s" s="2">
+        <v>206</v>
+      </c>
       <c r="P36" t="s" s="2">
         <v>77</v>
       </c>
@@ -5855,7 +5716,7 @@
         <v>77</v>
       </c>
       <c r="S36" t="s" s="2">
-        <v>77</v>
+        <v>251</v>
       </c>
       <c r="T36" t="s" s="2">
         <v>77</v>
@@ -5870,13 +5731,11 @@
         <v>77</v>
       </c>
       <c r="X36" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="Y36" t="s" s="2">
-        <v>77</v>
-      </c>
+        <v>168</v>
+      </c>
+      <c r="Y36" s="2"/>
       <c r="Z36" t="s" s="2">
-        <v>77</v>
+        <v>252</v>
       </c>
       <c r="AA36" t="s" s="2">
         <v>77</v>
@@ -5894,13 +5753,13 @@
         <v>77</v>
       </c>
       <c r="AF36" t="s" s="2">
-        <v>222</v>
+        <v>207</v>
       </c>
       <c r="AG36" t="s" s="2">
         <v>75</v>
       </c>
       <c r="AH36" t="s" s="2">
-        <v>85</v>
+        <v>76</v>
       </c>
       <c r="AI36" t="s" s="2">
         <v>92</v>
@@ -5912,12 +5771,12 @@
         <v>77</v>
       </c>
     </row>
-    <row r="37" hidden="true">
+    <row r="37">
       <c r="A37" t="s" s="2">
-        <v>268</v>
+        <v>253</v>
       </c>
       <c r="B37" t="s" s="2">
-        <v>268</v>
+        <v>208</v>
       </c>
       <c r="C37" s="2"/>
       <c r="D37" t="s" s="2">
@@ -5925,7 +5784,7 @@
       </c>
       <c r="E37" s="2"/>
       <c r="F37" t="s" s="2">
-        <v>85</v>
+        <v>75</v>
       </c>
       <c r="G37" t="s" s="2">
         <v>85</v>
@@ -5937,23 +5796,19 @@
         <v>77</v>
       </c>
       <c r="J37" t="s" s="2">
-        <v>86</v>
+        <v>77</v>
       </c>
       <c r="K37" t="s" s="2">
-        <v>106</v>
+        <v>194</v>
       </c>
       <c r="L37" t="s" s="2">
-        <v>225</v>
+        <v>195</v>
       </c>
       <c r="M37" t="s" s="2">
-        <v>226</v>
-      </c>
-      <c r="N37" t="s" s="2">
-        <v>227</v>
-      </c>
-      <c r="O37" t="s" s="2">
-        <v>228</v>
-      </c>
+        <v>196</v>
+      </c>
+      <c r="N37" s="2"/>
+      <c r="O37" s="2"/>
       <c r="P37" t="s" s="2">
         <v>77</v>
       </c>
@@ -6001,7 +5856,7 @@
         <v>77</v>
       </c>
       <c r="AF37" t="s" s="2">
-        <v>229</v>
+        <v>197</v>
       </c>
       <c r="AG37" t="s" s="2">
         <v>75</v>
@@ -6010,32 +5865,32 @@
         <v>85</v>
       </c>
       <c r="AI37" t="s" s="2">
-        <v>92</v>
+        <v>77</v>
       </c>
       <c r="AJ37" t="s" s="2">
-        <v>93</v>
+        <v>77</v>
       </c>
       <c r="AK37" t="s" s="2">
         <v>77</v>
       </c>
     </row>
-    <row r="38" hidden="true">
+    <row r="38">
       <c r="A38" t="s" s="2">
-        <v>269</v>
+        <v>254</v>
       </c>
       <c r="B38" t="s" s="2">
-        <v>269</v>
+        <v>209</v>
       </c>
       <c r="C38" s="2"/>
       <c r="D38" t="s" s="2">
-        <v>77</v>
+        <v>129</v>
       </c>
       <c r="E38" s="2"/>
       <c r="F38" t="s" s="2">
         <v>75</v>
       </c>
       <c r="G38" t="s" s="2">
-        <v>85</v>
+        <v>76</v>
       </c>
       <c r="H38" t="s" s="2">
         <v>77</v>
@@ -6044,23 +5899,21 @@
         <v>77</v>
       </c>
       <c r="J38" t="s" s="2">
-        <v>86</v>
+        <v>77</v>
       </c>
       <c r="K38" t="s" s="2">
-        <v>189</v>
+        <v>130</v>
       </c>
       <c r="L38" t="s" s="2">
-        <v>232</v>
+        <v>131</v>
       </c>
       <c r="M38" t="s" s="2">
-        <v>233</v>
+        <v>199</v>
       </c>
       <c r="N38" t="s" s="2">
-        <v>227</v>
-      </c>
-      <c r="O38" t="s" s="2">
-        <v>234</v>
-      </c>
+        <v>133</v>
+      </c>
+      <c r="O38" s="2"/>
       <c r="P38" t="s" s="2">
         <v>77</v>
       </c>
@@ -6096,42 +5949,42 @@
         <v>77</v>
       </c>
       <c r="AB38" t="s" s="2">
-        <v>77</v>
+        <v>134</v>
       </c>
       <c r="AC38" t="s" s="2">
-        <v>77</v>
+        <v>135</v>
       </c>
       <c r="AD38" t="s" s="2">
         <v>77</v>
       </c>
       <c r="AE38" t="s" s="2">
-        <v>77</v>
+        <v>136</v>
       </c>
       <c r="AF38" t="s" s="2">
-        <v>235</v>
+        <v>200</v>
       </c>
       <c r="AG38" t="s" s="2">
         <v>75</v>
       </c>
       <c r="AH38" t="s" s="2">
-        <v>85</v>
+        <v>76</v>
       </c>
       <c r="AI38" t="s" s="2">
         <v>92</v>
       </c>
       <c r="AJ38" t="s" s="2">
-        <v>93</v>
+        <v>138</v>
       </c>
       <c r="AK38" t="s" s="2">
         <v>77</v>
       </c>
     </row>
-    <row r="39" hidden="true">
+    <row r="39">
       <c r="A39" t="s" s="2">
-        <v>270</v>
+        <v>255</v>
       </c>
       <c r="B39" t="s" s="2">
-        <v>270</v>
+        <v>210</v>
       </c>
       <c r="C39" s="2"/>
       <c r="D39" t="s" s="2">
@@ -6139,7 +5992,7 @@
       </c>
       <c r="E39" s="2"/>
       <c r="F39" t="s" s="2">
-        <v>75</v>
+        <v>85</v>
       </c>
       <c r="G39" t="s" s="2">
         <v>85</v>
@@ -6154,19 +6007,19 @@
         <v>86</v>
       </c>
       <c r="K39" t="s" s="2">
-        <v>238</v>
+        <v>100</v>
       </c>
       <c r="L39" t="s" s="2">
-        <v>239</v>
+        <v>211</v>
       </c>
       <c r="M39" t="s" s="2">
-        <v>240</v>
+        <v>212</v>
       </c>
       <c r="N39" t="s" s="2">
-        <v>241</v>
+        <v>213</v>
       </c>
       <c r="O39" t="s" s="2">
-        <v>242</v>
+        <v>214</v>
       </c>
       <c r="P39" t="s" s="2">
         <v>77</v>
@@ -6215,7 +6068,7 @@
         <v>77</v>
       </c>
       <c r="AF39" t="s" s="2">
-        <v>243</v>
+        <v>215</v>
       </c>
       <c r="AG39" t="s" s="2">
         <v>75</v>
@@ -6233,22 +6086,20 @@
         <v>77</v>
       </c>
     </row>
-    <row r="40" hidden="true">
+    <row r="40">
       <c r="A40" t="s" s="2">
-        <v>271</v>
+        <v>256</v>
       </c>
       <c r="B40" t="s" s="2">
-        <v>262</v>
-      </c>
-      <c r="C40" t="s" s="2">
-        <v>272</v>
-      </c>
+        <v>216</v>
+      </c>
+      <c r="C40" s="2"/>
       <c r="D40" t="s" s="2">
         <v>77</v>
       </c>
       <c r="E40" s="2"/>
       <c r="F40" t="s" s="2">
-        <v>85</v>
+        <v>75</v>
       </c>
       <c r="G40" t="s" s="2">
         <v>85</v>
@@ -6263,20 +6114,18 @@
         <v>86</v>
       </c>
       <c r="K40" t="s" s="2">
-        <v>199</v>
+        <v>194</v>
       </c>
       <c r="L40" t="s" s="2">
-        <v>200</v>
+        <v>217</v>
       </c>
       <c r="M40" t="s" s="2">
-        <v>201</v>
+        <v>218</v>
       </c>
       <c r="N40" t="s" s="2">
-        <v>202</v>
-      </c>
-      <c r="O40" t="s" s="2">
-        <v>203</v>
-      </c>
+        <v>219</v>
+      </c>
+      <c r="O40" s="2"/>
       <c r="P40" t="s" s="2">
         <v>77</v>
       </c>
@@ -6285,7 +6134,7 @@
         <v>77</v>
       </c>
       <c r="S40" t="s" s="2">
-        <v>273</v>
+        <v>77</v>
       </c>
       <c r="T40" t="s" s="2">
         <v>77</v>
@@ -6324,13 +6173,13 @@
         <v>77</v>
       </c>
       <c r="AF40" t="s" s="2">
-        <v>205</v>
+        <v>220</v>
       </c>
       <c r="AG40" t="s" s="2">
         <v>75</v>
       </c>
       <c r="AH40" t="s" s="2">
-        <v>76</v>
+        <v>85</v>
       </c>
       <c r="AI40" t="s" s="2">
         <v>92</v>
@@ -6342,12 +6191,12 @@
         <v>77</v>
       </c>
     </row>
-    <row r="41" hidden="true">
+    <row r="41">
       <c r="A41" t="s" s="2">
-        <v>274</v>
+        <v>257</v>
       </c>
       <c r="B41" t="s" s="2">
-        <v>264</v>
+        <v>221</v>
       </c>
       <c r="C41" s="2"/>
       <c r="D41" t="s" s="2">
@@ -6355,7 +6204,7 @@
       </c>
       <c r="E41" s="2"/>
       <c r="F41" t="s" s="2">
-        <v>75</v>
+        <v>85</v>
       </c>
       <c r="G41" t="s" s="2">
         <v>85</v>
@@ -6367,19 +6216,23 @@
         <v>77</v>
       </c>
       <c r="J41" t="s" s="2">
-        <v>77</v>
+        <v>86</v>
       </c>
       <c r="K41" t="s" s="2">
-        <v>189</v>
+        <v>106</v>
       </c>
       <c r="L41" t="s" s="2">
-        <v>190</v>
+        <v>222</v>
       </c>
       <c r="M41" t="s" s="2">
-        <v>191</v>
-      </c>
-      <c r="N41" s="2"/>
-      <c r="O41" s="2"/>
+        <v>223</v>
+      </c>
+      <c r="N41" t="s" s="2">
+        <v>224</v>
+      </c>
+      <c r="O41" t="s" s="2">
+        <v>225</v>
+      </c>
       <c r="P41" t="s" s="2">
         <v>77</v>
       </c>
@@ -6427,7 +6280,7 @@
         <v>77</v>
       </c>
       <c r="AF41" t="s" s="2">
-        <v>192</v>
+        <v>226</v>
       </c>
       <c r="AG41" t="s" s="2">
         <v>75</v>
@@ -6436,32 +6289,32 @@
         <v>85</v>
       </c>
       <c r="AI41" t="s" s="2">
-        <v>77</v>
+        <v>92</v>
       </c>
       <c r="AJ41" t="s" s="2">
-        <v>77</v>
+        <v>93</v>
       </c>
       <c r="AK41" t="s" s="2">
         <v>77</v>
       </c>
     </row>
-    <row r="42" hidden="true">
+    <row r="42">
       <c r="A42" t="s" s="2">
-        <v>275</v>
+        <v>258</v>
       </c>
       <c r="B42" t="s" s="2">
-        <v>265</v>
+        <v>227</v>
       </c>
       <c r="C42" s="2"/>
       <c r="D42" t="s" s="2">
-        <v>129</v>
+        <v>77</v>
       </c>
       <c r="E42" s="2"/>
       <c r="F42" t="s" s="2">
         <v>75</v>
       </c>
       <c r="G42" t="s" s="2">
-        <v>76</v>
+        <v>85</v>
       </c>
       <c r="H42" t="s" s="2">
         <v>77</v>
@@ -6470,21 +6323,23 @@
         <v>77</v>
       </c>
       <c r="J42" t="s" s="2">
-        <v>77</v>
+        <v>86</v>
       </c>
       <c r="K42" t="s" s="2">
-        <v>130</v>
+        <v>194</v>
       </c>
       <c r="L42" t="s" s="2">
-        <v>131</v>
+        <v>228</v>
       </c>
       <c r="M42" t="s" s="2">
-        <v>195</v>
+        <v>229</v>
       </c>
       <c r="N42" t="s" s="2">
-        <v>133</v>
-      </c>
-      <c r="O42" s="2"/>
+        <v>224</v>
+      </c>
+      <c r="O42" t="s" s="2">
+        <v>230</v>
+      </c>
       <c r="P42" t="s" s="2">
         <v>77</v>
       </c>
@@ -6520,31 +6375,31 @@
         <v>77</v>
       </c>
       <c r="AB42" t="s" s="2">
-        <v>134</v>
+        <v>77</v>
       </c>
       <c r="AC42" t="s" s="2">
-        <v>135</v>
+        <v>77</v>
       </c>
       <c r="AD42" t="s" s="2">
         <v>77</v>
       </c>
       <c r="AE42" t="s" s="2">
-        <v>136</v>
+        <v>77</v>
       </c>
       <c r="AF42" t="s" s="2">
-        <v>196</v>
+        <v>231</v>
       </c>
       <c r="AG42" t="s" s="2">
         <v>75</v>
       </c>
       <c r="AH42" t="s" s="2">
-        <v>76</v>
+        <v>85</v>
       </c>
       <c r="AI42" t="s" s="2">
         <v>92</v>
       </c>
       <c r="AJ42" t="s" s="2">
-        <v>138</v>
+        <v>93</v>
       </c>
       <c r="AK42" t="s" s="2">
         <v>77</v>
@@ -6552,10 +6407,10 @@
     </row>
     <row r="43">
       <c r="A43" t="s" s="2">
-        <v>276</v>
+        <v>259</v>
       </c>
       <c r="B43" t="s" s="2">
-        <v>266</v>
+        <v>232</v>
       </c>
       <c r="C43" s="2"/>
       <c r="D43" t="s" s="2">
@@ -6563,13 +6418,13 @@
       </c>
       <c r="E43" s="2"/>
       <c r="F43" t="s" s="2">
-        <v>85</v>
+        <v>75</v>
       </c>
       <c r="G43" t="s" s="2">
         <v>85</v>
       </c>
       <c r="H43" t="s" s="2">
-        <v>86</v>
+        <v>77</v>
       </c>
       <c r="I43" t="s" s="2">
         <v>77</v>
@@ -6578,19 +6433,19 @@
         <v>86</v>
       </c>
       <c r="K43" t="s" s="2">
-        <v>100</v>
+        <v>233</v>
       </c>
       <c r="L43" t="s" s="2">
-        <v>212</v>
+        <v>234</v>
       </c>
       <c r="M43" t="s" s="2">
-        <v>213</v>
+        <v>235</v>
       </c>
       <c r="N43" t="s" s="2">
-        <v>214</v>
+        <v>236</v>
       </c>
       <c r="O43" t="s" s="2">
-        <v>215</v>
+        <v>237</v>
       </c>
       <c r="P43" t="s" s="2">
         <v>77</v>
@@ -6639,7 +6494,7 @@
         <v>77</v>
       </c>
       <c r="AF43" t="s" s="2">
-        <v>216</v>
+        <v>238</v>
       </c>
       <c r="AG43" t="s" s="2">
         <v>75</v>
@@ -6657,12 +6512,12 @@
         <v>77</v>
       </c>
     </row>
-    <row r="44" hidden="true">
+    <row r="44">
       <c r="A44" t="s" s="2">
-        <v>277</v>
+        <v>260</v>
       </c>
       <c r="B44" t="s" s="2">
-        <v>267</v>
+        <v>260</v>
       </c>
       <c r="C44" s="2"/>
       <c r="D44" t="s" s="2">
@@ -6685,18 +6540,20 @@
         <v>86</v>
       </c>
       <c r="K44" t="s" s="2">
-        <v>189</v>
+        <v>194</v>
       </c>
       <c r="L44" t="s" s="2">
-        <v>219</v>
+        <v>261</v>
       </c>
       <c r="M44" t="s" s="2">
-        <v>220</v>
+        <v>262</v>
       </c>
       <c r="N44" t="s" s="2">
-        <v>221</v>
-      </c>
-      <c r="O44" s="2"/>
+        <v>263</v>
+      </c>
+      <c r="O44" t="s" s="2">
+        <v>264</v>
+      </c>
       <c r="P44" t="s" s="2">
         <v>77</v>
       </c>
@@ -6744,7 +6601,7 @@
         <v>77</v>
       </c>
       <c r="AF44" t="s" s="2">
-        <v>222</v>
+        <v>265</v>
       </c>
       <c r="AG44" t="s" s="2">
         <v>75</v>
@@ -6764,10 +6621,10 @@
     </row>
     <row r="45">
       <c r="A45" t="s" s="2">
-        <v>278</v>
+        <v>266</v>
       </c>
       <c r="B45" t="s" s="2">
-        <v>268</v>
+        <v>266</v>
       </c>
       <c r="C45" s="2"/>
       <c r="D45" t="s" s="2">
@@ -6781,7 +6638,7 @@
         <v>85</v>
       </c>
       <c r="H45" t="s" s="2">
-        <v>86</v>
+        <v>77</v>
       </c>
       <c r="I45" t="s" s="2">
         <v>77</v>
@@ -6790,19 +6647,19 @@
         <v>86</v>
       </c>
       <c r="K45" t="s" s="2">
-        <v>106</v>
+        <v>267</v>
       </c>
       <c r="L45" t="s" s="2">
-        <v>225</v>
+        <v>268</v>
       </c>
       <c r="M45" t="s" s="2">
-        <v>226</v>
+        <v>269</v>
       </c>
       <c r="N45" t="s" s="2">
-        <v>227</v>
+        <v>270</v>
       </c>
       <c r="O45" t="s" s="2">
-        <v>228</v>
+        <v>271</v>
       </c>
       <c r="P45" t="s" s="2">
         <v>77</v>
@@ -6851,7 +6708,7 @@
         <v>77</v>
       </c>
       <c r="AF45" t="s" s="2">
-        <v>229</v>
+        <v>266</v>
       </c>
       <c r="AG45" t="s" s="2">
         <v>75</v>
@@ -6863,18 +6720,18 @@
         <v>92</v>
       </c>
       <c r="AJ45" t="s" s="2">
-        <v>93</v>
+        <v>156</v>
       </c>
       <c r="AK45" t="s" s="2">
-        <v>77</v>
+        <v>272</v>
       </c>
     </row>
-    <row r="46" hidden="true">
+    <row r="46">
       <c r="A46" t="s" s="2">
-        <v>279</v>
+        <v>273</v>
       </c>
       <c r="B46" t="s" s="2">
-        <v>269</v>
+        <v>273</v>
       </c>
       <c r="C46" s="2"/>
       <c r="D46" t="s" s="2">
@@ -6885,7 +6742,7 @@
         <v>75</v>
       </c>
       <c r="G46" t="s" s="2">
-        <v>85</v>
+        <v>76</v>
       </c>
       <c r="H46" t="s" s="2">
         <v>77</v>
@@ -6897,20 +6754,18 @@
         <v>86</v>
       </c>
       <c r="K46" t="s" s="2">
-        <v>189</v>
+        <v>274</v>
       </c>
       <c r="L46" t="s" s="2">
-        <v>232</v>
+        <v>275</v>
       </c>
       <c r="M46" t="s" s="2">
-        <v>233</v>
+        <v>276</v>
       </c>
       <c r="N46" t="s" s="2">
-        <v>227</v>
-      </c>
-      <c r="O46" t="s" s="2">
-        <v>234</v>
-      </c>
+        <v>277</v>
+      </c>
+      <c r="O46" s="2"/>
       <c r="P46" t="s" s="2">
         <v>77</v>
       </c>
@@ -6958,34 +6813,34 @@
         <v>77</v>
       </c>
       <c r="AF46" t="s" s="2">
-        <v>235</v>
+        <v>273</v>
       </c>
       <c r="AG46" t="s" s="2">
         <v>75</v>
       </c>
       <c r="AH46" t="s" s="2">
-        <v>85</v>
+        <v>76</v>
       </c>
       <c r="AI46" t="s" s="2">
         <v>92</v>
       </c>
       <c r="AJ46" t="s" s="2">
-        <v>93</v>
+        <v>156</v>
       </c>
       <c r="AK46" t="s" s="2">
         <v>77</v>
       </c>
     </row>
-    <row r="47" hidden="true">
+    <row r="47">
       <c r="A47" t="s" s="2">
-        <v>280</v>
+        <v>278</v>
       </c>
       <c r="B47" t="s" s="2">
-        <v>270</v>
+        <v>278</v>
       </c>
       <c r="C47" s="2"/>
       <c r="D47" t="s" s="2">
-        <v>77</v>
+        <v>279</v>
       </c>
       <c r="E47" s="2"/>
       <c r="F47" t="s" s="2">
@@ -7004,19 +6859,19 @@
         <v>86</v>
       </c>
       <c r="K47" t="s" s="2">
-        <v>238</v>
+        <v>280</v>
       </c>
       <c r="L47" t="s" s="2">
-        <v>239</v>
+        <v>281</v>
       </c>
       <c r="M47" t="s" s="2">
-        <v>240</v>
+        <v>282</v>
       </c>
       <c r="N47" t="s" s="2">
-        <v>241</v>
+        <v>283</v>
       </c>
       <c r="O47" t="s" s="2">
-        <v>242</v>
+        <v>284</v>
       </c>
       <c r="P47" t="s" s="2">
         <v>77</v>
@@ -7065,7 +6920,7 @@
         <v>77</v>
       </c>
       <c r="AF47" t="s" s="2">
-        <v>243</v>
+        <v>278</v>
       </c>
       <c r="AG47" t="s" s="2">
         <v>75</v>
@@ -7077,7 +6932,7 @@
         <v>92</v>
       </c>
       <c r="AJ47" t="s" s="2">
-        <v>93</v>
+        <v>156</v>
       </c>
       <c r="AK47" t="s" s="2">
         <v>77</v>
@@ -7085,16 +6940,14 @@
     </row>
     <row r="48">
       <c r="A48" t="s" s="2">
-        <v>281</v>
+        <v>285</v>
       </c>
       <c r="B48" t="s" s="2">
-        <v>262</v>
-      </c>
-      <c r="C48" t="s" s="2">
-        <v>282</v>
-      </c>
+        <v>285</v>
+      </c>
+      <c r="C48" s="2"/>
       <c r="D48" t="s" s="2">
-        <v>77</v>
+        <v>286</v>
       </c>
       <c r="E48" s="2"/>
       <c r="F48" t="s" s="2">
@@ -7104,7 +6957,7 @@
         <v>85</v>
       </c>
       <c r="H48" t="s" s="2">
-        <v>86</v>
+        <v>77</v>
       </c>
       <c r="I48" t="s" s="2">
         <v>77</v>
@@ -7113,19 +6966,19 @@
         <v>86</v>
       </c>
       <c r="K48" t="s" s="2">
-        <v>199</v>
+        <v>287</v>
       </c>
       <c r="L48" t="s" s="2">
-        <v>200</v>
+        <v>288</v>
       </c>
       <c r="M48" t="s" s="2">
-        <v>201</v>
+        <v>289</v>
       </c>
       <c r="N48" t="s" s="2">
-        <v>202</v>
+        <v>290</v>
       </c>
       <c r="O48" t="s" s="2">
-        <v>203</v>
+        <v>291</v>
       </c>
       <c r="P48" t="s" s="2">
         <v>77</v>
@@ -7135,7 +6988,7 @@
         <v>77</v>
       </c>
       <c r="S48" t="s" s="2">
-        <v>204</v>
+        <v>77</v>
       </c>
       <c r="T48" t="s" s="2">
         <v>77</v>
@@ -7150,56 +7003,58 @@
         <v>77</v>
       </c>
       <c r="X48" t="s" s="2">
-        <v>168</v>
-      </c>
-      <c r="Y48" s="2"/>
+        <v>77</v>
+      </c>
+      <c r="Y48" t="s" s="2">
+        <v>77</v>
+      </c>
       <c r="Z48" t="s" s="2">
-        <v>283</v>
+        <v>77</v>
       </c>
       <c r="AA48" t="s" s="2">
         <v>77</v>
       </c>
       <c r="AB48" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="AC48" t="s" s="2">
-        <v>77</v>
-      </c>
+        <v>292</v>
+      </c>
+      <c r="AC48" s="2"/>
       <c r="AD48" t="s" s="2">
         <v>77</v>
       </c>
       <c r="AE48" t="s" s="2">
-        <v>77</v>
+        <v>136</v>
       </c>
       <c r="AF48" t="s" s="2">
-        <v>205</v>
+        <v>285</v>
       </c>
       <c r="AG48" t="s" s="2">
         <v>75</v>
       </c>
       <c r="AH48" t="s" s="2">
-        <v>76</v>
+        <v>85</v>
       </c>
       <c r="AI48" t="s" s="2">
         <v>92</v>
       </c>
       <c r="AJ48" t="s" s="2">
-        <v>93</v>
+        <v>293</v>
       </c>
       <c r="AK48" t="s" s="2">
         <v>77</v>
       </c>
     </row>
-    <row r="49" hidden="true">
+    <row r="49">
       <c r="A49" t="s" s="2">
-        <v>284</v>
+        <v>294</v>
       </c>
       <c r="B49" t="s" s="2">
-        <v>264</v>
-      </c>
-      <c r="C49" s="2"/>
+        <v>285</v>
+      </c>
+      <c r="C49" t="s" s="2">
+        <v>295</v>
+      </c>
       <c r="D49" t="s" s="2">
-        <v>77</v>
+        <v>286</v>
       </c>
       <c r="E49" s="2"/>
       <c r="F49" t="s" s="2">
@@ -7215,19 +7070,23 @@
         <v>77</v>
       </c>
       <c r="J49" t="s" s="2">
-        <v>77</v>
+        <v>86</v>
       </c>
       <c r="K49" t="s" s="2">
-        <v>189</v>
+        <v>296</v>
       </c>
       <c r="L49" t="s" s="2">
-        <v>190</v>
+        <v>288</v>
       </c>
       <c r="M49" t="s" s="2">
-        <v>191</v>
-      </c>
-      <c r="N49" s="2"/>
-      <c r="O49" s="2"/>
+        <v>289</v>
+      </c>
+      <c r="N49" t="s" s="2">
+        <v>290</v>
+      </c>
+      <c r="O49" t="s" s="2">
+        <v>291</v>
+      </c>
       <c r="P49" t="s" s="2">
         <v>77</v>
       </c>
@@ -7275,7 +7134,7 @@
         <v>77</v>
       </c>
       <c r="AF49" t="s" s="2">
-        <v>192</v>
+        <v>285</v>
       </c>
       <c r="AG49" t="s" s="2">
         <v>75</v>
@@ -7284,32 +7143,32 @@
         <v>85</v>
       </c>
       <c r="AI49" t="s" s="2">
-        <v>77</v>
+        <v>92</v>
       </c>
       <c r="AJ49" t="s" s="2">
-        <v>77</v>
+        <v>293</v>
       </c>
       <c r="AK49" t="s" s="2">
-        <v>77</v>
+        <v>297</v>
       </c>
     </row>
-    <row r="50" hidden="true">
+    <row r="50">
       <c r="A50" t="s" s="2">
-        <v>285</v>
+        <v>298</v>
       </c>
       <c r="B50" t="s" s="2">
-        <v>265</v>
+        <v>298</v>
       </c>
       <c r="C50" s="2"/>
       <c r="D50" t="s" s="2">
-        <v>129</v>
+        <v>77</v>
       </c>
       <c r="E50" s="2"/>
       <c r="F50" t="s" s="2">
         <v>75</v>
       </c>
       <c r="G50" t="s" s="2">
-        <v>76</v>
+        <v>85</v>
       </c>
       <c r="H50" t="s" s="2">
         <v>77</v>
@@ -7318,19 +7177,19 @@
         <v>77</v>
       </c>
       <c r="J50" t="s" s="2">
-        <v>77</v>
+        <v>86</v>
       </c>
       <c r="K50" t="s" s="2">
-        <v>130</v>
+        <v>299</v>
       </c>
       <c r="L50" t="s" s="2">
-        <v>131</v>
+        <v>300</v>
       </c>
       <c r="M50" t="s" s="2">
-        <v>195</v>
+        <v>301</v>
       </c>
       <c r="N50" t="s" s="2">
-        <v>133</v>
+        <v>302</v>
       </c>
       <c r="O50" s="2"/>
       <c r="P50" t="s" s="2">
@@ -7368,31 +7227,31 @@
         <v>77</v>
       </c>
       <c r="AB50" t="s" s="2">
-        <v>134</v>
+        <v>77</v>
       </c>
       <c r="AC50" t="s" s="2">
-        <v>135</v>
+        <v>77</v>
       </c>
       <c r="AD50" t="s" s="2">
         <v>77</v>
       </c>
       <c r="AE50" t="s" s="2">
-        <v>136</v>
+        <v>77</v>
       </c>
       <c r="AF50" t="s" s="2">
-        <v>196</v>
+        <v>298</v>
       </c>
       <c r="AG50" t="s" s="2">
         <v>75</v>
       </c>
       <c r="AH50" t="s" s="2">
-        <v>76</v>
+        <v>85</v>
       </c>
       <c r="AI50" t="s" s="2">
         <v>92</v>
       </c>
       <c r="AJ50" t="s" s="2">
-        <v>138</v>
+        <v>93</v>
       </c>
       <c r="AK50" t="s" s="2">
         <v>77</v>
@@ -7400,10 +7259,10 @@
     </row>
     <row r="51">
       <c r="A51" t="s" s="2">
-        <v>286</v>
+        <v>303</v>
       </c>
       <c r="B51" t="s" s="2">
-        <v>266</v>
+        <v>303</v>
       </c>
       <c r="C51" s="2"/>
       <c r="D51" t="s" s="2">
@@ -7411,13 +7270,13 @@
       </c>
       <c r="E51" s="2"/>
       <c r="F51" t="s" s="2">
-        <v>85</v>
+        <v>75</v>
       </c>
       <c r="G51" t="s" s="2">
-        <v>85</v>
+        <v>76</v>
       </c>
       <c r="H51" t="s" s="2">
-        <v>86</v>
+        <v>77</v>
       </c>
       <c r="I51" t="s" s="2">
         <v>77</v>
@@ -7426,19 +7285,19 @@
         <v>86</v>
       </c>
       <c r="K51" t="s" s="2">
-        <v>100</v>
+        <v>304</v>
       </c>
       <c r="L51" t="s" s="2">
-        <v>212</v>
+        <v>305</v>
       </c>
       <c r="M51" t="s" s="2">
-        <v>213</v>
+        <v>306</v>
       </c>
       <c r="N51" t="s" s="2">
-        <v>214</v>
+        <v>154</v>
       </c>
       <c r="O51" t="s" s="2">
-        <v>215</v>
+        <v>307</v>
       </c>
       <c r="P51" t="s" s="2">
         <v>77</v>
@@ -7487,30 +7346,30 @@
         <v>77</v>
       </c>
       <c r="AF51" t="s" s="2">
-        <v>216</v>
+        <v>303</v>
       </c>
       <c r="AG51" t="s" s="2">
         <v>75</v>
       </c>
       <c r="AH51" t="s" s="2">
-        <v>85</v>
+        <v>76</v>
       </c>
       <c r="AI51" t="s" s="2">
         <v>92</v>
       </c>
       <c r="AJ51" t="s" s="2">
-        <v>93</v>
+        <v>156</v>
       </c>
       <c r="AK51" t="s" s="2">
         <v>77</v>
       </c>
     </row>
-    <row r="52" hidden="true">
+    <row r="52">
       <c r="A52" t="s" s="2">
-        <v>287</v>
+        <v>308</v>
       </c>
       <c r="B52" t="s" s="2">
-        <v>267</v>
+        <v>308</v>
       </c>
       <c r="C52" s="2"/>
       <c r="D52" t="s" s="2">
@@ -7533,18 +7392,20 @@
         <v>86</v>
       </c>
       <c r="K52" t="s" s="2">
-        <v>189</v>
+        <v>309</v>
       </c>
       <c r="L52" t="s" s="2">
-        <v>219</v>
+        <v>310</v>
       </c>
       <c r="M52" t="s" s="2">
-        <v>220</v>
+        <v>311</v>
       </c>
       <c r="N52" t="s" s="2">
-        <v>221</v>
-      </c>
-      <c r="O52" s="2"/>
+        <v>312</v>
+      </c>
+      <c r="O52" t="s" s="2">
+        <v>313</v>
+      </c>
       <c r="P52" t="s" s="2">
         <v>77</v>
       </c>
@@ -7580,19 +7441,17 @@
         <v>77</v>
       </c>
       <c r="AB52" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="AC52" t="s" s="2">
-        <v>77</v>
-      </c>
+        <v>292</v>
+      </c>
+      <c r="AC52" s="2"/>
       <c r="AD52" t="s" s="2">
         <v>77</v>
       </c>
       <c r="AE52" t="s" s="2">
-        <v>77</v>
+        <v>314</v>
       </c>
       <c r="AF52" t="s" s="2">
-        <v>222</v>
+        <v>308</v>
       </c>
       <c r="AG52" t="s" s="2">
         <v>75</v>
@@ -7601,7 +7460,7 @@
         <v>85</v>
       </c>
       <c r="AI52" t="s" s="2">
-        <v>92</v>
+        <v>315</v>
       </c>
       <c r="AJ52" t="s" s="2">
         <v>93</v>
@@ -7612,24 +7471,26 @@
     </row>
     <row r="53">
       <c r="A53" t="s" s="2">
-        <v>288</v>
+        <v>316</v>
       </c>
       <c r="B53" t="s" s="2">
-        <v>268</v>
-      </c>
-      <c r="C53" s="2"/>
+        <v>308</v>
+      </c>
+      <c r="C53" t="s" s="2">
+        <v>317</v>
+      </c>
       <c r="D53" t="s" s="2">
         <v>77</v>
       </c>
       <c r="E53" s="2"/>
       <c r="F53" t="s" s="2">
-        <v>85</v>
+        <v>75</v>
       </c>
       <c r="G53" t="s" s="2">
         <v>85</v>
       </c>
       <c r="H53" t="s" s="2">
-        <v>86</v>
+        <v>77</v>
       </c>
       <c r="I53" t="s" s="2">
         <v>77</v>
@@ -7638,19 +7499,19 @@
         <v>86</v>
       </c>
       <c r="K53" t="s" s="2">
-        <v>106</v>
+        <v>318</v>
       </c>
       <c r="L53" t="s" s="2">
-        <v>225</v>
+        <v>310</v>
       </c>
       <c r="M53" t="s" s="2">
-        <v>226</v>
+        <v>311</v>
       </c>
       <c r="N53" t="s" s="2">
-        <v>227</v>
+        <v>312</v>
       </c>
       <c r="O53" t="s" s="2">
-        <v>228</v>
+        <v>313</v>
       </c>
       <c r="P53" t="s" s="2">
         <v>77</v>
@@ -7675,13 +7536,11 @@
         <v>77</v>
       </c>
       <c r="X53" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="Y53" t="s" s="2">
-        <v>77</v>
-      </c>
+        <v>168</v>
+      </c>
+      <c r="Y53" s="2"/>
       <c r="Z53" t="s" s="2">
-        <v>77</v>
+        <v>319</v>
       </c>
       <c r="AA53" t="s" s="2">
         <v>77</v>
@@ -7699,7 +7558,7 @@
         <v>77</v>
       </c>
       <c r="AF53" t="s" s="2">
-        <v>229</v>
+        <v>308</v>
       </c>
       <c r="AG53" t="s" s="2">
         <v>75</v>
@@ -7708,7 +7567,7 @@
         <v>85</v>
       </c>
       <c r="AI53" t="s" s="2">
-        <v>92</v>
+        <v>315</v>
       </c>
       <c r="AJ53" t="s" s="2">
         <v>93</v>
@@ -7717,12 +7576,12 @@
         <v>77</v>
       </c>
     </row>
-    <row r="54" hidden="true">
+    <row r="54">
       <c r="A54" t="s" s="2">
-        <v>289</v>
+        <v>320</v>
       </c>
       <c r="B54" t="s" s="2">
-        <v>269</v>
+        <v>321</v>
       </c>
       <c r="C54" s="2"/>
       <c r="D54" t="s" s="2">
@@ -7742,23 +7601,19 @@
         <v>77</v>
       </c>
       <c r="J54" t="s" s="2">
-        <v>86</v>
+        <v>77</v>
       </c>
       <c r="K54" t="s" s="2">
-        <v>189</v>
+        <v>194</v>
       </c>
       <c r="L54" t="s" s="2">
-        <v>232</v>
+        <v>195</v>
       </c>
       <c r="M54" t="s" s="2">
-        <v>233</v>
-      </c>
-      <c r="N54" t="s" s="2">
-        <v>227</v>
-      </c>
-      <c r="O54" t="s" s="2">
-        <v>234</v>
-      </c>
+        <v>196</v>
+      </c>
+      <c r="N54" s="2"/>
+      <c r="O54" s="2"/>
       <c r="P54" t="s" s="2">
         <v>77</v>
       </c>
@@ -7806,7 +7661,7 @@
         <v>77</v>
       </c>
       <c r="AF54" t="s" s="2">
-        <v>235</v>
+        <v>197</v>
       </c>
       <c r="AG54" t="s" s="2">
         <v>75</v>
@@ -7815,32 +7670,32 @@
         <v>85</v>
       </c>
       <c r="AI54" t="s" s="2">
-        <v>92</v>
+        <v>77</v>
       </c>
       <c r="AJ54" t="s" s="2">
-        <v>93</v>
+        <v>77</v>
       </c>
       <c r="AK54" t="s" s="2">
         <v>77</v>
       </c>
     </row>
-    <row r="55" hidden="true">
+    <row r="55">
       <c r="A55" t="s" s="2">
-        <v>290</v>
+        <v>322</v>
       </c>
       <c r="B55" t="s" s="2">
-        <v>270</v>
+        <v>323</v>
       </c>
       <c r="C55" s="2"/>
       <c r="D55" t="s" s="2">
-        <v>77</v>
+        <v>129</v>
       </c>
       <c r="E55" s="2"/>
       <c r="F55" t="s" s="2">
         <v>75</v>
       </c>
       <c r="G55" t="s" s="2">
-        <v>85</v>
+        <v>76</v>
       </c>
       <c r="H55" t="s" s="2">
         <v>77</v>
@@ -7849,23 +7704,21 @@
         <v>77</v>
       </c>
       <c r="J55" t="s" s="2">
-        <v>86</v>
+        <v>77</v>
       </c>
       <c r="K55" t="s" s="2">
-        <v>238</v>
+        <v>130</v>
       </c>
       <c r="L55" t="s" s="2">
-        <v>239</v>
+        <v>131</v>
       </c>
       <c r="M55" t="s" s="2">
-        <v>240</v>
+        <v>199</v>
       </c>
       <c r="N55" t="s" s="2">
-        <v>241</v>
-      </c>
-      <c r="O55" t="s" s="2">
-        <v>242</v>
-      </c>
+        <v>133</v>
+      </c>
+      <c r="O55" s="2"/>
       <c r="P55" t="s" s="2">
         <v>77</v>
       </c>
@@ -7901,42 +7754,42 @@
         <v>77</v>
       </c>
       <c r="AB55" t="s" s="2">
-        <v>77</v>
+        <v>134</v>
       </c>
       <c r="AC55" t="s" s="2">
-        <v>77</v>
+        <v>135</v>
       </c>
       <c r="AD55" t="s" s="2">
         <v>77</v>
       </c>
       <c r="AE55" t="s" s="2">
-        <v>77</v>
+        <v>136</v>
       </c>
       <c r="AF55" t="s" s="2">
-        <v>243</v>
+        <v>200</v>
       </c>
       <c r="AG55" t="s" s="2">
         <v>75</v>
       </c>
       <c r="AH55" t="s" s="2">
-        <v>85</v>
+        <v>76</v>
       </c>
       <c r="AI55" t="s" s="2">
         <v>92</v>
       </c>
       <c r="AJ55" t="s" s="2">
-        <v>93</v>
+        <v>138</v>
       </c>
       <c r="AK55" t="s" s="2">
         <v>77</v>
       </c>
     </row>
-    <row r="56" hidden="true">
+    <row r="56">
       <c r="A56" t="s" s="2">
-        <v>291</v>
+        <v>324</v>
       </c>
       <c r="B56" t="s" s="2">
-        <v>291</v>
+        <v>325</v>
       </c>
       <c r="C56" s="2"/>
       <c r="D56" t="s" s="2">
@@ -7944,7 +7797,7 @@
       </c>
       <c r="E56" s="2"/>
       <c r="F56" t="s" s="2">
-        <v>75</v>
+        <v>85</v>
       </c>
       <c r="G56" t="s" s="2">
         <v>85</v>
@@ -7959,19 +7812,19 @@
         <v>86</v>
       </c>
       <c r="K56" t="s" s="2">
-        <v>189</v>
+        <v>326</v>
       </c>
       <c r="L56" t="s" s="2">
-        <v>246</v>
+        <v>327</v>
       </c>
       <c r="M56" t="s" s="2">
-        <v>247</v>
+        <v>328</v>
       </c>
       <c r="N56" t="s" s="2">
-        <v>248</v>
+        <v>329</v>
       </c>
       <c r="O56" t="s" s="2">
-        <v>249</v>
+        <v>330</v>
       </c>
       <c r="P56" t="s" s="2">
         <v>77</v>
@@ -8020,7 +7873,7 @@
         <v>77</v>
       </c>
       <c r="AF56" t="s" s="2">
-        <v>250</v>
+        <v>331</v>
       </c>
       <c r="AG56" t="s" s="2">
         <v>75</v>
@@ -8035,15 +7888,15 @@
         <v>93</v>
       </c>
       <c r="AK56" t="s" s="2">
-        <v>77</v>
+        <v>332</v>
       </c>
     </row>
     <row r="57">
       <c r="A57" t="s" s="2">
-        <v>292</v>
+        <v>333</v>
       </c>
       <c r="B57" t="s" s="2">
-        <v>292</v>
+        <v>334</v>
       </c>
       <c r="C57" s="2"/>
       <c r="D57" t="s" s="2">
@@ -8051,39 +7904,41 @@
       </c>
       <c r="E57" s="2"/>
       <c r="F57" t="s" s="2">
-        <v>85</v>
+        <v>75</v>
       </c>
       <c r="G57" t="s" s="2">
         <v>85</v>
       </c>
       <c r="H57" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="I57" t="s" s="2">
         <v>86</v>
-      </c>
-      <c r="I57" t="s" s="2">
-        <v>77</v>
       </c>
       <c r="J57" t="s" s="2">
         <v>86</v>
       </c>
       <c r="K57" t="s" s="2">
-        <v>293</v>
+        <v>106</v>
       </c>
       <c r="L57" t="s" s="2">
-        <v>294</v>
+        <v>335</v>
       </c>
       <c r="M57" t="s" s="2">
-        <v>295</v>
+        <v>336</v>
       </c>
       <c r="N57" t="s" s="2">
-        <v>296</v>
+        <v>224</v>
       </c>
       <c r="O57" t="s" s="2">
-        <v>297</v>
+        <v>337</v>
       </c>
       <c r="P57" t="s" s="2">
         <v>77</v>
       </c>
-      <c r="Q57" s="2"/>
+      <c r="Q57" t="s" s="2">
+        <v>338</v>
+      </c>
       <c r="R57" t="s" s="2">
         <v>77</v>
       </c>
@@ -8103,13 +7958,13 @@
         <v>77</v>
       </c>
       <c r="X57" t="s" s="2">
-        <v>77</v>
+        <v>168</v>
       </c>
       <c r="Y57" t="s" s="2">
-        <v>77</v>
+        <v>339</v>
       </c>
       <c r="Z57" t="s" s="2">
-        <v>77</v>
+        <v>340</v>
       </c>
       <c r="AA57" t="s" s="2">
         <v>77</v>
@@ -8127,7 +7982,7 @@
         <v>77</v>
       </c>
       <c r="AF57" t="s" s="2">
-        <v>292</v>
+        <v>341</v>
       </c>
       <c r="AG57" t="s" s="2">
         <v>75</v>
@@ -8139,18 +7994,18 @@
         <v>92</v>
       </c>
       <c r="AJ57" t="s" s="2">
-        <v>156</v>
+        <v>93</v>
       </c>
       <c r="AK57" t="s" s="2">
-        <v>298</v>
+        <v>77</v>
       </c>
     </row>
-    <row r="58" hidden="true">
+    <row r="58">
       <c r="A58" t="s" s="2">
-        <v>299</v>
+        <v>342</v>
       </c>
       <c r="B58" t="s" s="2">
-        <v>299</v>
+        <v>343</v>
       </c>
       <c r="C58" s="2"/>
       <c r="D58" t="s" s="2">
@@ -8158,10 +8013,10 @@
       </c>
       <c r="E58" s="2"/>
       <c r="F58" t="s" s="2">
-        <v>75</v>
+        <v>85</v>
       </c>
       <c r="G58" t="s" s="2">
-        <v>76</v>
+        <v>85</v>
       </c>
       <c r="H58" t="s" s="2">
         <v>77</v>
@@ -8173,18 +8028,20 @@
         <v>86</v>
       </c>
       <c r="K58" t="s" s="2">
-        <v>300</v>
+        <v>194</v>
       </c>
       <c r="L58" t="s" s="2">
-        <v>301</v>
+        <v>344</v>
       </c>
       <c r="M58" t="s" s="2">
-        <v>302</v>
+        <v>345</v>
       </c>
       <c r="N58" t="s" s="2">
-        <v>303</v>
-      </c>
-      <c r="O58" s="2"/>
+        <v>224</v>
+      </c>
+      <c r="O58" t="s" s="2">
+        <v>346</v>
+      </c>
       <c r="P58" t="s" s="2">
         <v>77</v>
       </c>
@@ -8232,38 +8089,38 @@
         <v>77</v>
       </c>
       <c r="AF58" t="s" s="2">
-        <v>299</v>
+        <v>347</v>
       </c>
       <c r="AG58" t="s" s="2">
         <v>75</v>
       </c>
       <c r="AH58" t="s" s="2">
-        <v>76</v>
+        <v>85</v>
       </c>
       <c r="AI58" t="s" s="2">
         <v>92</v>
       </c>
       <c r="AJ58" t="s" s="2">
-        <v>156</v>
+        <v>93</v>
       </c>
       <c r="AK58" t="s" s="2">
         <v>77</v>
       </c>
     </row>
-    <row r="59" hidden="true">
+    <row r="59">
       <c r="A59" t="s" s="2">
-        <v>304</v>
+        <v>348</v>
       </c>
       <c r="B59" t="s" s="2">
-        <v>304</v>
+        <v>349</v>
       </c>
       <c r="C59" s="2"/>
       <c r="D59" t="s" s="2">
-        <v>305</v>
+        <v>77</v>
       </c>
       <c r="E59" s="2"/>
       <c r="F59" t="s" s="2">
-        <v>75</v>
+        <v>85</v>
       </c>
       <c r="G59" t="s" s="2">
         <v>85</v>
@@ -8278,19 +8135,19 @@
         <v>86</v>
       </c>
       <c r="K59" t="s" s="2">
-        <v>306</v>
+        <v>100</v>
       </c>
       <c r="L59" t="s" s="2">
-        <v>307</v>
+        <v>350</v>
       </c>
       <c r="M59" t="s" s="2">
-        <v>308</v>
+        <v>351</v>
       </c>
       <c r="N59" t="s" s="2">
-        <v>309</v>
+        <v>352</v>
       </c>
       <c r="O59" t="s" s="2">
-        <v>310</v>
+        <v>353</v>
       </c>
       <c r="P59" t="s" s="2">
         <v>77</v>
@@ -8300,7 +8157,7 @@
         <v>77</v>
       </c>
       <c r="S59" t="s" s="2">
-        <v>77</v>
+        <v>354</v>
       </c>
       <c r="T59" t="s" s="2">
         <v>77</v>
@@ -8339,7 +8196,7 @@
         <v>77</v>
       </c>
       <c r="AF59" t="s" s="2">
-        <v>304</v>
+        <v>355</v>
       </c>
       <c r="AG59" t="s" s="2">
         <v>75</v>
@@ -8348,25 +8205,25 @@
         <v>85</v>
       </c>
       <c r="AI59" t="s" s="2">
-        <v>92</v>
+        <v>356</v>
       </c>
       <c r="AJ59" t="s" s="2">
-        <v>156</v>
+        <v>93</v>
       </c>
       <c r="AK59" t="s" s="2">
         <v>77</v>
       </c>
     </row>
-    <row r="60" hidden="true">
+    <row r="60">
       <c r="A60" t="s" s="2">
-        <v>311</v>
+        <v>357</v>
       </c>
       <c r="B60" t="s" s="2">
-        <v>311</v>
+        <v>358</v>
       </c>
       <c r="C60" s="2"/>
       <c r="D60" t="s" s="2">
-        <v>312</v>
+        <v>77</v>
       </c>
       <c r="E60" s="2"/>
       <c r="F60" t="s" s="2">
@@ -8376,7 +8233,7 @@
         <v>85</v>
       </c>
       <c r="H60" t="s" s="2">
-        <v>86</v>
+        <v>77</v>
       </c>
       <c r="I60" t="s" s="2">
         <v>77</v>
@@ -8385,19 +8242,19 @@
         <v>86</v>
       </c>
       <c r="K60" t="s" s="2">
-        <v>313</v>
+        <v>106</v>
       </c>
       <c r="L60" t="s" s="2">
-        <v>314</v>
+        <v>359</v>
       </c>
       <c r="M60" t="s" s="2">
-        <v>315</v>
+        <v>360</v>
       </c>
       <c r="N60" t="s" s="2">
-        <v>316</v>
+        <v>361</v>
       </c>
       <c r="O60" t="s" s="2">
-        <v>317</v>
+        <v>362</v>
       </c>
       <c r="P60" t="s" s="2">
         <v>77</v>
@@ -8422,29 +8279,29 @@
         <v>77</v>
       </c>
       <c r="X60" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="Y60" t="s" s="2">
-        <v>77</v>
-      </c>
+        <v>168</v>
+      </c>
+      <c r="Y60" s="2"/>
       <c r="Z60" t="s" s="2">
-        <v>77</v>
+        <v>363</v>
       </c>
       <c r="AA60" t="s" s="2">
         <v>77</v>
       </c>
       <c r="AB60" t="s" s="2">
-        <v>318</v>
-      </c>
-      <c r="AC60" s="2"/>
+        <v>77</v>
+      </c>
+      <c r="AC60" t="s" s="2">
+        <v>77</v>
+      </c>
       <c r="AD60" t="s" s="2">
         <v>77</v>
       </c>
       <c r="AE60" t="s" s="2">
-        <v>319</v>
+        <v>77</v>
       </c>
       <c r="AF60" t="s" s="2">
-        <v>311</v>
+        <v>364</v>
       </c>
       <c r="AG60" t="s" s="2">
         <v>75</v>
@@ -8456,7 +8313,7 @@
         <v>92</v>
       </c>
       <c r="AJ60" t="s" s="2">
-        <v>320</v>
+        <v>93</v>
       </c>
       <c r="AK60" t="s" s="2">
         <v>77</v>
@@ -8464,16 +8321,14 @@
     </row>
     <row r="61">
       <c r="A61" t="s" s="2">
-        <v>321</v>
+        <v>365</v>
       </c>
       <c r="B61" t="s" s="2">
-        <v>311</v>
-      </c>
-      <c r="C61" t="s" s="2">
-        <v>322</v>
-      </c>
+        <v>365</v>
+      </c>
+      <c r="C61" s="2"/>
       <c r="D61" t="s" s="2">
-        <v>312</v>
+        <v>77</v>
       </c>
       <c r="E61" s="2"/>
       <c r="F61" t="s" s="2">
@@ -8483,28 +8338,28 @@
         <v>85</v>
       </c>
       <c r="H61" t="s" s="2">
-        <v>86</v>
+        <v>77</v>
       </c>
       <c r="I61" t="s" s="2">
         <v>77</v>
       </c>
       <c r="J61" t="s" s="2">
-        <v>86</v>
+        <v>77</v>
       </c>
       <c r="K61" t="s" s="2">
-        <v>323</v>
+        <v>173</v>
       </c>
       <c r="L61" t="s" s="2">
-        <v>314</v>
+        <v>366</v>
       </c>
       <c r="M61" t="s" s="2">
-        <v>315</v>
+        <v>367</v>
       </c>
       <c r="N61" t="s" s="2">
-        <v>316</v>
+        <v>368</v>
       </c>
       <c r="O61" t="s" s="2">
-        <v>317</v>
+        <v>369</v>
       </c>
       <c r="P61" t="s" s="2">
         <v>77</v>
@@ -8529,13 +8384,13 @@
         <v>77</v>
       </c>
       <c r="X61" t="s" s="2">
-        <v>77</v>
+        <v>370</v>
       </c>
       <c r="Y61" t="s" s="2">
-        <v>77</v>
+        <v>371</v>
       </c>
       <c r="Z61" t="s" s="2">
-        <v>77</v>
+        <v>372</v>
       </c>
       <c r="AA61" t="s" s="2">
         <v>77</v>
@@ -8553,7 +8408,7 @@
         <v>77</v>
       </c>
       <c r="AF61" t="s" s="2">
-        <v>311</v>
+        <v>365</v>
       </c>
       <c r="AG61" t="s" s="2">
         <v>75</v>
@@ -8562,32 +8417,32 @@
         <v>85</v>
       </c>
       <c r="AI61" t="s" s="2">
-        <v>92</v>
+        <v>373</v>
       </c>
       <c r="AJ61" t="s" s="2">
-        <v>320</v>
+        <v>93</v>
       </c>
       <c r="AK61" t="s" s="2">
-        <v>324</v>
+        <v>77</v>
       </c>
     </row>
-    <row r="62" hidden="true">
+    <row r="62">
       <c r="A62" t="s" s="2">
-        <v>325</v>
+        <v>374</v>
       </c>
       <c r="B62" t="s" s="2">
-        <v>325</v>
+        <v>374</v>
       </c>
       <c r="C62" s="2"/>
       <c r="D62" t="s" s="2">
-        <v>77</v>
+        <v>375</v>
       </c>
       <c r="E62" s="2"/>
       <c r="F62" t="s" s="2">
         <v>75</v>
       </c>
       <c r="G62" t="s" s="2">
-        <v>85</v>
+        <v>76</v>
       </c>
       <c r="H62" t="s" s="2">
         <v>77</v>
@@ -8596,21 +8451,23 @@
         <v>77</v>
       </c>
       <c r="J62" t="s" s="2">
-        <v>86</v>
+        <v>77</v>
       </c>
       <c r="K62" t="s" s="2">
-        <v>326</v>
+        <v>173</v>
       </c>
       <c r="L62" t="s" s="2">
-        <v>327</v>
+        <v>376</v>
       </c>
       <c r="M62" t="s" s="2">
-        <v>328</v>
+        <v>377</v>
       </c>
       <c r="N62" t="s" s="2">
-        <v>329</v>
-      </c>
-      <c r="O62" s="2"/>
+        <v>378</v>
+      </c>
+      <c r="O62" t="s" s="2">
+        <v>379</v>
+      </c>
       <c r="P62" t="s" s="2">
         <v>77</v>
       </c>
@@ -8634,13 +8491,13 @@
         <v>77</v>
       </c>
       <c r="X62" t="s" s="2">
-        <v>77</v>
+        <v>370</v>
       </c>
       <c r="Y62" t="s" s="2">
-        <v>77</v>
+        <v>380</v>
       </c>
       <c r="Z62" t="s" s="2">
-        <v>77</v>
+        <v>381</v>
       </c>
       <c r="AA62" t="s" s="2">
         <v>77</v>
@@ -8658,13 +8515,13 @@
         <v>77</v>
       </c>
       <c r="AF62" t="s" s="2">
-        <v>325</v>
+        <v>374</v>
       </c>
       <c r="AG62" t="s" s="2">
         <v>75</v>
       </c>
       <c r="AH62" t="s" s="2">
-        <v>85</v>
+        <v>76</v>
       </c>
       <c r="AI62" t="s" s="2">
         <v>92</v>
@@ -8676,12 +8533,12 @@
         <v>77</v>
       </c>
     </row>
-    <row r="63" hidden="true">
+    <row r="63">
       <c r="A63" t="s" s="2">
-        <v>330</v>
+        <v>382</v>
       </c>
       <c r="B63" t="s" s="2">
-        <v>330</v>
+        <v>382</v>
       </c>
       <c r="C63" s="2"/>
       <c r="D63" t="s" s="2">
@@ -8701,22 +8558,22 @@
         <v>77</v>
       </c>
       <c r="J63" t="s" s="2">
-        <v>86</v>
+        <v>77</v>
       </c>
       <c r="K63" t="s" s="2">
-        <v>331</v>
+        <v>383</v>
       </c>
       <c r="L63" t="s" s="2">
-        <v>332</v>
+        <v>384</v>
       </c>
       <c r="M63" t="s" s="2">
-        <v>333</v>
+        <v>385</v>
       </c>
       <c r="N63" t="s" s="2">
-        <v>154</v>
+        <v>386</v>
       </c>
       <c r="O63" t="s" s="2">
-        <v>334</v>
+        <v>387</v>
       </c>
       <c r="P63" t="s" s="2">
         <v>77</v>
@@ -8765,7 +8622,7 @@
         <v>77</v>
       </c>
       <c r="AF63" t="s" s="2">
-        <v>330</v>
+        <v>382</v>
       </c>
       <c r="AG63" t="s" s="2">
         <v>75</v>
@@ -8777,18 +8634,18 @@
         <v>92</v>
       </c>
       <c r="AJ63" t="s" s="2">
-        <v>156</v>
+        <v>93</v>
       </c>
       <c r="AK63" t="s" s="2">
         <v>77</v>
       </c>
     </row>
-    <row r="64" hidden="true">
+    <row r="64">
       <c r="A64" t="s" s="2">
-        <v>335</v>
+        <v>388</v>
       </c>
       <c r="B64" t="s" s="2">
-        <v>335</v>
+        <v>388</v>
       </c>
       <c r="C64" s="2"/>
       <c r="D64" t="s" s="2">
@@ -8802,29 +8659,27 @@
         <v>85</v>
       </c>
       <c r="H64" t="s" s="2">
-        <v>86</v>
+        <v>77</v>
       </c>
       <c r="I64" t="s" s="2">
         <v>77</v>
       </c>
       <c r="J64" t="s" s="2">
-        <v>86</v>
+        <v>77</v>
       </c>
       <c r="K64" t="s" s="2">
-        <v>336</v>
+        <v>173</v>
       </c>
       <c r="L64" t="s" s="2">
-        <v>337</v>
+        <v>389</v>
       </c>
       <c r="M64" t="s" s="2">
-        <v>338</v>
+        <v>390</v>
       </c>
       <c r="N64" t="s" s="2">
-        <v>339</v>
-      </c>
-      <c r="O64" t="s" s="2">
-        <v>340</v>
-      </c>
+        <v>391</v>
+      </c>
+      <c r="O64" s="2"/>
       <c r="P64" t="s" s="2">
         <v>77</v>
       </c>
@@ -8848,29 +8703,31 @@
         <v>77</v>
       </c>
       <c r="X64" t="s" s="2">
-        <v>77</v>
+        <v>190</v>
       </c>
       <c r="Y64" t="s" s="2">
-        <v>77</v>
+        <v>392</v>
       </c>
       <c r="Z64" t="s" s="2">
-        <v>77</v>
+        <v>393</v>
       </c>
       <c r="AA64" t="s" s="2">
         <v>77</v>
       </c>
       <c r="AB64" t="s" s="2">
-        <v>318</v>
-      </c>
-      <c r="AC64" s="2"/>
+        <v>77</v>
+      </c>
+      <c r="AC64" t="s" s="2">
+        <v>77</v>
+      </c>
       <c r="AD64" t="s" s="2">
         <v>77</v>
       </c>
       <c r="AE64" t="s" s="2">
-        <v>319</v>
+        <v>77</v>
       </c>
       <c r="AF64" t="s" s="2">
-        <v>335</v>
+        <v>388</v>
       </c>
       <c r="AG64" t="s" s="2">
         <v>75</v>
@@ -8879,7 +8736,7 @@
         <v>85</v>
       </c>
       <c r="AI64" t="s" s="2">
-        <v>341</v>
+        <v>92</v>
       </c>
       <c r="AJ64" t="s" s="2">
         <v>93</v>
@@ -8890,14 +8747,12 @@
     </row>
     <row r="65">
       <c r="A65" t="s" s="2">
-        <v>342</v>
+        <v>394</v>
       </c>
       <c r="B65" t="s" s="2">
-        <v>335</v>
-      </c>
-      <c r="C65" t="s" s="2">
-        <v>343</v>
-      </c>
+        <v>394</v>
+      </c>
+      <c r="C65" s="2"/>
       <c r="D65" t="s" s="2">
         <v>77</v>
       </c>
@@ -8909,28 +8764,28 @@
         <v>85</v>
       </c>
       <c r="H65" t="s" s="2">
-        <v>86</v>
+        <v>77</v>
       </c>
       <c r="I65" t="s" s="2">
         <v>77</v>
       </c>
       <c r="J65" t="s" s="2">
-        <v>86</v>
+        <v>77</v>
       </c>
       <c r="K65" t="s" s="2">
-        <v>344</v>
+        <v>173</v>
       </c>
       <c r="L65" t="s" s="2">
-        <v>337</v>
+        <v>395</v>
       </c>
       <c r="M65" t="s" s="2">
-        <v>338</v>
+        <v>396</v>
       </c>
       <c r="N65" t="s" s="2">
-        <v>339</v>
+        <v>397</v>
       </c>
       <c r="O65" t="s" s="2">
-        <v>340</v>
+        <v>398</v>
       </c>
       <c r="P65" t="s" s="2">
         <v>77</v>
@@ -8940,7 +8795,7 @@
         <v>77</v>
       </c>
       <c r="S65" t="s" s="2">
-        <v>345</v>
+        <v>77</v>
       </c>
       <c r="T65" t="s" s="2">
         <v>77</v>
@@ -8955,11 +8810,13 @@
         <v>77</v>
       </c>
       <c r="X65" t="s" s="2">
-        <v>168</v>
-      </c>
-      <c r="Y65" s="2"/>
+        <v>190</v>
+      </c>
+      <c r="Y65" t="s" s="2">
+        <v>399</v>
+      </c>
       <c r="Z65" t="s" s="2">
-        <v>346</v>
+        <v>400</v>
       </c>
       <c r="AA65" t="s" s="2">
         <v>77</v>
@@ -8977,7 +8834,7 @@
         <v>77</v>
       </c>
       <c r="AF65" t="s" s="2">
-        <v>335</v>
+        <v>394</v>
       </c>
       <c r="AG65" t="s" s="2">
         <v>75</v>
@@ -8986,7 +8843,7 @@
         <v>85</v>
       </c>
       <c r="AI65" t="s" s="2">
-        <v>341</v>
+        <v>92</v>
       </c>
       <c r="AJ65" t="s" s="2">
         <v>93</v>
@@ -8995,12 +8852,12 @@
         <v>77</v>
       </c>
     </row>
-    <row r="66" hidden="true">
+    <row r="66">
       <c r="A66" t="s" s="2">
-        <v>347</v>
+        <v>401</v>
       </c>
       <c r="B66" t="s" s="2">
-        <v>348</v>
+        <v>401</v>
       </c>
       <c r="C66" s="2"/>
       <c r="D66" t="s" s="2">
@@ -9023,15 +8880,17 @@
         <v>77</v>
       </c>
       <c r="K66" t="s" s="2">
-        <v>189</v>
+        <v>402</v>
       </c>
       <c r="L66" t="s" s="2">
-        <v>190</v>
+        <v>403</v>
       </c>
       <c r="M66" t="s" s="2">
-        <v>191</v>
-      </c>
-      <c r="N66" s="2"/>
+        <v>404</v>
+      </c>
+      <c r="N66" t="s" s="2">
+        <v>405</v>
+      </c>
       <c r="O66" s="2"/>
       <c r="P66" t="s" s="2">
         <v>77</v>
@@ -9080,7 +8939,7 @@
         <v>77</v>
       </c>
       <c r="AF66" t="s" s="2">
-        <v>192</v>
+        <v>401</v>
       </c>
       <c r="AG66" t="s" s="2">
         <v>75</v>
@@ -9089,32 +8948,32 @@
         <v>85</v>
       </c>
       <c r="AI66" t="s" s="2">
-        <v>77</v>
+        <v>92</v>
       </c>
       <c r="AJ66" t="s" s="2">
-        <v>77</v>
+        <v>156</v>
       </c>
       <c r="AK66" t="s" s="2">
         <v>77</v>
       </c>
     </row>
-    <row r="67" hidden="true">
+    <row r="67">
       <c r="A67" t="s" s="2">
-        <v>349</v>
+        <v>406</v>
       </c>
       <c r="B67" t="s" s="2">
-        <v>350</v>
+        <v>406</v>
       </c>
       <c r="C67" s="2"/>
       <c r="D67" t="s" s="2">
-        <v>129</v>
+        <v>77</v>
       </c>
       <c r="E67" s="2"/>
       <c r="F67" t="s" s="2">
         <v>75</v>
       </c>
       <c r="G67" t="s" s="2">
-        <v>76</v>
+        <v>85</v>
       </c>
       <c r="H67" t="s" s="2">
         <v>77</v>
@@ -9126,16 +8985,16 @@
         <v>77</v>
       </c>
       <c r="K67" t="s" s="2">
-        <v>130</v>
+        <v>407</v>
       </c>
       <c r="L67" t="s" s="2">
-        <v>131</v>
+        <v>408</v>
       </c>
       <c r="M67" t="s" s="2">
-        <v>195</v>
+        <v>409</v>
       </c>
       <c r="N67" t="s" s="2">
-        <v>133</v>
+        <v>410</v>
       </c>
       <c r="O67" s="2"/>
       <c r="P67" t="s" s="2">
@@ -9173,31 +9032,31 @@
         <v>77</v>
       </c>
       <c r="AB67" t="s" s="2">
-        <v>134</v>
+        <v>77</v>
       </c>
       <c r="AC67" t="s" s="2">
-        <v>135</v>
+        <v>77</v>
       </c>
       <c r="AD67" t="s" s="2">
         <v>77</v>
       </c>
       <c r="AE67" t="s" s="2">
-        <v>136</v>
+        <v>77</v>
       </c>
       <c r="AF67" t="s" s="2">
-        <v>196</v>
+        <v>406</v>
       </c>
       <c r="AG67" t="s" s="2">
         <v>75</v>
       </c>
       <c r="AH67" t="s" s="2">
-        <v>76</v>
+        <v>85</v>
       </c>
       <c r="AI67" t="s" s="2">
         <v>92</v>
       </c>
       <c r="AJ67" t="s" s="2">
-        <v>138</v>
+        <v>156</v>
       </c>
       <c r="AK67" t="s" s="2">
         <v>77</v>
@@ -9205,10 +9064,10 @@
     </row>
     <row r="68">
       <c r="A68" t="s" s="2">
-        <v>351</v>
+        <v>411</v>
       </c>
       <c r="B68" t="s" s="2">
-        <v>352</v>
+        <v>411</v>
       </c>
       <c r="C68" s="2"/>
       <c r="D68" t="s" s="2">
@@ -9216,34 +9075,34 @@
       </c>
       <c r="E68" s="2"/>
       <c r="F68" t="s" s="2">
-        <v>85</v>
+        <v>75</v>
       </c>
       <c r="G68" t="s" s="2">
-        <v>85</v>
+        <v>76</v>
       </c>
       <c r="H68" t="s" s="2">
-        <v>86</v>
+        <v>77</v>
       </c>
       <c r="I68" t="s" s="2">
         <v>77</v>
       </c>
       <c r="J68" t="s" s="2">
-        <v>86</v>
+        <v>77</v>
       </c>
       <c r="K68" t="s" s="2">
-        <v>353</v>
+        <v>412</v>
       </c>
       <c r="L68" t="s" s="2">
-        <v>354</v>
+        <v>413</v>
       </c>
       <c r="M68" t="s" s="2">
-        <v>355</v>
+        <v>414</v>
       </c>
       <c r="N68" t="s" s="2">
-        <v>356</v>
+        <v>415</v>
       </c>
       <c r="O68" t="s" s="2">
-        <v>357</v>
+        <v>416</v>
       </c>
       <c r="P68" t="s" s="2">
         <v>77</v>
@@ -9292,30 +9151,30 @@
         <v>77</v>
       </c>
       <c r="AF68" t="s" s="2">
-        <v>358</v>
+        <v>411</v>
       </c>
       <c r="AG68" t="s" s="2">
         <v>75</v>
       </c>
       <c r="AH68" t="s" s="2">
-        <v>85</v>
+        <v>76</v>
       </c>
       <c r="AI68" t="s" s="2">
         <v>92</v>
       </c>
       <c r="AJ68" t="s" s="2">
-        <v>93</v>
+        <v>417</v>
       </c>
       <c r="AK68" t="s" s="2">
-        <v>359</v>
+        <v>77</v>
       </c>
     </row>
-    <row r="69" hidden="true">
+    <row r="69">
       <c r="A69" t="s" s="2">
-        <v>360</v>
+        <v>418</v>
       </c>
       <c r="B69" t="s" s="2">
-        <v>361</v>
+        <v>418</v>
       </c>
       <c r="C69" s="2"/>
       <c r="D69" t="s" s="2">
@@ -9332,32 +9191,26 @@
         <v>77</v>
       </c>
       <c r="I69" t="s" s="2">
-        <v>86</v>
+        <v>77</v>
       </c>
       <c r="J69" t="s" s="2">
-        <v>86</v>
+        <v>77</v>
       </c>
       <c r="K69" t="s" s="2">
-        <v>106</v>
+        <v>194</v>
       </c>
       <c r="L69" t="s" s="2">
-        <v>362</v>
+        <v>195</v>
       </c>
       <c r="M69" t="s" s="2">
-        <v>363</v>
-      </c>
-      <c r="N69" t="s" s="2">
-        <v>227</v>
-      </c>
-      <c r="O69" t="s" s="2">
-        <v>364</v>
-      </c>
+        <v>196</v>
+      </c>
+      <c r="N69" s="2"/>
+      <c r="O69" s="2"/>
       <c r="P69" t="s" s="2">
         <v>77</v>
       </c>
-      <c r="Q69" t="s" s="2">
-        <v>365</v>
-      </c>
+      <c r="Q69" s="2"/>
       <c r="R69" t="s" s="2">
         <v>77</v>
       </c>
@@ -9377,13 +9230,13 @@
         <v>77</v>
       </c>
       <c r="X69" t="s" s="2">
-        <v>168</v>
+        <v>77</v>
       </c>
       <c r="Y69" t="s" s="2">
-        <v>366</v>
+        <v>77</v>
       </c>
       <c r="Z69" t="s" s="2">
-        <v>367</v>
+        <v>77</v>
       </c>
       <c r="AA69" t="s" s="2">
         <v>77</v>
@@ -9401,7 +9254,7 @@
         <v>77</v>
       </c>
       <c r="AF69" t="s" s="2">
-        <v>368</v>
+        <v>197</v>
       </c>
       <c r="AG69" t="s" s="2">
         <v>75</v>
@@ -9410,10 +9263,10 @@
         <v>85</v>
       </c>
       <c r="AI69" t="s" s="2">
-        <v>92</v>
+        <v>77</v>
       </c>
       <c r="AJ69" t="s" s="2">
-        <v>93</v>
+        <v>77</v>
       </c>
       <c r="AK69" t="s" s="2">
         <v>77</v>
@@ -9421,46 +9274,44 @@
     </row>
     <row r="70">
       <c r="A70" t="s" s="2">
-        <v>369</v>
+        <v>419</v>
       </c>
       <c r="B70" t="s" s="2">
-        <v>370</v>
+        <v>419</v>
       </c>
       <c r="C70" s="2"/>
       <c r="D70" t="s" s="2">
-        <v>77</v>
+        <v>129</v>
       </c>
       <c r="E70" s="2"/>
       <c r="F70" t="s" s="2">
-        <v>85</v>
+        <v>75</v>
       </c>
       <c r="G70" t="s" s="2">
-        <v>85</v>
+        <v>76</v>
       </c>
       <c r="H70" t="s" s="2">
-        <v>86</v>
+        <v>77</v>
       </c>
       <c r="I70" t="s" s="2">
         <v>77</v>
       </c>
       <c r="J70" t="s" s="2">
-        <v>86</v>
+        <v>77</v>
       </c>
       <c r="K70" t="s" s="2">
-        <v>189</v>
+        <v>130</v>
       </c>
       <c r="L70" t="s" s="2">
-        <v>371</v>
+        <v>131</v>
       </c>
       <c r="M70" t="s" s="2">
-        <v>372</v>
+        <v>199</v>
       </c>
       <c r="N70" t="s" s="2">
-        <v>227</v>
-      </c>
-      <c r="O70" t="s" s="2">
-        <v>373</v>
-      </c>
+        <v>133</v>
+      </c>
+      <c r="O70" s="2"/>
       <c r="P70" t="s" s="2">
         <v>77</v>
       </c>
@@ -9496,31 +9347,31 @@
         <v>77</v>
       </c>
       <c r="AB70" t="s" s="2">
-        <v>77</v>
+        <v>134</v>
       </c>
       <c r="AC70" t="s" s="2">
-        <v>77</v>
+        <v>135</v>
       </c>
       <c r="AD70" t="s" s="2">
         <v>77</v>
       </c>
       <c r="AE70" t="s" s="2">
-        <v>77</v>
+        <v>136</v>
       </c>
       <c r="AF70" t="s" s="2">
-        <v>374</v>
+        <v>200</v>
       </c>
       <c r="AG70" t="s" s="2">
         <v>75</v>
       </c>
       <c r="AH70" t="s" s="2">
-        <v>85</v>
+        <v>76</v>
       </c>
       <c r="AI70" t="s" s="2">
         <v>92</v>
       </c>
       <c r="AJ70" t="s" s="2">
-        <v>93</v>
+        <v>138</v>
       </c>
       <c r="AK70" t="s" s="2">
         <v>77</v>
@@ -9528,45 +9379,45 @@
     </row>
     <row r="71">
       <c r="A71" t="s" s="2">
-        <v>375</v>
+        <v>420</v>
       </c>
       <c r="B71" t="s" s="2">
-        <v>376</v>
+        <v>420</v>
       </c>
       <c r="C71" s="2"/>
       <c r="D71" t="s" s="2">
-        <v>77</v>
+        <v>421</v>
       </c>
       <c r="E71" s="2"/>
       <c r="F71" t="s" s="2">
-        <v>85</v>
+        <v>75</v>
       </c>
       <c r="G71" t="s" s="2">
-        <v>85</v>
+        <v>76</v>
       </c>
       <c r="H71" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="I71" t="s" s="2">
         <v>86</v>
-      </c>
-      <c r="I71" t="s" s="2">
-        <v>77</v>
       </c>
       <c r="J71" t="s" s="2">
         <v>86</v>
       </c>
       <c r="K71" t="s" s="2">
-        <v>100</v>
+        <v>130</v>
       </c>
       <c r="L71" t="s" s="2">
-        <v>377</v>
+        <v>422</v>
       </c>
       <c r="M71" t="s" s="2">
-        <v>378</v>
+        <v>423</v>
       </c>
       <c r="N71" t="s" s="2">
-        <v>379</v>
+        <v>133</v>
       </c>
       <c r="O71" t="s" s="2">
-        <v>380</v>
+        <v>142</v>
       </c>
       <c r="P71" t="s" s="2">
         <v>77</v>
@@ -9576,7 +9427,7 @@
         <v>77</v>
       </c>
       <c r="S71" t="s" s="2">
-        <v>381</v>
+        <v>77</v>
       </c>
       <c r="T71" t="s" s="2">
         <v>77</v>
@@ -9615,19 +9466,19 @@
         <v>77</v>
       </c>
       <c r="AF71" t="s" s="2">
-        <v>382</v>
+        <v>424</v>
       </c>
       <c r="AG71" t="s" s="2">
         <v>75</v>
       </c>
       <c r="AH71" t="s" s="2">
-        <v>85</v>
+        <v>76</v>
       </c>
       <c r="AI71" t="s" s="2">
-        <v>383</v>
+        <v>92</v>
       </c>
       <c r="AJ71" t="s" s="2">
-        <v>93</v>
+        <v>138</v>
       </c>
       <c r="AK71" t="s" s="2">
         <v>77</v>
@@ -9635,10 +9486,10 @@
     </row>
     <row r="72">
       <c r="A72" t="s" s="2">
-        <v>384</v>
+        <v>425</v>
       </c>
       <c r="B72" t="s" s="2">
-        <v>385</v>
+        <v>425</v>
       </c>
       <c r="C72" s="2"/>
       <c r="D72" t="s" s="2">
@@ -9646,35 +9497,33 @@
       </c>
       <c r="E72" s="2"/>
       <c r="F72" t="s" s="2">
-        <v>85</v>
+        <v>75</v>
       </c>
       <c r="G72" t="s" s="2">
         <v>85</v>
       </c>
       <c r="H72" t="s" s="2">
-        <v>86</v>
+        <v>77</v>
       </c>
       <c r="I72" t="s" s="2">
         <v>77</v>
       </c>
       <c r="J72" t="s" s="2">
-        <v>86</v>
+        <v>77</v>
       </c>
       <c r="K72" t="s" s="2">
-        <v>106</v>
+        <v>426</v>
       </c>
       <c r="L72" t="s" s="2">
-        <v>386</v>
+        <v>427</v>
       </c>
       <c r="M72" t="s" s="2">
-        <v>387</v>
+        <v>428</v>
       </c>
       <c r="N72" t="s" s="2">
-        <v>388</v>
-      </c>
-      <c r="O72" t="s" s="2">
-        <v>389</v>
-      </c>
+        <v>429</v>
+      </c>
+      <c r="O72" s="2"/>
       <c r="P72" t="s" s="2">
         <v>77</v>
       </c>
@@ -9698,11 +9547,13 @@
         <v>77</v>
       </c>
       <c r="X72" t="s" s="2">
-        <v>168</v>
-      </c>
-      <c r="Y72" s="2"/>
+        <v>77</v>
+      </c>
+      <c r="Y72" t="s" s="2">
+        <v>77</v>
+      </c>
       <c r="Z72" t="s" s="2">
-        <v>390</v>
+        <v>77</v>
       </c>
       <c r="AA72" t="s" s="2">
         <v>77</v>
@@ -9720,7 +9571,7 @@
         <v>77</v>
       </c>
       <c r="AF72" t="s" s="2">
-        <v>391</v>
+        <v>425</v>
       </c>
       <c r="AG72" t="s" s="2">
         <v>75</v>
@@ -9729,10 +9580,10 @@
         <v>85</v>
       </c>
       <c r="AI72" t="s" s="2">
-        <v>92</v>
+        <v>430</v>
       </c>
       <c r="AJ72" t="s" s="2">
-        <v>93</v>
+        <v>431</v>
       </c>
       <c r="AK72" t="s" s="2">
         <v>77</v>
@@ -9740,10 +9591,10 @@
     </row>
     <row r="73">
       <c r="A73" t="s" s="2">
-        <v>392</v>
+        <v>432</v>
       </c>
       <c r="B73" t="s" s="2">
-        <v>392</v>
+        <v>432</v>
       </c>
       <c r="C73" s="2"/>
       <c r="D73" t="s" s="2">
@@ -9757,7 +9608,7 @@
         <v>85</v>
       </c>
       <c r="H73" t="s" s="2">
-        <v>86</v>
+        <v>77</v>
       </c>
       <c r="I73" t="s" s="2">
         <v>77</v>
@@ -9766,20 +9617,18 @@
         <v>77</v>
       </c>
       <c r="K73" t="s" s="2">
-        <v>173</v>
+        <v>426</v>
       </c>
       <c r="L73" t="s" s="2">
-        <v>393</v>
+        <v>433</v>
       </c>
       <c r="M73" t="s" s="2">
-        <v>394</v>
+        <v>434</v>
       </c>
       <c r="N73" t="s" s="2">
-        <v>395</v>
-      </c>
-      <c r="O73" t="s" s="2">
-        <v>396</v>
-      </c>
+        <v>429</v>
+      </c>
+      <c r="O73" s="2"/>
       <c r="P73" t="s" s="2">
         <v>77</v>
       </c>
@@ -9803,13 +9652,13 @@
         <v>77</v>
       </c>
       <c r="X73" t="s" s="2">
-        <v>397</v>
+        <v>77</v>
       </c>
       <c r="Y73" t="s" s="2">
-        <v>398</v>
+        <v>77</v>
       </c>
       <c r="Z73" t="s" s="2">
-        <v>399</v>
+        <v>77</v>
       </c>
       <c r="AA73" t="s" s="2">
         <v>77</v>
@@ -9827,7 +9676,7 @@
         <v>77</v>
       </c>
       <c r="AF73" t="s" s="2">
-        <v>392</v>
+        <v>432</v>
       </c>
       <c r="AG73" t="s" s="2">
         <v>75</v>
@@ -9836,32 +9685,32 @@
         <v>85</v>
       </c>
       <c r="AI73" t="s" s="2">
-        <v>400</v>
+        <v>430</v>
       </c>
       <c r="AJ73" t="s" s="2">
-        <v>93</v>
+        <v>431</v>
       </c>
       <c r="AK73" t="s" s="2">
         <v>77</v>
       </c>
     </row>
-    <row r="74" hidden="true">
+    <row r="74">
       <c r="A74" t="s" s="2">
-        <v>401</v>
+        <v>435</v>
       </c>
       <c r="B74" t="s" s="2">
-        <v>401</v>
+        <v>435</v>
       </c>
       <c r="C74" s="2"/>
       <c r="D74" t="s" s="2">
-        <v>402</v>
+        <v>77</v>
       </c>
       <c r="E74" s="2"/>
       <c r="F74" t="s" s="2">
         <v>75</v>
       </c>
       <c r="G74" t="s" s="2">
-        <v>76</v>
+        <v>85</v>
       </c>
       <c r="H74" t="s" s="2">
         <v>77</v>
@@ -9876,16 +9725,16 @@
         <v>173</v>
       </c>
       <c r="L74" t="s" s="2">
-        <v>403</v>
+        <v>436</v>
       </c>
       <c r="M74" t="s" s="2">
-        <v>404</v>
+        <v>437</v>
       </c>
       <c r="N74" t="s" s="2">
-        <v>405</v>
+        <v>438</v>
       </c>
       <c r="O74" t="s" s="2">
-        <v>406</v>
+        <v>439</v>
       </c>
       <c r="P74" t="s" s="2">
         <v>77</v>
@@ -9910,13 +9759,13 @@
         <v>77</v>
       </c>
       <c r="X74" t="s" s="2">
-        <v>397</v>
+        <v>110</v>
       </c>
       <c r="Y74" t="s" s="2">
-        <v>407</v>
+        <v>440</v>
       </c>
       <c r="Z74" t="s" s="2">
-        <v>408</v>
+        <v>441</v>
       </c>
       <c r="AA74" t="s" s="2">
         <v>77</v>
@@ -9934,13 +9783,13 @@
         <v>77</v>
       </c>
       <c r="AF74" t="s" s="2">
-        <v>401</v>
+        <v>435</v>
       </c>
       <c r="AG74" t="s" s="2">
         <v>75</v>
       </c>
       <c r="AH74" t="s" s="2">
-        <v>76</v>
+        <v>85</v>
       </c>
       <c r="AI74" t="s" s="2">
         <v>92</v>
@@ -9952,12 +9801,12 @@
         <v>77</v>
       </c>
     </row>
-    <row r="75" hidden="true">
+    <row r="75">
       <c r="A75" t="s" s="2">
-        <v>409</v>
+        <v>442</v>
       </c>
       <c r="B75" t="s" s="2">
-        <v>409</v>
+        <v>442</v>
       </c>
       <c r="C75" s="2"/>
       <c r="D75" t="s" s="2">
@@ -9980,19 +9829,19 @@
         <v>77</v>
       </c>
       <c r="K75" t="s" s="2">
-        <v>410</v>
+        <v>173</v>
       </c>
       <c r="L75" t="s" s="2">
-        <v>411</v>
+        <v>443</v>
       </c>
       <c r="M75" t="s" s="2">
-        <v>412</v>
+        <v>444</v>
       </c>
       <c r="N75" t="s" s="2">
-        <v>413</v>
+        <v>445</v>
       </c>
       <c r="O75" t="s" s="2">
-        <v>414</v>
+        <v>446</v>
       </c>
       <c r="P75" t="s" s="2">
         <v>77</v>
@@ -10017,13 +9866,13 @@
         <v>77</v>
       </c>
       <c r="X75" t="s" s="2">
-        <v>77</v>
+        <v>190</v>
       </c>
       <c r="Y75" t="s" s="2">
-        <v>77</v>
+        <v>447</v>
       </c>
       <c r="Z75" t="s" s="2">
-        <v>77</v>
+        <v>448</v>
       </c>
       <c r="AA75" t="s" s="2">
         <v>77</v>
@@ -10041,7 +9890,7 @@
         <v>77</v>
       </c>
       <c r="AF75" t="s" s="2">
-        <v>409</v>
+        <v>442</v>
       </c>
       <c r="AG75" t="s" s="2">
         <v>75</v>
@@ -10061,10 +9910,10 @@
     </row>
     <row r="76">
       <c r="A76" t="s" s="2">
-        <v>415</v>
+        <v>449</v>
       </c>
       <c r="B76" t="s" s="2">
-        <v>415</v>
+        <v>449</v>
       </c>
       <c r="C76" s="2"/>
       <c r="D76" t="s" s="2">
@@ -10078,7 +9927,7 @@
         <v>85</v>
       </c>
       <c r="H76" t="s" s="2">
-        <v>86</v>
+        <v>77</v>
       </c>
       <c r="I76" t="s" s="2">
         <v>77</v>
@@ -10087,18 +9936,20 @@
         <v>77</v>
       </c>
       <c r="K76" t="s" s="2">
-        <v>173</v>
+        <v>450</v>
       </c>
       <c r="L76" t="s" s="2">
-        <v>416</v>
+        <v>451</v>
       </c>
       <c r="M76" t="s" s="2">
-        <v>417</v>
+        <v>452</v>
       </c>
       <c r="N76" t="s" s="2">
-        <v>418</v>
-      </c>
-      <c r="O76" s="2"/>
+        <v>453</v>
+      </c>
+      <c r="O76" t="s" s="2">
+        <v>454</v>
+      </c>
       <c r="P76" t="s" s="2">
         <v>77</v>
       </c>
@@ -10107,7 +9958,7 @@
         <v>77</v>
       </c>
       <c r="S76" t="s" s="2">
-        <v>419</v>
+        <v>77</v>
       </c>
       <c r="T76" t="s" s="2">
         <v>77</v>
@@ -10122,13 +9973,13 @@
         <v>77</v>
       </c>
       <c r="X76" t="s" s="2">
-        <v>257</v>
+        <v>77</v>
       </c>
       <c r="Y76" t="s" s="2">
-        <v>420</v>
+        <v>77</v>
       </c>
       <c r="Z76" t="s" s="2">
-        <v>421</v>
+        <v>77</v>
       </c>
       <c r="AA76" t="s" s="2">
         <v>77</v>
@@ -10146,7 +9997,7 @@
         <v>77</v>
       </c>
       <c r="AF76" t="s" s="2">
-        <v>415</v>
+        <v>449</v>
       </c>
       <c r="AG76" t="s" s="2">
         <v>75</v>
@@ -10158,18 +10009,18 @@
         <v>92</v>
       </c>
       <c r="AJ76" t="s" s="2">
-        <v>93</v>
+        <v>455</v>
       </c>
       <c r="AK76" t="s" s="2">
         <v>77</v>
       </c>
     </row>
-    <row r="77" hidden="true">
+    <row r="77">
       <c r="A77" t="s" s="2">
-        <v>422</v>
+        <v>456</v>
       </c>
       <c r="B77" t="s" s="2">
-        <v>422</v>
+        <v>456</v>
       </c>
       <c r="C77" s="2"/>
       <c r="D77" t="s" s="2">
@@ -10192,15 +10043,17 @@
         <v>77</v>
       </c>
       <c r="K77" t="s" s="2">
-        <v>189</v>
+        <v>194</v>
       </c>
       <c r="L77" t="s" s="2">
-        <v>190</v>
+        <v>457</v>
       </c>
       <c r="M77" t="s" s="2">
-        <v>191</v>
-      </c>
-      <c r="N77" s="2"/>
+        <v>458</v>
+      </c>
+      <c r="N77" t="s" s="2">
+        <v>224</v>
+      </c>
       <c r="O77" s="2"/>
       <c r="P77" t="s" s="2">
         <v>77</v>
@@ -10249,7 +10102,7 @@
         <v>77</v>
       </c>
       <c r="AF77" t="s" s="2">
-        <v>192</v>
+        <v>456</v>
       </c>
       <c r="AG77" t="s" s="2">
         <v>75</v>
@@ -10258,25 +10111,25 @@
         <v>85</v>
       </c>
       <c r="AI77" t="s" s="2">
-        <v>77</v>
+        <v>92</v>
       </c>
       <c r="AJ77" t="s" s="2">
-        <v>77</v>
+        <v>93</v>
       </c>
       <c r="AK77" t="s" s="2">
         <v>77</v>
       </c>
     </row>
-    <row r="78" hidden="true">
+    <row r="78">
       <c r="A78" t="s" s="2">
-        <v>423</v>
+        <v>459</v>
       </c>
       <c r="B78" t="s" s="2">
-        <v>423</v>
+        <v>459</v>
       </c>
       <c r="C78" s="2"/>
       <c r="D78" t="s" s="2">
-        <v>129</v>
+        <v>77</v>
       </c>
       <c r="E78" s="2"/>
       <c r="F78" t="s" s="2">
@@ -10292,19 +10145,19 @@
         <v>77</v>
       </c>
       <c r="J78" t="s" s="2">
-        <v>77</v>
+        <v>86</v>
       </c>
       <c r="K78" t="s" s="2">
-        <v>130</v>
+        <v>460</v>
       </c>
       <c r="L78" t="s" s="2">
-        <v>131</v>
+        <v>461</v>
       </c>
       <c r="M78" t="s" s="2">
-        <v>195</v>
+        <v>462</v>
       </c>
       <c r="N78" t="s" s="2">
-        <v>133</v>
+        <v>463</v>
       </c>
       <c r="O78" s="2"/>
       <c r="P78" t="s" s="2">
@@ -10342,19 +10195,19 @@
         <v>77</v>
       </c>
       <c r="AB78" t="s" s="2">
-        <v>134</v>
+        <v>77</v>
       </c>
       <c r="AC78" t="s" s="2">
-        <v>135</v>
+        <v>77</v>
       </c>
       <c r="AD78" t="s" s="2">
         <v>77</v>
       </c>
       <c r="AE78" t="s" s="2">
-        <v>136</v>
+        <v>77</v>
       </c>
       <c r="AF78" t="s" s="2">
-        <v>196</v>
+        <v>459</v>
       </c>
       <c r="AG78" t="s" s="2">
         <v>75</v>
@@ -10366,7 +10219,7 @@
         <v>92</v>
       </c>
       <c r="AJ78" t="s" s="2">
-        <v>138</v>
+        <v>156</v>
       </c>
       <c r="AK78" t="s" s="2">
         <v>77</v>
@@ -10374,10 +10227,10 @@
     </row>
     <row r="79">
       <c r="A79" t="s" s="2">
-        <v>424</v>
+        <v>464</v>
       </c>
       <c r="B79" t="s" s="2">
-        <v>424</v>
+        <v>464</v>
       </c>
       <c r="C79" s="2"/>
       <c r="D79" t="s" s="2">
@@ -10391,7 +10244,7 @@
         <v>76</v>
       </c>
       <c r="H79" t="s" s="2">
-        <v>86</v>
+        <v>77</v>
       </c>
       <c r="I79" t="s" s="2">
         <v>77</v>
@@ -10400,20 +10253,18 @@
         <v>86</v>
       </c>
       <c r="K79" t="s" s="2">
-        <v>199</v>
+        <v>465</v>
       </c>
       <c r="L79" t="s" s="2">
-        <v>200</v>
+        <v>466</v>
       </c>
       <c r="M79" t="s" s="2">
-        <v>201</v>
+        <v>467</v>
       </c>
       <c r="N79" t="s" s="2">
-        <v>202</v>
-      </c>
-      <c r="O79" t="s" s="2">
-        <v>203</v>
-      </c>
+        <v>468</v>
+      </c>
+      <c r="O79" s="2"/>
       <c r="P79" t="s" s="2">
         <v>77</v>
       </c>
@@ -10461,7 +10312,7 @@
         <v>77</v>
       </c>
       <c r="AF79" t="s" s="2">
-        <v>205</v>
+        <v>464</v>
       </c>
       <c r="AG79" t="s" s="2">
         <v>75</v>
@@ -10473,18 +10324,18 @@
         <v>92</v>
       </c>
       <c r="AJ79" t="s" s="2">
-        <v>93</v>
+        <v>156</v>
       </c>
       <c r="AK79" t="s" s="2">
         <v>77</v>
       </c>
     </row>
-    <row r="80" hidden="true">
+    <row r="80">
       <c r="A80" t="s" s="2">
-        <v>425</v>
+        <v>469</v>
       </c>
       <c r="B80" t="s" s="2">
-        <v>425</v>
+        <v>469</v>
       </c>
       <c r="C80" s="2"/>
       <c r="D80" t="s" s="2">
@@ -10495,7 +10346,7 @@
         <v>75</v>
       </c>
       <c r="G80" t="s" s="2">
-        <v>85</v>
+        <v>76</v>
       </c>
       <c r="H80" t="s" s="2">
         <v>77</v>
@@ -10504,19 +10355,23 @@
         <v>77</v>
       </c>
       <c r="J80" t="s" s="2">
-        <v>77</v>
+        <v>86</v>
       </c>
       <c r="K80" t="s" s="2">
-        <v>189</v>
+        <v>412</v>
       </c>
       <c r="L80" t="s" s="2">
-        <v>190</v>
+        <v>470</v>
       </c>
       <c r="M80" t="s" s="2">
-        <v>191</v>
-      </c>
-      <c r="N80" s="2"/>
-      <c r="O80" s="2"/>
+        <v>471</v>
+      </c>
+      <c r="N80" t="s" s="2">
+        <v>472</v>
+      </c>
+      <c r="O80" t="s" s="2">
+        <v>473</v>
+      </c>
       <c r="P80" t="s" s="2">
         <v>77</v>
       </c>
@@ -10564,41 +10419,41 @@
         <v>77</v>
       </c>
       <c r="AF80" t="s" s="2">
-        <v>192</v>
+        <v>469</v>
       </c>
       <c r="AG80" t="s" s="2">
         <v>75</v>
       </c>
       <c r="AH80" t="s" s="2">
-        <v>85</v>
+        <v>76</v>
       </c>
       <c r="AI80" t="s" s="2">
-        <v>77</v>
+        <v>92</v>
       </c>
       <c r="AJ80" t="s" s="2">
-        <v>77</v>
+        <v>474</v>
       </c>
       <c r="AK80" t="s" s="2">
         <v>77</v>
       </c>
     </row>
-    <row r="81" hidden="true">
+    <row r="81">
       <c r="A81" t="s" s="2">
-        <v>426</v>
+        <v>475</v>
       </c>
       <c r="B81" t="s" s="2">
-        <v>426</v>
+        <v>475</v>
       </c>
       <c r="C81" s="2"/>
       <c r="D81" t="s" s="2">
-        <v>129</v>
+        <v>77</v>
       </c>
       <c r="E81" s="2"/>
       <c r="F81" t="s" s="2">
         <v>75</v>
       </c>
       <c r="G81" t="s" s="2">
-        <v>76</v>
+        <v>85</v>
       </c>
       <c r="H81" t="s" s="2">
         <v>77</v>
@@ -10610,17 +10465,15 @@
         <v>77</v>
       </c>
       <c r="K81" t="s" s="2">
-        <v>130</v>
+        <v>194</v>
       </c>
       <c r="L81" t="s" s="2">
-        <v>131</v>
+        <v>195</v>
       </c>
       <c r="M81" t="s" s="2">
-        <v>195</v>
-      </c>
-      <c r="N81" t="s" s="2">
-        <v>133</v>
-      </c>
+        <v>196</v>
+      </c>
+      <c r="N81" s="2"/>
       <c r="O81" s="2"/>
       <c r="P81" t="s" s="2">
         <v>77</v>
@@ -10657,31 +10510,31 @@
         <v>77</v>
       </c>
       <c r="AB81" t="s" s="2">
-        <v>134</v>
+        <v>77</v>
       </c>
       <c r="AC81" t="s" s="2">
-        <v>135</v>
+        <v>77</v>
       </c>
       <c r="AD81" t="s" s="2">
         <v>77</v>
       </c>
       <c r="AE81" t="s" s="2">
-        <v>136</v>
+        <v>77</v>
       </c>
       <c r="AF81" t="s" s="2">
-        <v>196</v>
+        <v>197</v>
       </c>
       <c r="AG81" t="s" s="2">
         <v>75</v>
       </c>
       <c r="AH81" t="s" s="2">
-        <v>76</v>
+        <v>85</v>
       </c>
       <c r="AI81" t="s" s="2">
-        <v>92</v>
+        <v>77</v>
       </c>
       <c r="AJ81" t="s" s="2">
-        <v>138</v>
+        <v>77</v>
       </c>
       <c r="AK81" t="s" s="2">
         <v>77</v>
@@ -10689,46 +10542,44 @@
     </row>
     <row r="82">
       <c r="A82" t="s" s="2">
-        <v>427</v>
+        <v>476</v>
       </c>
       <c r="B82" t="s" s="2">
-        <v>427</v>
+        <v>476</v>
       </c>
       <c r="C82" s="2"/>
       <c r="D82" t="s" s="2">
-        <v>77</v>
+        <v>129</v>
       </c>
       <c r="E82" s="2"/>
       <c r="F82" t="s" s="2">
-        <v>85</v>
+        <v>75</v>
       </c>
       <c r="G82" t="s" s="2">
-        <v>85</v>
+        <v>76</v>
       </c>
       <c r="H82" t="s" s="2">
-        <v>86</v>
+        <v>77</v>
       </c>
       <c r="I82" t="s" s="2">
         <v>77</v>
       </c>
       <c r="J82" t="s" s="2">
-        <v>86</v>
+        <v>77</v>
       </c>
       <c r="K82" t="s" s="2">
-        <v>100</v>
+        <v>130</v>
       </c>
       <c r="L82" t="s" s="2">
-        <v>212</v>
+        <v>131</v>
       </c>
       <c r="M82" t="s" s="2">
-        <v>213</v>
+        <v>199</v>
       </c>
       <c r="N82" t="s" s="2">
-        <v>214</v>
-      </c>
-      <c r="O82" t="s" s="2">
-        <v>215</v>
-      </c>
+        <v>133</v>
+      </c>
+      <c r="O82" s="2"/>
       <c r="P82" t="s" s="2">
         <v>77</v>
       </c>
@@ -10764,76 +10615,78 @@
         <v>77</v>
       </c>
       <c r="AB82" t="s" s="2">
-        <v>77</v>
+        <v>134</v>
       </c>
       <c r="AC82" t="s" s="2">
-        <v>77</v>
+        <v>135</v>
       </c>
       <c r="AD82" t="s" s="2">
         <v>77</v>
       </c>
       <c r="AE82" t="s" s="2">
-        <v>77</v>
+        <v>136</v>
       </c>
       <c r="AF82" t="s" s="2">
-        <v>216</v>
+        <v>200</v>
       </c>
       <c r="AG82" t="s" s="2">
         <v>75</v>
       </c>
       <c r="AH82" t="s" s="2">
-        <v>85</v>
+        <v>76</v>
       </c>
       <c r="AI82" t="s" s="2">
         <v>92</v>
       </c>
       <c r="AJ82" t="s" s="2">
-        <v>93</v>
+        <v>138</v>
       </c>
       <c r="AK82" t="s" s="2">
         <v>77</v>
       </c>
     </row>
-    <row r="83" hidden="true">
+    <row r="83">
       <c r="A83" t="s" s="2">
-        <v>428</v>
+        <v>477</v>
       </c>
       <c r="B83" t="s" s="2">
-        <v>428</v>
+        <v>477</v>
       </c>
       <c r="C83" s="2"/>
       <c r="D83" t="s" s="2">
-        <v>77</v>
+        <v>421</v>
       </c>
       <c r="E83" s="2"/>
       <c r="F83" t="s" s="2">
         <v>75</v>
       </c>
       <c r="G83" t="s" s="2">
-        <v>85</v>
+        <v>76</v>
       </c>
       <c r="H83" t="s" s="2">
         <v>77</v>
       </c>
       <c r="I83" t="s" s="2">
-        <v>77</v>
+        <v>86</v>
       </c>
       <c r="J83" t="s" s="2">
         <v>86</v>
       </c>
       <c r="K83" t="s" s="2">
-        <v>189</v>
+        <v>130</v>
       </c>
       <c r="L83" t="s" s="2">
-        <v>219</v>
+        <v>422</v>
       </c>
       <c r="M83" t="s" s="2">
-        <v>220</v>
+        <v>423</v>
       </c>
       <c r="N83" t="s" s="2">
-        <v>221</v>
-      </c>
-      <c r="O83" s="2"/>
+        <v>133</v>
+      </c>
+      <c r="O83" t="s" s="2">
+        <v>142</v>
+      </c>
       <c r="P83" t="s" s="2">
         <v>77</v>
       </c>
@@ -10881,19 +10734,19 @@
         <v>77</v>
       </c>
       <c r="AF83" t="s" s="2">
-        <v>222</v>
+        <v>424</v>
       </c>
       <c r="AG83" t="s" s="2">
         <v>75</v>
       </c>
       <c r="AH83" t="s" s="2">
-        <v>85</v>
+        <v>76</v>
       </c>
       <c r="AI83" t="s" s="2">
         <v>92</v>
       </c>
       <c r="AJ83" t="s" s="2">
-        <v>93</v>
+        <v>138</v>
       </c>
       <c r="AK83" t="s" s="2">
         <v>77</v>
@@ -10901,10 +10754,10 @@
     </row>
     <row r="84">
       <c r="A84" t="s" s="2">
-        <v>429</v>
+        <v>478</v>
       </c>
       <c r="B84" t="s" s="2">
-        <v>429</v>
+        <v>478</v>
       </c>
       <c r="C84" s="2"/>
       <c r="D84" t="s" s="2">
@@ -10918,7 +10771,7 @@
         <v>85</v>
       </c>
       <c r="H84" t="s" s="2">
-        <v>86</v>
+        <v>77</v>
       </c>
       <c r="I84" t="s" s="2">
         <v>77</v>
@@ -10927,19 +10780,19 @@
         <v>86</v>
       </c>
       <c r="K84" t="s" s="2">
-        <v>106</v>
+        <v>173</v>
       </c>
       <c r="L84" t="s" s="2">
-        <v>225</v>
+        <v>479</v>
       </c>
       <c r="M84" t="s" s="2">
-        <v>226</v>
+        <v>480</v>
       </c>
       <c r="N84" t="s" s="2">
-        <v>227</v>
+        <v>481</v>
       </c>
       <c r="O84" t="s" s="2">
-        <v>228</v>
+        <v>189</v>
       </c>
       <c r="P84" t="s" s="2">
         <v>77</v>
@@ -10964,13 +10817,13 @@
         <v>77</v>
       </c>
       <c r="X84" t="s" s="2">
-        <v>77</v>
+        <v>190</v>
       </c>
       <c r="Y84" t="s" s="2">
-        <v>77</v>
+        <v>191</v>
       </c>
       <c r="Z84" t="s" s="2">
-        <v>77</v>
+        <v>192</v>
       </c>
       <c r="AA84" t="s" s="2">
         <v>77</v>
@@ -10988,10 +10841,10 @@
         <v>77</v>
       </c>
       <c r="AF84" t="s" s="2">
-        <v>229</v>
+        <v>478</v>
       </c>
       <c r="AG84" t="s" s="2">
-        <v>75</v>
+        <v>85</v>
       </c>
       <c r="AH84" t="s" s="2">
         <v>85</v>
@@ -11006,12 +10859,12 @@
         <v>77</v>
       </c>
     </row>
-    <row r="85" hidden="true">
+    <row r="85">
       <c r="A85" t="s" s="2">
-        <v>430</v>
+        <v>482</v>
       </c>
       <c r="B85" t="s" s="2">
-        <v>430</v>
+        <v>482</v>
       </c>
       <c r="C85" s="2"/>
       <c r="D85" t="s" s="2">
@@ -11034,19 +10887,19 @@
         <v>86</v>
       </c>
       <c r="K85" t="s" s="2">
-        <v>189</v>
+        <v>309</v>
       </c>
       <c r="L85" t="s" s="2">
-        <v>232</v>
+        <v>483</v>
       </c>
       <c r="M85" t="s" s="2">
-        <v>233</v>
+        <v>311</v>
       </c>
       <c r="N85" t="s" s="2">
-        <v>227</v>
+        <v>484</v>
       </c>
       <c r="O85" t="s" s="2">
-        <v>234</v>
+        <v>313</v>
       </c>
       <c r="P85" t="s" s="2">
         <v>77</v>
@@ -11083,19 +10936,17 @@
         <v>77</v>
       </c>
       <c r="AB85" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="AC85" t="s" s="2">
-        <v>77</v>
-      </c>
+        <v>292</v>
+      </c>
+      <c r="AC85" s="2"/>
       <c r="AD85" t="s" s="2">
         <v>77</v>
       </c>
       <c r="AE85" t="s" s="2">
-        <v>77</v>
+        <v>136</v>
       </c>
       <c r="AF85" t="s" s="2">
-        <v>235</v>
+        <v>482</v>
       </c>
       <c r="AG85" t="s" s="2">
         <v>75</v>
@@ -11113,14 +10964,16 @@
         <v>77</v>
       </c>
     </row>
-    <row r="86" hidden="true">
+    <row r="86">
       <c r="A86" t="s" s="2">
-        <v>431</v>
+        <v>485</v>
       </c>
       <c r="B86" t="s" s="2">
-        <v>431</v>
-      </c>
-      <c r="C86" s="2"/>
+        <v>482</v>
+      </c>
+      <c r="C86" t="s" s="2">
+        <v>317</v>
+      </c>
       <c r="D86" t="s" s="2">
         <v>77</v>
       </c>
@@ -11141,19 +10994,19 @@
         <v>86</v>
       </c>
       <c r="K86" t="s" s="2">
-        <v>238</v>
+        <v>318</v>
       </c>
       <c r="L86" t="s" s="2">
-        <v>239</v>
+        <v>483</v>
       </c>
       <c r="M86" t="s" s="2">
-        <v>240</v>
+        <v>311</v>
       </c>
       <c r="N86" t="s" s="2">
-        <v>241</v>
+        <v>484</v>
       </c>
       <c r="O86" t="s" s="2">
-        <v>242</v>
+        <v>313</v>
       </c>
       <c r="P86" t="s" s="2">
         <v>77</v>
@@ -11202,7 +11055,7 @@
         <v>77</v>
       </c>
       <c r="AF86" t="s" s="2">
-        <v>243</v>
+        <v>482</v>
       </c>
       <c r="AG86" t="s" s="2">
         <v>75</v>
@@ -11220,12 +11073,12 @@
         <v>77</v>
       </c>
     </row>
-    <row r="87" hidden="true">
+    <row r="87">
       <c r="A87" t="s" s="2">
-        <v>432</v>
+        <v>486</v>
       </c>
       <c r="B87" t="s" s="2">
-        <v>432</v>
+        <v>487</v>
       </c>
       <c r="C87" s="2"/>
       <c r="D87" t="s" s="2">
@@ -11245,23 +11098,19 @@
         <v>77</v>
       </c>
       <c r="J87" t="s" s="2">
-        <v>86</v>
+        <v>77</v>
       </c>
       <c r="K87" t="s" s="2">
-        <v>189</v>
+        <v>194</v>
       </c>
       <c r="L87" t="s" s="2">
-        <v>246</v>
+        <v>195</v>
       </c>
       <c r="M87" t="s" s="2">
-        <v>247</v>
-      </c>
-      <c r="N87" t="s" s="2">
-        <v>248</v>
-      </c>
-      <c r="O87" t="s" s="2">
-        <v>249</v>
-      </c>
+        <v>196</v>
+      </c>
+      <c r="N87" s="2"/>
+      <c r="O87" s="2"/>
       <c r="P87" t="s" s="2">
         <v>77</v>
       </c>
@@ -11309,7 +11158,7 @@
         <v>77</v>
       </c>
       <c r="AF87" t="s" s="2">
-        <v>250</v>
+        <v>197</v>
       </c>
       <c r="AG87" t="s" s="2">
         <v>75</v>
@@ -11318,32 +11167,32 @@
         <v>85</v>
       </c>
       <c r="AI87" t="s" s="2">
-        <v>92</v>
+        <v>77</v>
       </c>
       <c r="AJ87" t="s" s="2">
-        <v>93</v>
+        <v>77</v>
       </c>
       <c r="AK87" t="s" s="2">
         <v>77</v>
       </c>
     </row>
-    <row r="88" hidden="true">
+    <row r="88">
       <c r="A88" t="s" s="2">
-        <v>433</v>
+        <v>488</v>
       </c>
       <c r="B88" t="s" s="2">
-        <v>433</v>
+        <v>489</v>
       </c>
       <c r="C88" s="2"/>
       <c r="D88" t="s" s="2">
-        <v>77</v>
+        <v>129</v>
       </c>
       <c r="E88" s="2"/>
       <c r="F88" t="s" s="2">
         <v>75</v>
       </c>
       <c r="G88" t="s" s="2">
-        <v>85</v>
+        <v>76</v>
       </c>
       <c r="H88" t="s" s="2">
         <v>77</v>
@@ -11355,20 +11204,18 @@
         <v>77</v>
       </c>
       <c r="K88" t="s" s="2">
-        <v>173</v>
+        <v>130</v>
       </c>
       <c r="L88" t="s" s="2">
-        <v>434</v>
+        <v>131</v>
       </c>
       <c r="M88" t="s" s="2">
-        <v>435</v>
+        <v>199</v>
       </c>
       <c r="N88" t="s" s="2">
-        <v>436</v>
-      </c>
-      <c r="O88" t="s" s="2">
-        <v>437</v>
-      </c>
+        <v>133</v>
+      </c>
+      <c r="O88" s="2"/>
       <c r="P88" t="s" s="2">
         <v>77</v>
       </c>
@@ -11392,54 +11239,54 @@
         <v>77</v>
       </c>
       <c r="X88" t="s" s="2">
-        <v>257</v>
+        <v>77</v>
       </c>
       <c r="Y88" t="s" s="2">
-        <v>438</v>
+        <v>77</v>
       </c>
       <c r="Z88" t="s" s="2">
-        <v>439</v>
+        <v>77</v>
       </c>
       <c r="AA88" t="s" s="2">
         <v>77</v>
       </c>
       <c r="AB88" t="s" s="2">
-        <v>77</v>
+        <v>134</v>
       </c>
       <c r="AC88" t="s" s="2">
-        <v>77</v>
+        <v>135</v>
       </c>
       <c r="AD88" t="s" s="2">
         <v>77</v>
       </c>
       <c r="AE88" t="s" s="2">
-        <v>77</v>
+        <v>136</v>
       </c>
       <c r="AF88" t="s" s="2">
-        <v>433</v>
+        <v>200</v>
       </c>
       <c r="AG88" t="s" s="2">
         <v>75</v>
       </c>
       <c r="AH88" t="s" s="2">
-        <v>85</v>
+        <v>76</v>
       </c>
       <c r="AI88" t="s" s="2">
         <v>92</v>
       </c>
       <c r="AJ88" t="s" s="2">
-        <v>93</v>
+        <v>138</v>
       </c>
       <c r="AK88" t="s" s="2">
         <v>77</v>
       </c>
     </row>
-    <row r="89" hidden="true">
+    <row r="89">
       <c r="A89" t="s" s="2">
-        <v>440</v>
+        <v>490</v>
       </c>
       <c r="B89" t="s" s="2">
-        <v>440</v>
+        <v>491</v>
       </c>
       <c r="C89" s="2"/>
       <c r="D89" t="s" s="2">
@@ -11447,7 +11294,7 @@
       </c>
       <c r="E89" s="2"/>
       <c r="F89" t="s" s="2">
-        <v>75</v>
+        <v>85</v>
       </c>
       <c r="G89" t="s" s="2">
         <v>85</v>
@@ -11459,21 +11306,23 @@
         <v>77</v>
       </c>
       <c r="J89" t="s" s="2">
-        <v>77</v>
+        <v>86</v>
       </c>
       <c r="K89" t="s" s="2">
-        <v>441</v>
+        <v>326</v>
       </c>
       <c r="L89" t="s" s="2">
-        <v>442</v>
+        <v>327</v>
       </c>
       <c r="M89" t="s" s="2">
-        <v>443</v>
+        <v>328</v>
       </c>
       <c r="N89" t="s" s="2">
-        <v>444</v>
-      </c>
-      <c r="O89" s="2"/>
+        <v>329</v>
+      </c>
+      <c r="O89" t="s" s="2">
+        <v>330</v>
+      </c>
       <c r="P89" t="s" s="2">
         <v>77</v>
       </c>
@@ -11521,7 +11370,7 @@
         <v>77</v>
       </c>
       <c r="AF89" t="s" s="2">
-        <v>440</v>
+        <v>331</v>
       </c>
       <c r="AG89" t="s" s="2">
         <v>75</v>
@@ -11533,18 +11382,18 @@
         <v>92</v>
       </c>
       <c r="AJ89" t="s" s="2">
-        <v>156</v>
+        <v>93</v>
       </c>
       <c r="AK89" t="s" s="2">
         <v>77</v>
       </c>
     </row>
-    <row r="90" hidden="true">
+    <row r="90">
       <c r="A90" t="s" s="2">
-        <v>445</v>
+        <v>492</v>
       </c>
       <c r="B90" t="s" s="2">
-        <v>445</v>
+        <v>493</v>
       </c>
       <c r="C90" s="2"/>
       <c r="D90" t="s" s="2">
@@ -11561,28 +11410,32 @@
         <v>77</v>
       </c>
       <c r="I90" t="s" s="2">
-        <v>77</v>
+        <v>86</v>
       </c>
       <c r="J90" t="s" s="2">
-        <v>77</v>
+        <v>86</v>
       </c>
       <c r="K90" t="s" s="2">
-        <v>446</v>
+        <v>106</v>
       </c>
       <c r="L90" t="s" s="2">
-        <v>447</v>
+        <v>335</v>
       </c>
       <c r="M90" t="s" s="2">
-        <v>448</v>
+        <v>336</v>
       </c>
       <c r="N90" t="s" s="2">
-        <v>449</v>
-      </c>
-      <c r="O90" s="2"/>
+        <v>224</v>
+      </c>
+      <c r="O90" t="s" s="2">
+        <v>337</v>
+      </c>
       <c r="P90" t="s" s="2">
         <v>77</v>
       </c>
-      <c r="Q90" s="2"/>
+      <c r="Q90" t="s" s="2">
+        <v>338</v>
+      </c>
       <c r="R90" t="s" s="2">
         <v>77</v>
       </c>
@@ -11602,13 +11455,13 @@
         <v>77</v>
       </c>
       <c r="X90" t="s" s="2">
-        <v>77</v>
+        <v>168</v>
       </c>
       <c r="Y90" t="s" s="2">
-        <v>77</v>
+        <v>339</v>
       </c>
       <c r="Z90" t="s" s="2">
-        <v>77</v>
+        <v>340</v>
       </c>
       <c r="AA90" t="s" s="2">
         <v>77</v>
@@ -11626,7 +11479,7 @@
         <v>77</v>
       </c>
       <c r="AF90" t="s" s="2">
-        <v>445</v>
+        <v>341</v>
       </c>
       <c r="AG90" t="s" s="2">
         <v>75</v>
@@ -11638,18 +11491,18 @@
         <v>92</v>
       </c>
       <c r="AJ90" t="s" s="2">
-        <v>156</v>
+        <v>93</v>
       </c>
       <c r="AK90" t="s" s="2">
         <v>77</v>
       </c>
     </row>
-    <row r="91" hidden="true">
+    <row r="91">
       <c r="A91" t="s" s="2">
-        <v>450</v>
+        <v>494</v>
       </c>
       <c r="B91" t="s" s="2">
-        <v>450</v>
+        <v>495</v>
       </c>
       <c r="C91" s="2"/>
       <c r="D91" t="s" s="2">
@@ -11657,10 +11510,10 @@
       </c>
       <c r="E91" s="2"/>
       <c r="F91" t="s" s="2">
-        <v>75</v>
+        <v>85</v>
       </c>
       <c r="G91" t="s" s="2">
-        <v>76</v>
+        <v>85</v>
       </c>
       <c r="H91" t="s" s="2">
         <v>77</v>
@@ -11669,22 +11522,22 @@
         <v>77</v>
       </c>
       <c r="J91" t="s" s="2">
-        <v>77</v>
+        <v>86</v>
       </c>
       <c r="K91" t="s" s="2">
-        <v>451</v>
+        <v>194</v>
       </c>
       <c r="L91" t="s" s="2">
-        <v>452</v>
+        <v>344</v>
       </c>
       <c r="M91" t="s" s="2">
-        <v>453</v>
+        <v>345</v>
       </c>
       <c r="N91" t="s" s="2">
-        <v>454</v>
+        <v>224</v>
       </c>
       <c r="O91" t="s" s="2">
-        <v>455</v>
+        <v>346</v>
       </c>
       <c r="P91" t="s" s="2">
         <v>77</v>
@@ -11733,30 +11586,30 @@
         <v>77</v>
       </c>
       <c r="AF91" t="s" s="2">
-        <v>450</v>
+        <v>347</v>
       </c>
       <c r="AG91" t="s" s="2">
         <v>75</v>
       </c>
       <c r="AH91" t="s" s="2">
-        <v>76</v>
+        <v>85</v>
       </c>
       <c r="AI91" t="s" s="2">
         <v>92</v>
       </c>
       <c r="AJ91" t="s" s="2">
-        <v>456</v>
+        <v>93</v>
       </c>
       <c r="AK91" t="s" s="2">
         <v>77</v>
       </c>
     </row>
-    <row r="92" hidden="true">
+    <row r="92">
       <c r="A92" t="s" s="2">
-        <v>457</v>
+        <v>496</v>
       </c>
       <c r="B92" t="s" s="2">
-        <v>457</v>
+        <v>497</v>
       </c>
       <c r="C92" s="2"/>
       <c r="D92" t="s" s="2">
@@ -11764,7 +11617,7 @@
       </c>
       <c r="E92" s="2"/>
       <c r="F92" t="s" s="2">
-        <v>75</v>
+        <v>85</v>
       </c>
       <c r="G92" t="s" s="2">
         <v>85</v>
@@ -11776,19 +11629,23 @@
         <v>77</v>
       </c>
       <c r="J92" t="s" s="2">
-        <v>77</v>
+        <v>86</v>
       </c>
       <c r="K92" t="s" s="2">
-        <v>189</v>
+        <v>100</v>
       </c>
       <c r="L92" t="s" s="2">
-        <v>190</v>
+        <v>350</v>
       </c>
       <c r="M92" t="s" s="2">
-        <v>191</v>
-      </c>
-      <c r="N92" s="2"/>
-      <c r="O92" s="2"/>
+        <v>351</v>
+      </c>
+      <c r="N92" t="s" s="2">
+        <v>352</v>
+      </c>
+      <c r="O92" t="s" s="2">
+        <v>353</v>
+      </c>
       <c r="P92" t="s" s="2">
         <v>77</v>
       </c>
@@ -11797,7 +11654,7 @@
         <v>77</v>
       </c>
       <c r="S92" t="s" s="2">
-        <v>77</v>
+        <v>354</v>
       </c>
       <c r="T92" t="s" s="2">
         <v>77</v>
@@ -11836,7 +11693,7 @@
         <v>77</v>
       </c>
       <c r="AF92" t="s" s="2">
-        <v>192</v>
+        <v>355</v>
       </c>
       <c r="AG92" t="s" s="2">
         <v>75</v>
@@ -11845,32 +11702,32 @@
         <v>85</v>
       </c>
       <c r="AI92" t="s" s="2">
-        <v>77</v>
+        <v>356</v>
       </c>
       <c r="AJ92" t="s" s="2">
-        <v>77</v>
+        <v>93</v>
       </c>
       <c r="AK92" t="s" s="2">
         <v>77</v>
       </c>
     </row>
-    <row r="93" hidden="true">
+    <row r="93">
       <c r="A93" t="s" s="2">
-        <v>458</v>
+        <v>498</v>
       </c>
       <c r="B93" t="s" s="2">
-        <v>458</v>
+        <v>499</v>
       </c>
       <c r="C93" s="2"/>
       <c r="D93" t="s" s="2">
-        <v>129</v>
+        <v>77</v>
       </c>
       <c r="E93" s="2"/>
       <c r="F93" t="s" s="2">
-        <v>75</v>
+        <v>85</v>
       </c>
       <c r="G93" t="s" s="2">
-        <v>76</v>
+        <v>85</v>
       </c>
       <c r="H93" t="s" s="2">
         <v>77</v>
@@ -11879,21 +11736,23 @@
         <v>77</v>
       </c>
       <c r="J93" t="s" s="2">
-        <v>77</v>
+        <v>86</v>
       </c>
       <c r="K93" t="s" s="2">
-        <v>130</v>
+        <v>106</v>
       </c>
       <c r="L93" t="s" s="2">
-        <v>131</v>
+        <v>359</v>
       </c>
       <c r="M93" t="s" s="2">
-        <v>195</v>
+        <v>360</v>
       </c>
       <c r="N93" t="s" s="2">
-        <v>133</v>
-      </c>
-      <c r="O93" s="2"/>
+        <v>361</v>
+      </c>
+      <c r="O93" t="s" s="2">
+        <v>362</v>
+      </c>
       <c r="P93" t="s" s="2">
         <v>77</v>
       </c>
@@ -11929,77 +11788,77 @@
         <v>77</v>
       </c>
       <c r="AB93" t="s" s="2">
-        <v>134</v>
+        <v>77</v>
       </c>
       <c r="AC93" t="s" s="2">
-        <v>135</v>
+        <v>77</v>
       </c>
       <c r="AD93" t="s" s="2">
         <v>77</v>
       </c>
       <c r="AE93" t="s" s="2">
-        <v>136</v>
+        <v>77</v>
       </c>
       <c r="AF93" t="s" s="2">
-        <v>196</v>
+        <v>364</v>
       </c>
       <c r="AG93" t="s" s="2">
         <v>75</v>
       </c>
       <c r="AH93" t="s" s="2">
-        <v>76</v>
+        <v>85</v>
       </c>
       <c r="AI93" t="s" s="2">
         <v>92</v>
       </c>
       <c r="AJ93" t="s" s="2">
-        <v>138</v>
+        <v>93</v>
       </c>
       <c r="AK93" t="s" s="2">
         <v>77</v>
       </c>
     </row>
-    <row r="94" hidden="true">
+    <row r="94">
       <c r="A94" t="s" s="2">
-        <v>459</v>
+        <v>500</v>
       </c>
       <c r="B94" t="s" s="2">
-        <v>459</v>
+        <v>500</v>
       </c>
       <c r="C94" s="2"/>
       <c r="D94" t="s" s="2">
-        <v>460</v>
+        <v>77</v>
       </c>
       <c r="E94" s="2"/>
       <c r="F94" t="s" s="2">
         <v>75</v>
       </c>
       <c r="G94" t="s" s="2">
-        <v>76</v>
+        <v>85</v>
       </c>
       <c r="H94" t="s" s="2">
         <v>77</v>
       </c>
       <c r="I94" t="s" s="2">
-        <v>86</v>
+        <v>77</v>
       </c>
       <c r="J94" t="s" s="2">
-        <v>86</v>
+        <v>77</v>
       </c>
       <c r="K94" t="s" s="2">
-        <v>130</v>
+        <v>173</v>
       </c>
       <c r="L94" t="s" s="2">
-        <v>461</v>
+        <v>501</v>
       </c>
       <c r="M94" t="s" s="2">
-        <v>462</v>
+        <v>502</v>
       </c>
       <c r="N94" t="s" s="2">
-        <v>133</v>
+        <v>503</v>
       </c>
       <c r="O94" t="s" s="2">
-        <v>142</v>
+        <v>369</v>
       </c>
       <c r="P94" t="s" s="2">
         <v>77</v>
@@ -12024,13 +11883,13 @@
         <v>77</v>
       </c>
       <c r="X94" t="s" s="2">
-        <v>77</v>
+        <v>370</v>
       </c>
       <c r="Y94" t="s" s="2">
-        <v>77</v>
+        <v>371</v>
       </c>
       <c r="Z94" t="s" s="2">
-        <v>77</v>
+        <v>372</v>
       </c>
       <c r="AA94" t="s" s="2">
         <v>77</v>
@@ -12048,41 +11907,41 @@
         <v>77</v>
       </c>
       <c r="AF94" t="s" s="2">
-        <v>463</v>
+        <v>500</v>
       </c>
       <c r="AG94" t="s" s="2">
         <v>75</v>
       </c>
       <c r="AH94" t="s" s="2">
-        <v>76</v>
+        <v>85</v>
       </c>
       <c r="AI94" t="s" s="2">
-        <v>92</v>
+        <v>373</v>
       </c>
       <c r="AJ94" t="s" s="2">
-        <v>138</v>
+        <v>93</v>
       </c>
       <c r="AK94" t="s" s="2">
         <v>77</v>
       </c>
     </row>
-    <row r="95" hidden="true">
+    <row r="95">
       <c r="A95" t="s" s="2">
-        <v>464</v>
+        <v>504</v>
       </c>
       <c r="B95" t="s" s="2">
-        <v>464</v>
+        <v>504</v>
       </c>
       <c r="C95" s="2"/>
       <c r="D95" t="s" s="2">
-        <v>77</v>
+        <v>375</v>
       </c>
       <c r="E95" s="2"/>
       <c r="F95" t="s" s="2">
         <v>75</v>
       </c>
       <c r="G95" t="s" s="2">
-        <v>85</v>
+        <v>76</v>
       </c>
       <c r="H95" t="s" s="2">
         <v>77</v>
@@ -12094,18 +11953,20 @@
         <v>77</v>
       </c>
       <c r="K95" t="s" s="2">
-        <v>465</v>
+        <v>173</v>
       </c>
       <c r="L95" t="s" s="2">
-        <v>466</v>
+        <v>376</v>
       </c>
       <c r="M95" t="s" s="2">
-        <v>467</v>
+        <v>377</v>
       </c>
       <c r="N95" t="s" s="2">
-        <v>468</v>
-      </c>
-      <c r="O95" s="2"/>
+        <v>378</v>
+      </c>
+      <c r="O95" t="s" s="2">
+        <v>379</v>
+      </c>
       <c r="P95" t="s" s="2">
         <v>77</v>
       </c>
@@ -12129,13 +11990,13 @@
         <v>77</v>
       </c>
       <c r="X95" t="s" s="2">
-        <v>77</v>
+        <v>370</v>
       </c>
       <c r="Y95" t="s" s="2">
-        <v>77</v>
+        <v>380</v>
       </c>
       <c r="Z95" t="s" s="2">
-        <v>77</v>
+        <v>381</v>
       </c>
       <c r="AA95" t="s" s="2">
         <v>77</v>
@@ -12153,30 +12014,30 @@
         <v>77</v>
       </c>
       <c r="AF95" t="s" s="2">
-        <v>464</v>
+        <v>504</v>
       </c>
       <c r="AG95" t="s" s="2">
         <v>75</v>
       </c>
       <c r="AH95" t="s" s="2">
-        <v>85</v>
+        <v>76</v>
       </c>
       <c r="AI95" t="s" s="2">
-        <v>469</v>
+        <v>92</v>
       </c>
       <c r="AJ95" t="s" s="2">
-        <v>470</v>
+        <v>93</v>
       </c>
       <c r="AK95" t="s" s="2">
         <v>77</v>
       </c>
     </row>
-    <row r="96" hidden="true">
+    <row r="96">
       <c r="A96" t="s" s="2">
-        <v>471</v>
+        <v>505</v>
       </c>
       <c r="B96" t="s" s="2">
-        <v>471</v>
+        <v>505</v>
       </c>
       <c r="C96" s="2"/>
       <c r="D96" t="s" s="2">
@@ -12187,7 +12048,7 @@
         <v>75</v>
       </c>
       <c r="G96" t="s" s="2">
-        <v>85</v>
+        <v>76</v>
       </c>
       <c r="H96" t="s" s="2">
         <v>77</v>
@@ -12199,18 +12060,20 @@
         <v>77</v>
       </c>
       <c r="K96" t="s" s="2">
-        <v>465</v>
+        <v>78</v>
       </c>
       <c r="L96" t="s" s="2">
-        <v>472</v>
+        <v>506</v>
       </c>
       <c r="M96" t="s" s="2">
-        <v>473</v>
+        <v>507</v>
       </c>
       <c r="N96" t="s" s="2">
-        <v>468</v>
-      </c>
-      <c r="O96" s="2"/>
+        <v>415</v>
+      </c>
+      <c r="O96" t="s" s="2">
+        <v>416</v>
+      </c>
       <c r="P96" t="s" s="2">
         <v>77</v>
       </c>
@@ -12258,2488 +12121,25 @@
         <v>77</v>
       </c>
       <c r="AF96" t="s" s="2">
-        <v>471</v>
+        <v>505</v>
       </c>
       <c r="AG96" t="s" s="2">
         <v>75</v>
       </c>
       <c r="AH96" t="s" s="2">
-        <v>85</v>
+        <v>76</v>
       </c>
       <c r="AI96" t="s" s="2">
-        <v>469</v>
+        <v>77</v>
       </c>
       <c r="AJ96" t="s" s="2">
-        <v>470</v>
+        <v>77</v>
       </c>
       <c r="AK96" t="s" s="2">
-        <v>77</v>
-      </c>
-    </row>
-    <row r="97" hidden="true">
-      <c r="A97" t="s" s="2">
-        <v>474</v>
-      </c>
-      <c r="B97" t="s" s="2">
-        <v>474</v>
-      </c>
-      <c r="C97" s="2"/>
-      <c r="D97" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="E97" s="2"/>
-      <c r="F97" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="G97" t="s" s="2">
-        <v>85</v>
-      </c>
-      <c r="H97" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="I97" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="J97" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="K97" t="s" s="2">
-        <v>173</v>
-      </c>
-      <c r="L97" t="s" s="2">
-        <v>475</v>
-      </c>
-      <c r="M97" t="s" s="2">
-        <v>476</v>
-      </c>
-      <c r="N97" t="s" s="2">
-        <v>477</v>
-      </c>
-      <c r="O97" t="s" s="2">
-        <v>478</v>
-      </c>
-      <c r="P97" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="Q97" s="2"/>
-      <c r="R97" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="S97" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="T97" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="U97" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="V97" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="W97" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="X97" t="s" s="2">
-        <v>110</v>
-      </c>
-      <c r="Y97" t="s" s="2">
-        <v>479</v>
-      </c>
-      <c r="Z97" t="s" s="2">
-        <v>480</v>
-      </c>
-      <c r="AA97" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="AB97" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="AC97" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="AD97" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="AE97" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="AF97" t="s" s="2">
-        <v>474</v>
-      </c>
-      <c r="AG97" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="AH97" t="s" s="2">
-        <v>85</v>
-      </c>
-      <c r="AI97" t="s" s="2">
-        <v>92</v>
-      </c>
-      <c r="AJ97" t="s" s="2">
-        <v>93</v>
-      </c>
-      <c r="AK97" t="s" s="2">
-        <v>77</v>
-      </c>
-    </row>
-    <row r="98" hidden="true">
-      <c r="A98" t="s" s="2">
-        <v>481</v>
-      </c>
-      <c r="B98" t="s" s="2">
-        <v>481</v>
-      </c>
-      <c r="C98" s="2"/>
-      <c r="D98" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="E98" s="2"/>
-      <c r="F98" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="G98" t="s" s="2">
-        <v>76</v>
-      </c>
-      <c r="H98" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="I98" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="J98" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="K98" t="s" s="2">
-        <v>173</v>
-      </c>
-      <c r="L98" t="s" s="2">
-        <v>482</v>
-      </c>
-      <c r="M98" t="s" s="2">
-        <v>483</v>
-      </c>
-      <c r="N98" t="s" s="2">
-        <v>484</v>
-      </c>
-      <c r="O98" t="s" s="2">
-        <v>485</v>
-      </c>
-      <c r="P98" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="Q98" s="2"/>
-      <c r="R98" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="S98" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="T98" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="U98" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="V98" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="W98" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="X98" t="s" s="2">
-        <v>257</v>
-      </c>
-      <c r="Y98" t="s" s="2">
-        <v>486</v>
-      </c>
-      <c r="Z98" t="s" s="2">
-        <v>487</v>
-      </c>
-      <c r="AA98" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="AB98" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="AC98" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="AD98" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="AE98" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="AF98" t="s" s="2">
-        <v>481</v>
-      </c>
-      <c r="AG98" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="AH98" t="s" s="2">
-        <v>76</v>
-      </c>
-      <c r="AI98" t="s" s="2">
-        <v>92</v>
-      </c>
-      <c r="AJ98" t="s" s="2">
-        <v>93</v>
-      </c>
-      <c r="AK98" t="s" s="2">
-        <v>77</v>
-      </c>
-    </row>
-    <row r="99" hidden="true">
-      <c r="A99" t="s" s="2">
-        <v>488</v>
-      </c>
-      <c r="B99" t="s" s="2">
-        <v>488</v>
-      </c>
-      <c r="C99" s="2"/>
-      <c r="D99" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="E99" s="2"/>
-      <c r="F99" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="G99" t="s" s="2">
-        <v>85</v>
-      </c>
-      <c r="H99" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="I99" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="J99" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="K99" t="s" s="2">
-        <v>489</v>
-      </c>
-      <c r="L99" t="s" s="2">
-        <v>490</v>
-      </c>
-      <c r="M99" t="s" s="2">
-        <v>491</v>
-      </c>
-      <c r="N99" t="s" s="2">
-        <v>492</v>
-      </c>
-      <c r="O99" t="s" s="2">
-        <v>493</v>
-      </c>
-      <c r="P99" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="Q99" s="2"/>
-      <c r="R99" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="S99" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="T99" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="U99" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="V99" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="W99" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="X99" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="Y99" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="Z99" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="AA99" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="AB99" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="AC99" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="AD99" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="AE99" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="AF99" t="s" s="2">
-        <v>488</v>
-      </c>
-      <c r="AG99" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="AH99" t="s" s="2">
-        <v>85</v>
-      </c>
-      <c r="AI99" t="s" s="2">
-        <v>92</v>
-      </c>
-      <c r="AJ99" t="s" s="2">
-        <v>494</v>
-      </c>
-      <c r="AK99" t="s" s="2">
-        <v>77</v>
-      </c>
-    </row>
-    <row r="100" hidden="true">
-      <c r="A100" t="s" s="2">
-        <v>495</v>
-      </c>
-      <c r="B100" t="s" s="2">
-        <v>495</v>
-      </c>
-      <c r="C100" s="2"/>
-      <c r="D100" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="E100" s="2"/>
-      <c r="F100" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="G100" t="s" s="2">
-        <v>85</v>
-      </c>
-      <c r="H100" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="I100" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="J100" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="K100" t="s" s="2">
-        <v>189</v>
-      </c>
-      <c r="L100" t="s" s="2">
-        <v>496</v>
-      </c>
-      <c r="M100" t="s" s="2">
-        <v>497</v>
-      </c>
-      <c r="N100" t="s" s="2">
-        <v>227</v>
-      </c>
-      <c r="O100" s="2"/>
-      <c r="P100" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="Q100" s="2"/>
-      <c r="R100" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="S100" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="T100" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="U100" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="V100" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="W100" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="X100" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="Y100" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="Z100" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="AA100" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="AB100" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="AC100" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="AD100" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="AE100" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="AF100" t="s" s="2">
-        <v>495</v>
-      </c>
-      <c r="AG100" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="AH100" t="s" s="2">
-        <v>85</v>
-      </c>
-      <c r="AI100" t="s" s="2">
-        <v>92</v>
-      </c>
-      <c r="AJ100" t="s" s="2">
-        <v>93</v>
-      </c>
-      <c r="AK100" t="s" s="2">
-        <v>77</v>
-      </c>
-    </row>
-    <row r="101" hidden="true">
-      <c r="A101" t="s" s="2">
-        <v>498</v>
-      </c>
-      <c r="B101" t="s" s="2">
-        <v>498</v>
-      </c>
-      <c r="C101" s="2"/>
-      <c r="D101" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="E101" s="2"/>
-      <c r="F101" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="G101" t="s" s="2">
-        <v>76</v>
-      </c>
-      <c r="H101" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="I101" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="J101" t="s" s="2">
-        <v>86</v>
-      </c>
-      <c r="K101" t="s" s="2">
-        <v>499</v>
-      </c>
-      <c r="L101" t="s" s="2">
-        <v>500</v>
-      </c>
-      <c r="M101" t="s" s="2">
-        <v>501</v>
-      </c>
-      <c r="N101" t="s" s="2">
-        <v>502</v>
-      </c>
-      <c r="O101" s="2"/>
-      <c r="P101" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="Q101" s="2"/>
-      <c r="R101" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="S101" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="T101" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="U101" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="V101" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="W101" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="X101" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="Y101" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="Z101" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="AA101" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="AB101" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="AC101" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="AD101" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="AE101" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="AF101" t="s" s="2">
-        <v>498</v>
-      </c>
-      <c r="AG101" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="AH101" t="s" s="2">
-        <v>76</v>
-      </c>
-      <c r="AI101" t="s" s="2">
-        <v>92</v>
-      </c>
-      <c r="AJ101" t="s" s="2">
-        <v>156</v>
-      </c>
-      <c r="AK101" t="s" s="2">
-        <v>77</v>
-      </c>
-    </row>
-    <row r="102" hidden="true">
-      <c r="A102" t="s" s="2">
-        <v>503</v>
-      </c>
-      <c r="B102" t="s" s="2">
-        <v>503</v>
-      </c>
-      <c r="C102" s="2"/>
-      <c r="D102" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="E102" s="2"/>
-      <c r="F102" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="G102" t="s" s="2">
-        <v>76</v>
-      </c>
-      <c r="H102" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="I102" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="J102" t="s" s="2">
-        <v>86</v>
-      </c>
-      <c r="K102" t="s" s="2">
-        <v>504</v>
-      </c>
-      <c r="L102" t="s" s="2">
-        <v>505</v>
-      </c>
-      <c r="M102" t="s" s="2">
-        <v>506</v>
-      </c>
-      <c r="N102" t="s" s="2">
-        <v>507</v>
-      </c>
-      <c r="O102" s="2"/>
-      <c r="P102" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="Q102" s="2"/>
-      <c r="R102" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="S102" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="T102" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="U102" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="V102" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="W102" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="X102" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="Y102" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="Z102" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="AA102" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="AB102" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="AC102" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="AD102" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="AE102" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="AF102" t="s" s="2">
-        <v>503</v>
-      </c>
-      <c r="AG102" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="AH102" t="s" s="2">
-        <v>76</v>
-      </c>
-      <c r="AI102" t="s" s="2">
-        <v>92</v>
-      </c>
-      <c r="AJ102" t="s" s="2">
-        <v>156</v>
-      </c>
-      <c r="AK102" t="s" s="2">
-        <v>77</v>
-      </c>
-    </row>
-    <row r="103" hidden="true">
-      <c r="A103" t="s" s="2">
-        <v>508</v>
-      </c>
-      <c r="B103" t="s" s="2">
-        <v>508</v>
-      </c>
-      <c r="C103" s="2"/>
-      <c r="D103" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="E103" s="2"/>
-      <c r="F103" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="G103" t="s" s="2">
-        <v>76</v>
-      </c>
-      <c r="H103" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="I103" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="J103" t="s" s="2">
-        <v>86</v>
-      </c>
-      <c r="K103" t="s" s="2">
-        <v>451</v>
-      </c>
-      <c r="L103" t="s" s="2">
-        <v>509</v>
-      </c>
-      <c r="M103" t="s" s="2">
-        <v>510</v>
-      </c>
-      <c r="N103" t="s" s="2">
-        <v>511</v>
-      </c>
-      <c r="O103" t="s" s="2">
-        <v>512</v>
-      </c>
-      <c r="P103" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="Q103" s="2"/>
-      <c r="R103" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="S103" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="T103" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="U103" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="V103" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="W103" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="X103" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="Y103" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="Z103" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="AA103" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="AB103" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="AC103" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="AD103" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="AE103" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="AF103" t="s" s="2">
-        <v>508</v>
-      </c>
-      <c r="AG103" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="AH103" t="s" s="2">
-        <v>76</v>
-      </c>
-      <c r="AI103" t="s" s="2">
-        <v>92</v>
-      </c>
-      <c r="AJ103" t="s" s="2">
-        <v>513</v>
-      </c>
-      <c r="AK103" t="s" s="2">
-        <v>77</v>
-      </c>
-    </row>
-    <row r="104" hidden="true">
-      <c r="A104" t="s" s="2">
-        <v>514</v>
-      </c>
-      <c r="B104" t="s" s="2">
-        <v>514</v>
-      </c>
-      <c r="C104" s="2"/>
-      <c r="D104" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="E104" s="2"/>
-      <c r="F104" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="G104" t="s" s="2">
-        <v>85</v>
-      </c>
-      <c r="H104" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="I104" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="J104" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="K104" t="s" s="2">
-        <v>189</v>
-      </c>
-      <c r="L104" t="s" s="2">
-        <v>190</v>
-      </c>
-      <c r="M104" t="s" s="2">
-        <v>191</v>
-      </c>
-      <c r="N104" s="2"/>
-      <c r="O104" s="2"/>
-      <c r="P104" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="Q104" s="2"/>
-      <c r="R104" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="S104" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="T104" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="U104" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="V104" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="W104" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="X104" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="Y104" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="Z104" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="AA104" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="AB104" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="AC104" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="AD104" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="AE104" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="AF104" t="s" s="2">
-        <v>192</v>
-      </c>
-      <c r="AG104" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="AH104" t="s" s="2">
-        <v>85</v>
-      </c>
-      <c r="AI104" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="AJ104" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="AK104" t="s" s="2">
-        <v>77</v>
-      </c>
-    </row>
-    <row r="105" hidden="true">
-      <c r="A105" t="s" s="2">
-        <v>515</v>
-      </c>
-      <c r="B105" t="s" s="2">
-        <v>515</v>
-      </c>
-      <c r="C105" s="2"/>
-      <c r="D105" t="s" s="2">
-        <v>129</v>
-      </c>
-      <c r="E105" s="2"/>
-      <c r="F105" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="G105" t="s" s="2">
-        <v>76</v>
-      </c>
-      <c r="H105" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="I105" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="J105" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="K105" t="s" s="2">
-        <v>130</v>
-      </c>
-      <c r="L105" t="s" s="2">
-        <v>131</v>
-      </c>
-      <c r="M105" t="s" s="2">
-        <v>195</v>
-      </c>
-      <c r="N105" t="s" s="2">
-        <v>133</v>
-      </c>
-      <c r="O105" s="2"/>
-      <c r="P105" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="Q105" s="2"/>
-      <c r="R105" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="S105" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="T105" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="U105" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="V105" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="W105" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="X105" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="Y105" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="Z105" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="AA105" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="AB105" t="s" s="2">
-        <v>134</v>
-      </c>
-      <c r="AC105" t="s" s="2">
-        <v>135</v>
-      </c>
-      <c r="AD105" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="AE105" t="s" s="2">
-        <v>136</v>
-      </c>
-      <c r="AF105" t="s" s="2">
-        <v>196</v>
-      </c>
-      <c r="AG105" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="AH105" t="s" s="2">
-        <v>76</v>
-      </c>
-      <c r="AI105" t="s" s="2">
-        <v>92</v>
-      </c>
-      <c r="AJ105" t="s" s="2">
-        <v>138</v>
-      </c>
-      <c r="AK105" t="s" s="2">
-        <v>77</v>
-      </c>
-    </row>
-    <row r="106" hidden="true">
-      <c r="A106" t="s" s="2">
-        <v>516</v>
-      </c>
-      <c r="B106" t="s" s="2">
-        <v>516</v>
-      </c>
-      <c r="C106" s="2"/>
-      <c r="D106" t="s" s="2">
-        <v>460</v>
-      </c>
-      <c r="E106" s="2"/>
-      <c r="F106" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="G106" t="s" s="2">
-        <v>76</v>
-      </c>
-      <c r="H106" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="I106" t="s" s="2">
-        <v>86</v>
-      </c>
-      <c r="J106" t="s" s="2">
-        <v>86</v>
-      </c>
-      <c r="K106" t="s" s="2">
-        <v>130</v>
-      </c>
-      <c r="L106" t="s" s="2">
-        <v>461</v>
-      </c>
-      <c r="M106" t="s" s="2">
-        <v>462</v>
-      </c>
-      <c r="N106" t="s" s="2">
-        <v>133</v>
-      </c>
-      <c r="O106" t="s" s="2">
-        <v>142</v>
-      </c>
-      <c r="P106" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="Q106" s="2"/>
-      <c r="R106" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="S106" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="T106" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="U106" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="V106" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="W106" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="X106" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="Y106" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="Z106" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="AA106" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="AB106" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="AC106" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="AD106" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="AE106" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="AF106" t="s" s="2">
-        <v>463</v>
-      </c>
-      <c r="AG106" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="AH106" t="s" s="2">
-        <v>76</v>
-      </c>
-      <c r="AI106" t="s" s="2">
-        <v>92</v>
-      </c>
-      <c r="AJ106" t="s" s="2">
-        <v>138</v>
-      </c>
-      <c r="AK106" t="s" s="2">
-        <v>77</v>
-      </c>
-    </row>
-    <row r="107" hidden="true">
-      <c r="A107" t="s" s="2">
-        <v>517</v>
-      </c>
-      <c r="B107" t="s" s="2">
-        <v>517</v>
-      </c>
-      <c r="C107" s="2"/>
-      <c r="D107" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="E107" s="2"/>
-      <c r="F107" t="s" s="2">
-        <v>85</v>
-      </c>
-      <c r="G107" t="s" s="2">
-        <v>85</v>
-      </c>
-      <c r="H107" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="I107" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="J107" t="s" s="2">
-        <v>86</v>
-      </c>
-      <c r="K107" t="s" s="2">
-        <v>173</v>
-      </c>
-      <c r="L107" t="s" s="2">
-        <v>518</v>
-      </c>
-      <c r="M107" t="s" s="2">
-        <v>519</v>
-      </c>
-      <c r="N107" t="s" s="2">
-        <v>520</v>
-      </c>
-      <c r="O107" t="s" s="2">
-        <v>256</v>
-      </c>
-      <c r="P107" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="Q107" s="2"/>
-      <c r="R107" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="S107" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="T107" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="U107" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="V107" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="W107" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="X107" t="s" s="2">
-        <v>257</v>
-      </c>
-      <c r="Y107" t="s" s="2">
-        <v>258</v>
-      </c>
-      <c r="Z107" t="s" s="2">
-        <v>259</v>
-      </c>
-      <c r="AA107" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="AB107" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="AC107" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="AD107" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="AE107" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="AF107" t="s" s="2">
-        <v>517</v>
-      </c>
-      <c r="AG107" t="s" s="2">
-        <v>85</v>
-      </c>
-      <c r="AH107" t="s" s="2">
-        <v>85</v>
-      </c>
-      <c r="AI107" t="s" s="2">
-        <v>92</v>
-      </c>
-      <c r="AJ107" t="s" s="2">
-        <v>93</v>
-      </c>
-      <c r="AK107" t="s" s="2">
-        <v>77</v>
-      </c>
-    </row>
-    <row r="108" hidden="true">
-      <c r="A108" t="s" s="2">
-        <v>521</v>
-      </c>
-      <c r="B108" t="s" s="2">
-        <v>521</v>
-      </c>
-      <c r="C108" s="2"/>
-      <c r="D108" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="E108" s="2"/>
-      <c r="F108" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="G108" t="s" s="2">
-        <v>85</v>
-      </c>
-      <c r="H108" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="I108" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="J108" t="s" s="2">
-        <v>86</v>
-      </c>
-      <c r="K108" t="s" s="2">
-        <v>336</v>
-      </c>
-      <c r="L108" t="s" s="2">
-        <v>522</v>
-      </c>
-      <c r="M108" t="s" s="2">
-        <v>338</v>
-      </c>
-      <c r="N108" t="s" s="2">
-        <v>523</v>
-      </c>
-      <c r="O108" t="s" s="2">
-        <v>340</v>
-      </c>
-      <c r="P108" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="Q108" s="2"/>
-      <c r="R108" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="S108" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="T108" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="U108" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="V108" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="W108" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="X108" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="Y108" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="Z108" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="AA108" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="AB108" t="s" s="2">
-        <v>318</v>
-      </c>
-      <c r="AC108" s="2"/>
-      <c r="AD108" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="AE108" t="s" s="2">
-        <v>136</v>
-      </c>
-      <c r="AF108" t="s" s="2">
-        <v>521</v>
-      </c>
-      <c r="AG108" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="AH108" t="s" s="2">
-        <v>85</v>
-      </c>
-      <c r="AI108" t="s" s="2">
-        <v>92</v>
-      </c>
-      <c r="AJ108" t="s" s="2">
-        <v>93</v>
-      </c>
-      <c r="AK108" t="s" s="2">
-        <v>77</v>
-      </c>
-    </row>
-    <row r="109" hidden="true">
-      <c r="A109" t="s" s="2">
-        <v>524</v>
-      </c>
-      <c r="B109" t="s" s="2">
-        <v>521</v>
-      </c>
-      <c r="C109" t="s" s="2">
-        <v>343</v>
-      </c>
-      <c r="D109" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="E109" s="2"/>
-      <c r="F109" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="G109" t="s" s="2">
-        <v>85</v>
-      </c>
-      <c r="H109" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="I109" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="J109" t="s" s="2">
-        <v>86</v>
-      </c>
-      <c r="K109" t="s" s="2">
-        <v>344</v>
-      </c>
-      <c r="L109" t="s" s="2">
-        <v>522</v>
-      </c>
-      <c r="M109" t="s" s="2">
-        <v>338</v>
-      </c>
-      <c r="N109" t="s" s="2">
-        <v>523</v>
-      </c>
-      <c r="O109" t="s" s="2">
-        <v>340</v>
-      </c>
-      <c r="P109" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="Q109" s="2"/>
-      <c r="R109" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="S109" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="T109" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="U109" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="V109" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="W109" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="X109" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="Y109" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="Z109" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="AA109" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="AB109" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="AC109" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="AD109" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="AE109" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="AF109" t="s" s="2">
-        <v>521</v>
-      </c>
-      <c r="AG109" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="AH109" t="s" s="2">
-        <v>85</v>
-      </c>
-      <c r="AI109" t="s" s="2">
-        <v>92</v>
-      </c>
-      <c r="AJ109" t="s" s="2">
-        <v>93</v>
-      </c>
-      <c r="AK109" t="s" s="2">
-        <v>77</v>
-      </c>
-    </row>
-    <row r="110" hidden="true">
-      <c r="A110" t="s" s="2">
-        <v>525</v>
-      </c>
-      <c r="B110" t="s" s="2">
-        <v>526</v>
-      </c>
-      <c r="C110" s="2"/>
-      <c r="D110" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="E110" s="2"/>
-      <c r="F110" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="G110" t="s" s="2">
-        <v>85</v>
-      </c>
-      <c r="H110" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="I110" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="J110" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="K110" t="s" s="2">
-        <v>189</v>
-      </c>
-      <c r="L110" t="s" s="2">
-        <v>190</v>
-      </c>
-      <c r="M110" t="s" s="2">
-        <v>191</v>
-      </c>
-      <c r="N110" s="2"/>
-      <c r="O110" s="2"/>
-      <c r="P110" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="Q110" s="2"/>
-      <c r="R110" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="S110" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="T110" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="U110" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="V110" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="W110" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="X110" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="Y110" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="Z110" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="AA110" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="AB110" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="AC110" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="AD110" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="AE110" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="AF110" t="s" s="2">
-        <v>192</v>
-      </c>
-      <c r="AG110" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="AH110" t="s" s="2">
-        <v>85</v>
-      </c>
-      <c r="AI110" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="AJ110" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="AK110" t="s" s="2">
-        <v>77</v>
-      </c>
-    </row>
-    <row r="111" hidden="true">
-      <c r="A111" t="s" s="2">
-        <v>527</v>
-      </c>
-      <c r="B111" t="s" s="2">
-        <v>528</v>
-      </c>
-      <c r="C111" s="2"/>
-      <c r="D111" t="s" s="2">
-        <v>129</v>
-      </c>
-      <c r="E111" s="2"/>
-      <c r="F111" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="G111" t="s" s="2">
-        <v>76</v>
-      </c>
-      <c r="H111" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="I111" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="J111" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="K111" t="s" s="2">
-        <v>130</v>
-      </c>
-      <c r="L111" t="s" s="2">
-        <v>131</v>
-      </c>
-      <c r="M111" t="s" s="2">
-        <v>195</v>
-      </c>
-      <c r="N111" t="s" s="2">
-        <v>133</v>
-      </c>
-      <c r="O111" s="2"/>
-      <c r="P111" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="Q111" s="2"/>
-      <c r="R111" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="S111" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="T111" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="U111" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="V111" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="W111" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="X111" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="Y111" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="Z111" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="AA111" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="AB111" t="s" s="2">
-        <v>134</v>
-      </c>
-      <c r="AC111" t="s" s="2">
-        <v>135</v>
-      </c>
-      <c r="AD111" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="AE111" t="s" s="2">
-        <v>136</v>
-      </c>
-      <c r="AF111" t="s" s="2">
-        <v>196</v>
-      </c>
-      <c r="AG111" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="AH111" t="s" s="2">
-        <v>76</v>
-      </c>
-      <c r="AI111" t="s" s="2">
-        <v>92</v>
-      </c>
-      <c r="AJ111" t="s" s="2">
-        <v>138</v>
-      </c>
-      <c r="AK111" t="s" s="2">
-        <v>77</v>
-      </c>
-    </row>
-    <row r="112" hidden="true">
-      <c r="A112" t="s" s="2">
-        <v>529</v>
-      </c>
-      <c r="B112" t="s" s="2">
-        <v>530</v>
-      </c>
-      <c r="C112" s="2"/>
-      <c r="D112" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="E112" s="2"/>
-      <c r="F112" t="s" s="2">
-        <v>85</v>
-      </c>
-      <c r="G112" t="s" s="2">
-        <v>85</v>
-      </c>
-      <c r="H112" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="I112" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="J112" t="s" s="2">
-        <v>86</v>
-      </c>
-      <c r="K112" t="s" s="2">
-        <v>353</v>
-      </c>
-      <c r="L112" t="s" s="2">
-        <v>354</v>
-      </c>
-      <c r="M112" t="s" s="2">
-        <v>355</v>
-      </c>
-      <c r="N112" t="s" s="2">
-        <v>356</v>
-      </c>
-      <c r="O112" t="s" s="2">
-        <v>357</v>
-      </c>
-      <c r="P112" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="Q112" s="2"/>
-      <c r="R112" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="S112" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="T112" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="U112" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="V112" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="W112" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="X112" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="Y112" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="Z112" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="AA112" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="AB112" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="AC112" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="AD112" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="AE112" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="AF112" t="s" s="2">
-        <v>358</v>
-      </c>
-      <c r="AG112" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="AH112" t="s" s="2">
-        <v>85</v>
-      </c>
-      <c r="AI112" t="s" s="2">
-        <v>92</v>
-      </c>
-      <c r="AJ112" t="s" s="2">
-        <v>93</v>
-      </c>
-      <c r="AK112" t="s" s="2">
-        <v>77</v>
-      </c>
-    </row>
-    <row r="113" hidden="true">
-      <c r="A113" t="s" s="2">
-        <v>531</v>
-      </c>
-      <c r="B113" t="s" s="2">
-        <v>532</v>
-      </c>
-      <c r="C113" s="2"/>
-      <c r="D113" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="E113" s="2"/>
-      <c r="F113" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="G113" t="s" s="2">
-        <v>85</v>
-      </c>
-      <c r="H113" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="I113" t="s" s="2">
-        <v>86</v>
-      </c>
-      <c r="J113" t="s" s="2">
-        <v>86</v>
-      </c>
-      <c r="K113" t="s" s="2">
-        <v>106</v>
-      </c>
-      <c r="L113" t="s" s="2">
-        <v>362</v>
-      </c>
-      <c r="M113" t="s" s="2">
-        <v>363</v>
-      </c>
-      <c r="N113" t="s" s="2">
-        <v>227</v>
-      </c>
-      <c r="O113" t="s" s="2">
-        <v>364</v>
-      </c>
-      <c r="P113" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="Q113" t="s" s="2">
-        <v>365</v>
-      </c>
-      <c r="R113" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="S113" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="T113" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="U113" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="V113" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="W113" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="X113" t="s" s="2">
-        <v>168</v>
-      </c>
-      <c r="Y113" t="s" s="2">
-        <v>366</v>
-      </c>
-      <c r="Z113" t="s" s="2">
-        <v>367</v>
-      </c>
-      <c r="AA113" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="AB113" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="AC113" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="AD113" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="AE113" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="AF113" t="s" s="2">
-        <v>368</v>
-      </c>
-      <c r="AG113" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="AH113" t="s" s="2">
-        <v>85</v>
-      </c>
-      <c r="AI113" t="s" s="2">
-        <v>92</v>
-      </c>
-      <c r="AJ113" t="s" s="2">
-        <v>93</v>
-      </c>
-      <c r="AK113" t="s" s="2">
-        <v>77</v>
-      </c>
-    </row>
-    <row r="114" hidden="true">
-      <c r="A114" t="s" s="2">
-        <v>533</v>
-      </c>
-      <c r="B114" t="s" s="2">
-        <v>534</v>
-      </c>
-      <c r="C114" s="2"/>
-      <c r="D114" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="E114" s="2"/>
-      <c r="F114" t="s" s="2">
-        <v>85</v>
-      </c>
-      <c r="G114" t="s" s="2">
-        <v>85</v>
-      </c>
-      <c r="H114" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="I114" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="J114" t="s" s="2">
-        <v>86</v>
-      </c>
-      <c r="K114" t="s" s="2">
-        <v>189</v>
-      </c>
-      <c r="L114" t="s" s="2">
-        <v>371</v>
-      </c>
-      <c r="M114" t="s" s="2">
-        <v>372</v>
-      </c>
-      <c r="N114" t="s" s="2">
-        <v>227</v>
-      </c>
-      <c r="O114" t="s" s="2">
-        <v>373</v>
-      </c>
-      <c r="P114" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="Q114" s="2"/>
-      <c r="R114" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="S114" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="T114" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="U114" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="V114" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="W114" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="X114" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="Y114" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="Z114" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="AA114" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="AB114" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="AC114" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="AD114" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="AE114" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="AF114" t="s" s="2">
-        <v>374</v>
-      </c>
-      <c r="AG114" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="AH114" t="s" s="2">
-        <v>85</v>
-      </c>
-      <c r="AI114" t="s" s="2">
-        <v>92</v>
-      </c>
-      <c r="AJ114" t="s" s="2">
-        <v>93</v>
-      </c>
-      <c r="AK114" t="s" s="2">
-        <v>77</v>
-      </c>
-    </row>
-    <row r="115" hidden="true">
-      <c r="A115" t="s" s="2">
-        <v>535</v>
-      </c>
-      <c r="B115" t="s" s="2">
-        <v>536</v>
-      </c>
-      <c r="C115" s="2"/>
-      <c r="D115" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="E115" s="2"/>
-      <c r="F115" t="s" s="2">
-        <v>85</v>
-      </c>
-      <c r="G115" t="s" s="2">
-        <v>85</v>
-      </c>
-      <c r="H115" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="I115" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="J115" t="s" s="2">
-        <v>86</v>
-      </c>
-      <c r="K115" t="s" s="2">
-        <v>100</v>
-      </c>
-      <c r="L115" t="s" s="2">
-        <v>377</v>
-      </c>
-      <c r="M115" t="s" s="2">
-        <v>378</v>
-      </c>
-      <c r="N115" t="s" s="2">
-        <v>379</v>
-      </c>
-      <c r="O115" t="s" s="2">
-        <v>380</v>
-      </c>
-      <c r="P115" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="Q115" s="2"/>
-      <c r="R115" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="S115" t="s" s="2">
-        <v>381</v>
-      </c>
-      <c r="T115" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="U115" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="V115" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="W115" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="X115" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="Y115" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="Z115" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="AA115" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="AB115" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="AC115" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="AD115" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="AE115" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="AF115" t="s" s="2">
-        <v>382</v>
-      </c>
-      <c r="AG115" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="AH115" t="s" s="2">
-        <v>85</v>
-      </c>
-      <c r="AI115" t="s" s="2">
-        <v>383</v>
-      </c>
-      <c r="AJ115" t="s" s="2">
-        <v>93</v>
-      </c>
-      <c r="AK115" t="s" s="2">
-        <v>77</v>
-      </c>
-    </row>
-    <row r="116" hidden="true">
-      <c r="A116" t="s" s="2">
-        <v>537</v>
-      </c>
-      <c r="B116" t="s" s="2">
-        <v>538</v>
-      </c>
-      <c r="C116" s="2"/>
-      <c r="D116" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="E116" s="2"/>
-      <c r="F116" t="s" s="2">
-        <v>85</v>
-      </c>
-      <c r="G116" t="s" s="2">
-        <v>85</v>
-      </c>
-      <c r="H116" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="I116" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="J116" t="s" s="2">
-        <v>86</v>
-      </c>
-      <c r="K116" t="s" s="2">
-        <v>106</v>
-      </c>
-      <c r="L116" t="s" s="2">
-        <v>386</v>
-      </c>
-      <c r="M116" t="s" s="2">
-        <v>387</v>
-      </c>
-      <c r="N116" t="s" s="2">
-        <v>388</v>
-      </c>
-      <c r="O116" t="s" s="2">
-        <v>389</v>
-      </c>
-      <c r="P116" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="Q116" s="2"/>
-      <c r="R116" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="S116" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="T116" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="U116" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="V116" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="W116" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="X116" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="Y116" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="Z116" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="AA116" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="AB116" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="AC116" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="AD116" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="AE116" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="AF116" t="s" s="2">
-        <v>391</v>
-      </c>
-      <c r="AG116" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="AH116" t="s" s="2">
-        <v>85</v>
-      </c>
-      <c r="AI116" t="s" s="2">
-        <v>92</v>
-      </c>
-      <c r="AJ116" t="s" s="2">
-        <v>93</v>
-      </c>
-      <c r="AK116" t="s" s="2">
-        <v>77</v>
-      </c>
-    </row>
-    <row r="117" hidden="true">
-      <c r="A117" t="s" s="2">
-        <v>539</v>
-      </c>
-      <c r="B117" t="s" s="2">
-        <v>539</v>
-      </c>
-      <c r="C117" s="2"/>
-      <c r="D117" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="E117" s="2"/>
-      <c r="F117" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="G117" t="s" s="2">
-        <v>85</v>
-      </c>
-      <c r="H117" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="I117" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="J117" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="K117" t="s" s="2">
-        <v>173</v>
-      </c>
-      <c r="L117" t="s" s="2">
-        <v>540</v>
-      </c>
-      <c r="M117" t="s" s="2">
-        <v>541</v>
-      </c>
-      <c r="N117" t="s" s="2">
-        <v>542</v>
-      </c>
-      <c r="O117" t="s" s="2">
-        <v>396</v>
-      </c>
-      <c r="P117" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="Q117" s="2"/>
-      <c r="R117" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="S117" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="T117" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="U117" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="V117" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="W117" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="X117" t="s" s="2">
-        <v>397</v>
-      </c>
-      <c r="Y117" t="s" s="2">
-        <v>398</v>
-      </c>
-      <c r="Z117" t="s" s="2">
-        <v>399</v>
-      </c>
-      <c r="AA117" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="AB117" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="AC117" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="AD117" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="AE117" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="AF117" t="s" s="2">
-        <v>539</v>
-      </c>
-      <c r="AG117" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="AH117" t="s" s="2">
-        <v>85</v>
-      </c>
-      <c r="AI117" t="s" s="2">
-        <v>400</v>
-      </c>
-      <c r="AJ117" t="s" s="2">
-        <v>93</v>
-      </c>
-      <c r="AK117" t="s" s="2">
-        <v>77</v>
-      </c>
-    </row>
-    <row r="118" hidden="true">
-      <c r="A118" t="s" s="2">
-        <v>543</v>
-      </c>
-      <c r="B118" t="s" s="2">
-        <v>543</v>
-      </c>
-      <c r="C118" s="2"/>
-      <c r="D118" t="s" s="2">
-        <v>402</v>
-      </c>
-      <c r="E118" s="2"/>
-      <c r="F118" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="G118" t="s" s="2">
-        <v>76</v>
-      </c>
-      <c r="H118" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="I118" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="J118" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="K118" t="s" s="2">
-        <v>173</v>
-      </c>
-      <c r="L118" t="s" s="2">
-        <v>403</v>
-      </c>
-      <c r="M118" t="s" s="2">
-        <v>404</v>
-      </c>
-      <c r="N118" t="s" s="2">
-        <v>405</v>
-      </c>
-      <c r="O118" t="s" s="2">
-        <v>406</v>
-      </c>
-      <c r="P118" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="Q118" s="2"/>
-      <c r="R118" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="S118" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="T118" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="U118" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="V118" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="W118" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="X118" t="s" s="2">
-        <v>397</v>
-      </c>
-      <c r="Y118" t="s" s="2">
-        <v>407</v>
-      </c>
-      <c r="Z118" t="s" s="2">
-        <v>408</v>
-      </c>
-      <c r="AA118" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="AB118" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="AC118" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="AD118" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="AE118" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="AF118" t="s" s="2">
-        <v>543</v>
-      </c>
-      <c r="AG118" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="AH118" t="s" s="2">
-        <v>76</v>
-      </c>
-      <c r="AI118" t="s" s="2">
-        <v>92</v>
-      </c>
-      <c r="AJ118" t="s" s="2">
-        <v>93</v>
-      </c>
-      <c r="AK118" t="s" s="2">
-        <v>77</v>
-      </c>
-    </row>
-    <row r="119" hidden="true">
-      <c r="A119" t="s" s="2">
-        <v>544</v>
-      </c>
-      <c r="B119" t="s" s="2">
-        <v>544</v>
-      </c>
-      <c r="C119" s="2"/>
-      <c r="D119" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="E119" s="2"/>
-      <c r="F119" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="G119" t="s" s="2">
-        <v>76</v>
-      </c>
-      <c r="H119" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="I119" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="J119" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="K119" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="L119" t="s" s="2">
-        <v>545</v>
-      </c>
-      <c r="M119" t="s" s="2">
-        <v>546</v>
-      </c>
-      <c r="N119" t="s" s="2">
-        <v>454</v>
-      </c>
-      <c r="O119" t="s" s="2">
-        <v>455</v>
-      </c>
-      <c r="P119" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="Q119" s="2"/>
-      <c r="R119" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="S119" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="T119" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="U119" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="V119" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="W119" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="X119" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="Y119" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="Z119" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="AA119" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="AB119" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="AC119" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="AD119" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="AE119" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="AF119" t="s" s="2">
-        <v>544</v>
-      </c>
-      <c r="AG119" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="AH119" t="s" s="2">
-        <v>76</v>
-      </c>
-      <c r="AI119" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="AJ119" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="AK119" t="s" s="2">
         <v>77</v>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:AK119">
-    <filterColumn colId="7">
-      <customFilters>
-        <customFilter operator="notEqual" val=" "/>
-      </customFilters>
-    </filterColumn>
-    <filterColumn colId="27">
-      <filters blank="true"/>
-    </filterColumn>
-  </autoFilter>
-  <conditionalFormatting sqref="A2:AI118">
-    <cfRule type="expression" dxfId="0" priority="1">
-      <formula>$G2&lt;&gt;"Y"</formula>
-    </cfRule>
-    <cfRule type="expression" dxfId="1" priority="2">
-      <formula>$Q2&lt;&gt;""</formula>
-    </cfRule>
-  </conditionalFormatting>
   <pageMargins bottom="0.75" footer="0.3" header="0.3" left="0.7" right="0.7" top="0.75"/>
 </worksheet>
 </file>